--- a/tool/PMP/old/PMP_Sample.xlsx
+++ b/tool/PMP/old/PMP_Sample.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD8B775-AE80-4F1C-B0F2-69A12109E1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E813EEE7-D9D6-45FA-B251-5789A582DB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
   </bookViews>
   <sheets>
     <sheet name="Rain" sheetId="1" r:id="rId1"/>
     <sheet name="PMP" sheetId="2" r:id="rId2"/>
+    <sheet name="25020230" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,12 +38,327 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
   <si>
     <t>Year / Station</t>
   </si>
   <si>
-    <t>Station / Tr</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>tr</t>
+  </si>
+  <si>
+    <t>prob_l</t>
+  </si>
+  <si>
+    <t>prob_g</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>anglit</t>
+  </si>
+  <si>
+    <t>arcsine</t>
+  </si>
+  <si>
+    <t>argus</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>betaprime</t>
+  </si>
+  <si>
+    <t>bradford</t>
+  </si>
+  <si>
+    <t>burr</t>
+  </si>
+  <si>
+    <t>burr12</t>
+  </si>
+  <si>
+    <t>chi2</t>
+  </si>
+  <si>
+    <t>cosine</t>
+  </si>
+  <si>
+    <t>crystalball</t>
+  </si>
+  <si>
+    <t>dgamma</t>
+  </si>
+  <si>
+    <t>erlang</t>
+  </si>
+  <si>
+    <t>expon</t>
+  </si>
+  <si>
+    <t>exponnorm</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>fatiguelife</t>
+  </si>
+  <si>
+    <t>fisk</t>
+  </si>
+  <si>
+    <t>foldnorm</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>gausshyper</t>
+  </si>
+  <si>
+    <t>genexpon</t>
+  </si>
+  <si>
+    <t>genextreme</t>
+  </si>
+  <si>
+    <t>genhalflogistic</t>
+  </si>
+  <si>
+    <t>genhyperbolic</t>
+  </si>
+  <si>
+    <t>geninvgauss</t>
+  </si>
+  <si>
+    <t>genlogistic</t>
+  </si>
+  <si>
+    <t>gennorm</t>
+  </si>
+  <si>
+    <t>genpareto</t>
+  </si>
+  <si>
+    <t>gibrat</t>
+  </si>
+  <si>
+    <t>gompertz</t>
+  </si>
+  <si>
+    <t>gumbel_l</t>
+  </si>
+  <si>
+    <t>gumbel_r</t>
+  </si>
+  <si>
+    <t>halflogistic</t>
+  </si>
+  <si>
+    <t>halfnorm</t>
+  </si>
+  <si>
+    <t>hypsecant</t>
+  </si>
+  <si>
+    <t>invgamma</t>
+  </si>
+  <si>
+    <t>invgauss</t>
+  </si>
+  <si>
+    <t>invweibull</t>
+  </si>
+  <si>
+    <t>johnsonsb</t>
+  </si>
+  <si>
+    <t>johnsonsu</t>
+  </si>
+  <si>
+    <t>kappa3</t>
+  </si>
+  <si>
+    <t>kappa4</t>
+  </si>
+  <si>
+    <t>ksone</t>
+  </si>
+  <si>
+    <t>kstwobign</t>
+  </si>
+  <si>
+    <t>laplace</t>
+  </si>
+  <si>
+    <t>laplace_asymmetric</t>
+  </si>
+  <si>
+    <t>levy_l</t>
+  </si>
+  <si>
+    <t>levy_stable</t>
+  </si>
+  <si>
+    <t>loggamma</t>
+  </si>
+  <si>
+    <t>logistic</t>
+  </si>
+  <si>
+    <t>loglaplace</t>
+  </si>
+  <si>
+    <t>lognorm</t>
+  </si>
+  <si>
+    <t>loguniform</t>
+  </si>
+  <si>
+    <t>lomax</t>
+  </si>
+  <si>
+    <t>maxwell</t>
+  </si>
+  <si>
+    <t>mielke</t>
+  </si>
+  <si>
+    <t>moyal</t>
+  </si>
+  <si>
+    <t>nakagami</t>
+  </si>
+  <si>
+    <t>ncf</t>
+  </si>
+  <si>
+    <t>nct</t>
+  </si>
+  <si>
+    <t>ncx2</t>
+  </si>
+  <si>
+    <t>norm</t>
+  </si>
+  <si>
+    <t>pareto</t>
+  </si>
+  <si>
+    <t>pearson3</t>
+  </si>
+  <si>
+    <t>powerlaw</t>
+  </si>
+  <si>
+    <t>powerlognorm</t>
+  </si>
+  <si>
+    <t>powernorm</t>
+  </si>
+  <si>
+    <t>rayleigh</t>
+  </si>
+  <si>
+    <t>rdist</t>
+  </si>
+  <si>
+    <t>recipinvgauss</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>semicircular</t>
+  </si>
+  <si>
+    <t>skewnorm</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>trapezoid</t>
+  </si>
+  <si>
+    <t>triang</t>
+  </si>
+  <si>
+    <t>truncexpon</t>
+  </si>
+  <si>
+    <t>truncnorm</t>
+  </si>
+  <si>
+    <t>truncpareto</t>
+  </si>
+  <si>
+    <t>truncweibull_min</t>
+  </si>
+  <si>
+    <t>tukeylambda</t>
+  </si>
+  <si>
+    <t>uniform</t>
+  </si>
+  <si>
+    <t>vonmises</t>
+  </si>
+  <si>
+    <t>vonmises_line</t>
+  </si>
+  <si>
+    <t>wald</t>
+  </si>
+  <si>
+    <t>weibull_max</t>
+  </si>
+  <si>
+    <t>weibull_min</t>
+  </si>
+  <si>
+    <t>wrapcauchy</t>
+  </si>
+  <si>
+    <t>empirical_dist</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>risk_rate</t>
+  </si>
+  <si>
+    <t>emp_adamowski</t>
+  </si>
+  <si>
+    <t>25020230_1969_2009</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>zzgumbel</t>
+  </si>
+  <si>
+    <t>zzloggumbel</t>
+  </si>
+  <si>
+    <t>Tr</t>
+  </si>
+  <si>
+    <t>Excel-Gumbel</t>
+  </si>
+  <si>
+    <t>R.HydroTools-Gumbel</t>
   </si>
 </sst>
 </file>
@@ -84,9 +400,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -102,6 +424,1041 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2502023-Excel-Gumbel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>PMP!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>226</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B4A2-4502-9742-A60DED037D90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!$O$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020230-R.HydroTools-Gumbel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>PMP!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!$O$4:$O$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>122.61199999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>147.001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>166.86600000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>191.965</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>210.584</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>229.06700000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B4A2-4502-9742-A60DED037D90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="489679200"/>
+        <c:axId val="489674880"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="489679200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="489674880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="489674880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="489679200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>117311</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>182217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>45554</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>33130</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52EB77B0-162F-A9D5-023D-32098EA7E10C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2409,333 +3766,5289 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EEC4ED-A2A6-48CB-9363-E12F4E5CCB23}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="15" width="8.73046875" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="49.5" x14ac:dyDescent="0.45">
+      <c r="B1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="2">
+        <v>2502023</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2502026</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2502028</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2502069</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2802008</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2802023</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2802044</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2802060</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2802508</v>
+      </c>
+      <c r="K2" s="2">
+        <v>2802509</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2803504</v>
+      </c>
+      <c r="M2" s="2">
+        <v>2804031</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2804035</v>
+      </c>
+      <c r="O2" s="2">
+        <v>25020230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <f>_xlfn.CONCAT(B2,"-",B1)</f>
+        <v>2502023-Excel-Gumbel</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f t="shared" ref="C3:O3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
+        <v>2502026-Excel-Gumbel</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2502028-Excel-Gumbel</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2502069-Excel-Gumbel</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2802008-Excel-Gumbel</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2802023-Excel-Gumbel</v>
+      </c>
+      <c r="H3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2802044-Excel-Gumbel</v>
+      </c>
+      <c r="I3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2802060-Excel-Gumbel</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2802508-Excel-Gumbel</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2802509-Excel-Gumbel</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2803504-Excel-Gumbel</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2804031-Excel-Gumbel</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>2804035-Excel-Gumbel</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>25020230-R.HydroTools-Gumbel</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" s="3">
+        <v>2.33</v>
+      </c>
+      <c r="B4" s="3">
+        <v>103</v>
+      </c>
+      <c r="C4" s="3">
+        <v>107</v>
+      </c>
+      <c r="D4" s="3">
+        <v>111</v>
+      </c>
+      <c r="E4" s="3">
+        <v>92</v>
+      </c>
+      <c r="F4" s="3">
+        <v>102</v>
+      </c>
+      <c r="G4" s="3">
+        <v>102</v>
+      </c>
+      <c r="H4" s="3">
+        <v>92</v>
+      </c>
+      <c r="I4" s="3">
+        <v>91</v>
+      </c>
+      <c r="J4" s="3">
+        <v>100</v>
+      </c>
+      <c r="K4" s="3">
+        <v>100</v>
+      </c>
+      <c r="L4" s="3">
+        <v>89</v>
+      </c>
+      <c r="M4" s="3">
+        <v>98</v>
+      </c>
+      <c r="N4" s="3">
+        <v>96</v>
+      </c>
+      <c r="O4" s="3">
+        <v>122.61199999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" s="3">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>132</v>
+      </c>
+      <c r="C5" s="3">
+        <v>133</v>
+      </c>
+      <c r="D5" s="3">
+        <v>149</v>
+      </c>
+      <c r="E5" s="3">
+        <v>117</v>
+      </c>
+      <c r="F5" s="3">
+        <v>136</v>
+      </c>
+      <c r="G5" s="3">
+        <v>136</v>
+      </c>
+      <c r="H5" s="3">
+        <v>114</v>
+      </c>
+      <c r="I5" s="3">
+        <v>111</v>
+      </c>
+      <c r="J5" s="3">
+        <v>121</v>
+      </c>
+      <c r="K5" s="3">
+        <v>117</v>
+      </c>
+      <c r="L5" s="3">
+        <v>112</v>
+      </c>
+      <c r="M5" s="3">
+        <v>120</v>
+      </c>
+      <c r="N5" s="3">
+        <v>119</v>
+      </c>
+      <c r="O5" s="3">
+        <v>147.001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" s="3">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3">
+        <v>155</v>
+      </c>
+      <c r="C6" s="3">
+        <v>154</v>
+      </c>
+      <c r="D6" s="3">
+        <v>179</v>
+      </c>
+      <c r="E6" s="3">
+        <v>137</v>
+      </c>
+      <c r="F6" s="3">
+        <v>164</v>
+      </c>
+      <c r="G6" s="3">
+        <v>165</v>
+      </c>
+      <c r="H6" s="3">
+        <v>132</v>
+      </c>
+      <c r="I6" s="3">
+        <v>127</v>
+      </c>
+      <c r="J6" s="3">
+        <v>138</v>
+      </c>
+      <c r="K6" s="3">
+        <v>130</v>
+      </c>
+      <c r="L6" s="3">
+        <v>131</v>
+      </c>
+      <c r="M6" s="3">
+        <v>138</v>
+      </c>
+      <c r="N6" s="3">
+        <v>138</v>
+      </c>
+      <c r="O6" s="3">
+        <v>166.86600000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" s="3">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3">
+        <v>184</v>
+      </c>
+      <c r="C7" s="3">
+        <v>181</v>
+      </c>
+      <c r="D7" s="3">
+        <v>218</v>
+      </c>
+      <c r="E7" s="3">
+        <v>162</v>
+      </c>
+      <c r="F7" s="3">
+        <v>199</v>
+      </c>
+      <c r="G7" s="3">
+        <v>201</v>
+      </c>
+      <c r="H7" s="3">
+        <v>155</v>
+      </c>
+      <c r="I7" s="3">
+        <v>148</v>
+      </c>
+      <c r="J7" s="3">
+        <v>159</v>
+      </c>
+      <c r="K7" s="3">
+        <v>148</v>
+      </c>
+      <c r="L7" s="3">
+        <v>155</v>
+      </c>
+      <c r="M7" s="3">
+        <v>161</v>
+      </c>
+      <c r="N7" s="3">
+        <v>161</v>
+      </c>
+      <c r="O7" s="3">
+        <v>191.965</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A8" s="3">
+        <v>50</v>
+      </c>
+      <c r="B8" s="3">
+        <v>205</v>
+      </c>
+      <c r="C8" s="3">
+        <v>201</v>
+      </c>
+      <c r="D8" s="3">
+        <v>247</v>
+      </c>
+      <c r="E8" s="3">
+        <v>180</v>
+      </c>
+      <c r="F8" s="3">
+        <v>225</v>
+      </c>
+      <c r="G8" s="3">
+        <v>227</v>
+      </c>
+      <c r="H8" s="3">
+        <v>172</v>
+      </c>
+      <c r="I8" s="3">
+        <v>163</v>
+      </c>
+      <c r="J8" s="3">
+        <v>175</v>
+      </c>
+      <c r="K8" s="3">
+        <v>161</v>
+      </c>
+      <c r="L8" s="3">
+        <v>173</v>
+      </c>
+      <c r="M8" s="3">
+        <v>178</v>
+      </c>
+      <c r="N8" s="3">
+        <v>178</v>
+      </c>
+      <c r="O8" s="3">
+        <v>210.584</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A9" s="3">
+        <v>100</v>
+      </c>
+      <c r="B9" s="3">
+        <v>226</v>
+      </c>
+      <c r="C9" s="3">
+        <v>220</v>
+      </c>
+      <c r="D9" s="3">
+        <v>276</v>
+      </c>
+      <c r="E9" s="3">
+        <v>199</v>
+      </c>
+      <c r="F9" s="3">
+        <v>251</v>
+      </c>
+      <c r="G9" s="3">
+        <v>254</v>
+      </c>
+      <c r="H9" s="3">
+        <v>189</v>
+      </c>
+      <c r="I9" s="3">
+        <v>178</v>
+      </c>
+      <c r="J9" s="3">
+        <v>190</v>
+      </c>
+      <c r="K9" s="3">
+        <v>174</v>
+      </c>
+      <c r="L9" s="3">
+        <v>190</v>
+      </c>
+      <c r="M9" s="3">
+        <v>195</v>
+      </c>
+      <c r="N9" s="3">
+        <v>196</v>
+      </c>
+      <c r="O9" s="3">
+        <v>229.06700000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC3BD22-A60D-404D-A6C3-12A1448027F8}">
+  <dimension ref="A1:CV16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:100" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>105.29</v>
+      </c>
+      <c r="F2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="H2" s="1">
+        <v>111.52</v>
+      </c>
+      <c r="I2" s="1">
+        <v>107.997</v>
+      </c>
+      <c r="J2" s="1">
+        <v>104.071</v>
+      </c>
+      <c r="K2" s="1">
+        <v>90.5899</v>
+      </c>
+      <c r="L2" s="1">
+        <v>115.721</v>
+      </c>
+      <c r="M2" s="1">
+        <v>76.516199999999998</v>
+      </c>
+      <c r="N2" s="1">
+        <v>106.191</v>
+      </c>
+      <c r="O2" s="1">
+        <v>105.571</v>
+      </c>
+      <c r="P2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>102.877</v>
+      </c>
+      <c r="R2" s="1">
+        <v>106.512</v>
+      </c>
+      <c r="S2" s="1">
+        <v>86.660600000000002</v>
+      </c>
+      <c r="T2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="U2" s="1">
+        <v>107.223</v>
+      </c>
+      <c r="V2" s="1">
+        <v>107.077</v>
+      </c>
+      <c r="W2" s="1">
+        <v>108.127</v>
+      </c>
+      <c r="X2" s="1">
+        <v>114.503</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>106.67700000000001</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>111.73099999999999</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>84.124300000000005</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>113.199</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>117.679</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>115.09399999999999</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>99.575500000000005</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>108.518</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>101.511</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>97.251400000000004</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>113.126</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>112.82599999999999</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>101.80800000000001</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>99.069199999999995</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>100.453</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>104.55</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>102.181</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>101.249</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>110.76900000000001</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>111.85599999999999</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>114.486</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>96.061000000000007</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>100</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>100.27</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>108.628</v>
+      </c>
+      <c r="BA2" s="1">
+        <v>102.851</v>
+      </c>
+      <c r="BB2" s="1">
+        <v>109.196</v>
+      </c>
+      <c r="BC2" s="1">
+        <v>110.584</v>
+      </c>
+      <c r="BD2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>109</v>
+      </c>
+      <c r="BF2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>99.021100000000004</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>126.483</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>104.449</v>
+      </c>
+      <c r="BJ2" s="1">
+        <v>100.69</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>100.03</v>
+      </c>
+      <c r="BL2" s="1">
+        <v>107.346</v>
+      </c>
+      <c r="BM2" s="1">
+        <v>104.224</v>
+      </c>
+      <c r="BN2" s="1">
+        <v>107.31399999999999</v>
+      </c>
+      <c r="BO2" s="1">
+        <v>-11.0053</v>
+      </c>
+      <c r="BP2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="BQ2" s="1">
+        <v>86.660600000000002</v>
+      </c>
+      <c r="BR2" s="1">
+        <v>108.60899999999999</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>78.021199999999993</v>
+      </c>
+      <c r="BT2" s="1">
+        <v>109.31</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>111.61499999999999</v>
+      </c>
+      <c r="BV2" s="1">
+        <v>103.432</v>
+      </c>
+      <c r="BW2" s="1">
+        <v>67.500200000000007</v>
+      </c>
+      <c r="BX2" s="1">
+        <v>105.86199999999999</v>
+      </c>
+      <c r="BY2" s="1">
+        <v>110.85899999999999</v>
+      </c>
+      <c r="BZ2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="CA2" s="1">
+        <v>116.589</v>
+      </c>
+      <c r="CB2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="CC2" s="1">
+        <v>129.82300000000001</v>
+      </c>
+      <c r="CD2" s="1">
+        <v>116.613</v>
+      </c>
+      <c r="CE2" s="1">
+        <v>90.456699999999998</v>
+      </c>
+      <c r="CF2" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="CG2" s="1">
+        <v>84.0655</v>
+      </c>
+      <c r="CH2" s="1">
+        <v>95.730099999999993</v>
+      </c>
+      <c r="CI2" s="1">
+        <v>100</v>
+      </c>
+      <c r="CJ2" s="1">
+        <v>100</v>
+      </c>
+      <c r="CK2" s="1">
+        <v>2.96705</v>
+      </c>
+      <c r="CL2" s="1">
+        <v>97.678100000000001</v>
+      </c>
+      <c r="CM2" s="1">
+        <v>96.446799999999996</v>
+      </c>
+      <c r="CN2" s="1">
+        <v>159.721</v>
+      </c>
+      <c r="CO2" s="1">
+        <v>109.47199999999999</v>
+      </c>
+      <c r="CP2" s="1">
+        <v>100.309</v>
+      </c>
+      <c r="CQ2" s="1">
+        <v>116.998</v>
+      </c>
+      <c r="CR2" s="1">
+        <v>96.317999999999998</v>
+      </c>
+      <c r="CS2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU2" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV2" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
         <v>2.33</v>
       </c>
-      <c r="C1" s="1">
+      <c r="C3" s="1">
+        <v>0.57081499999999996</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.42918499999999998</v>
+      </c>
+      <c r="E3" s="1">
+        <v>111.379</v>
+      </c>
+      <c r="F3" s="1">
+        <v>114.28700000000001</v>
+      </c>
+      <c r="G3" s="1">
+        <v>117.78100000000001</v>
+      </c>
+      <c r="H3" s="1">
+        <v>118.01300000000001</v>
+      </c>
+      <c r="I3" s="1">
+        <v>116.04600000000001</v>
+      </c>
+      <c r="J3" s="1">
+        <v>110.43300000000001</v>
+      </c>
+      <c r="K3" s="1">
+        <v>99.137699999999995</v>
+      </c>
+      <c r="L3" s="1">
+        <v>122.631</v>
+      </c>
+      <c r="M3" s="1">
+        <v>88.101299999999995</v>
+      </c>
+      <c r="N3" s="1">
+        <v>112.31699999999999</v>
+      </c>
+      <c r="O3" s="1">
+        <v>111.833</v>
+      </c>
+      <c r="P3" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>115.94199999999999</v>
+      </c>
+      <c r="R3" s="1">
+        <v>112.557</v>
+      </c>
+      <c r="S3" s="1">
+        <v>96.941400000000002</v>
+      </c>
+      <c r="T3" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="U3" s="1">
+        <v>113.23399999999999</v>
+      </c>
+      <c r="V3" s="1">
+        <v>113.119</v>
+      </c>
+      <c r="W3" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="X3" s="1">
+        <v>114.572</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>112.726</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>119.681</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>93.846199999999996</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>119.205</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>125.488</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>121.026</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>107.1</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>114.27800000000001</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>113.20699999999999</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>100.283</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>118.83499999999999</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>118.032</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>107.35299999999999</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>104.77</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>106.911</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>112.10599999999999</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>110.739</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>108.654</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>107.932</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>118.82899999999999</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>117.621</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>125.036</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>104.84</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>110.197</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>107.42100000000001</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>110.938</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>112.983</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>119.254</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>116.01</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>116.357</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>112.589</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>114.03700000000001</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>107.56100000000001</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>145.53800000000001</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>110.666</v>
+      </c>
+      <c r="BJ3" s="1">
+        <v>107.348</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>105.279</v>
+      </c>
+      <c r="BL3" s="1">
+        <v>113.34399999999999</v>
+      </c>
+      <c r="BM3" s="1">
+        <v>110.51</v>
+      </c>
+      <c r="BN3" s="1">
+        <v>113.3</v>
+      </c>
+      <c r="BO3" s="1">
+        <v>62.697800000000001</v>
+      </c>
+      <c r="BP3" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="BQ3" s="1">
+        <v>96.941400000000002</v>
+      </c>
+      <c r="BR3" s="1">
+        <v>114.536</v>
+      </c>
+      <c r="BS3" s="1">
+        <v>87.360100000000003</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>115.205</v>
+      </c>
+      <c r="BU3" s="1">
+        <v>117.34699999999999</v>
+      </c>
+      <c r="BV3" s="1">
+        <v>109.741</v>
+      </c>
+      <c r="BW3" s="1">
+        <v>75.443899999999999</v>
+      </c>
+      <c r="BX3" s="1">
+        <v>111.96</v>
+      </c>
+      <c r="BY3" s="1">
+        <v>116.053</v>
+      </c>
+      <c r="BZ3" s="1">
+        <v>114.79300000000001</v>
+      </c>
+      <c r="CA3" s="1">
+        <v>123.045</v>
+      </c>
+      <c r="CB3" s="1">
+        <v>113.30200000000001</v>
+      </c>
+      <c r="CC3" s="1">
+        <v>136.79499999999999</v>
+      </c>
+      <c r="CD3" s="1">
+        <v>123.19799999999999</v>
+      </c>
+      <c r="CE3" s="1">
+        <v>98.857299999999995</v>
+      </c>
+      <c r="CF3" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="CG3" s="1">
+        <v>92.069800000000001</v>
+      </c>
+      <c r="CH3" s="1">
+        <v>104.181</v>
+      </c>
+      <c r="CI3" s="1">
+        <v>108.786</v>
+      </c>
+      <c r="CJ3" s="1">
+        <v>108.498</v>
+      </c>
+      <c r="CK3" s="1">
+        <v>3.2704300000000002</v>
+      </c>
+      <c r="CL3" s="1">
+        <v>105.13500000000001</v>
+      </c>
+      <c r="CM3" s="1">
+        <v>100.371</v>
+      </c>
+      <c r="CN3" s="1">
+        <v>159.89500000000001</v>
+      </c>
+      <c r="CO3" s="1">
+        <v>115.33799999999999</v>
+      </c>
+      <c r="CP3" s="1">
+        <v>108.851</v>
+      </c>
+      <c r="CQ3" s="1">
+        <v>122.61199999999999</v>
+      </c>
+      <c r="CR3" s="1">
+        <v>102.22499999999999</v>
+      </c>
+      <c r="CS3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU3" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV3" s="1">
+        <v>0.729209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
         <v>5</v>
       </c>
-      <c r="D1" s="1">
+      <c r="C4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>135.06899999999999</v>
+      </c>
+      <c r="F4" s="1">
+        <v>138.881</v>
+      </c>
+      <c r="G4" s="1">
+        <v>145.684</v>
+      </c>
+      <c r="H4" s="1">
+        <v>138.33000000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>140.715</v>
+      </c>
+      <c r="J4" s="1">
+        <v>135.857</v>
+      </c>
+      <c r="K4" s="1">
+        <v>129.57900000000001</v>
+      </c>
+      <c r="L4" s="1">
+        <v>142.167</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N4" s="1">
+        <v>135.61000000000001</v>
+      </c>
+      <c r="O4" s="1">
+        <v>134.40100000000001</v>
+      </c>
+      <c r="P4" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>133.84100000000001</v>
+      </c>
+      <c r="R4" s="1">
+        <v>135.364</v>
+      </c>
+      <c r="S4" s="1">
+        <v>148.34299999999999</v>
+      </c>
+      <c r="T4" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="U4" s="1">
+        <v>135.61199999999999</v>
+      </c>
+      <c r="V4" s="1">
+        <v>135.874</v>
+      </c>
+      <c r="W4" s="1">
+        <v>136.191</v>
+      </c>
+      <c r="X4" s="1">
+        <v>114.86</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>135.53399999999999</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>143.36600000000001</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>142.45400000000001</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>137.989</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>146.28700000000001</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>138.953</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>139.63499999999999</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>136.31800000000001</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>144.66399999999999</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>117.735</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>137.28</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>134.852</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>131.44300000000001</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>130.56700000000001</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>134.22300000000001</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>131.316</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>134.928</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>135.29599999999999</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>136.96299999999999</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>141.88900000000001</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>136.72200000000001</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>159.178</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>133.95500000000001</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>137.79900000000001</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>129.04400000000001</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>134.446</v>
+      </c>
+      <c r="BA4" s="1">
+        <v>146.429</v>
+      </c>
+      <c r="BB4" s="1">
+        <v>142.06200000000001</v>
+      </c>
+      <c r="BC4" s="1">
+        <v>136.18199999999999</v>
+      </c>
+      <c r="BD4" s="1">
+        <v>132.947</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>142.91900000000001</v>
+      </c>
+      <c r="BF4" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="BG4" s="1">
+        <v>135.41800000000001</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>240.80699999999999</v>
+      </c>
+      <c r="BI4" s="1">
+        <v>135.136</v>
+      </c>
+      <c r="BJ4" s="1">
+        <v>136.44300000000001</v>
+      </c>
+      <c r="BK4" s="1">
+        <v>129.59200000000001</v>
+      </c>
+      <c r="BL4" s="1">
+        <v>135.654</v>
+      </c>
+      <c r="BM4" s="1">
+        <v>135.71</v>
+      </c>
+      <c r="BN4" s="1">
+        <v>135.54300000000001</v>
+      </c>
+      <c r="BO4" s="1">
+        <v>353.13299999999998</v>
+      </c>
+      <c r="BP4" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="BQ4" s="1">
+        <v>148.34299999999999</v>
+      </c>
+      <c r="BR4" s="1">
+        <v>135.85</v>
+      </c>
+      <c r="BS4" s="1">
+        <v>122.88800000000001</v>
+      </c>
+      <c r="BT4" s="1">
+        <v>136.196</v>
+      </c>
+      <c r="BU4" s="1">
+        <v>136.63200000000001</v>
+      </c>
+      <c r="BV4" s="1">
+        <v>134.999</v>
+      </c>
+      <c r="BW4" s="1">
+        <v>92.534199999999998</v>
+      </c>
+      <c r="BX4" s="1">
+        <v>135.34899999999999</v>
+      </c>
+      <c r="BY4" s="1">
+        <v>135.899</v>
+      </c>
+      <c r="BZ4" s="1">
+        <v>140.30500000000001</v>
+      </c>
+      <c r="CA4" s="1">
+        <v>141.84700000000001</v>
+      </c>
+      <c r="CB4" s="1">
+        <v>135.542</v>
+      </c>
+      <c r="CC4" s="1">
+        <v>156.798</v>
+      </c>
+      <c r="CD4" s="1">
+        <v>142.09</v>
+      </c>
+      <c r="CE4" s="1">
+        <v>128.99100000000001</v>
+      </c>
+      <c r="CF4" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="CG4" s="1">
+        <v>123.018</v>
+      </c>
+      <c r="CH4" s="1">
+        <v>132.72300000000001</v>
+      </c>
+      <c r="CI4" s="1">
+        <v>136.93799999999999</v>
+      </c>
+      <c r="CJ4" s="1">
+        <v>136</v>
+      </c>
+      <c r="CK4" s="1">
+        <v>4.4239699999999997</v>
+      </c>
+      <c r="CL4" s="1">
+        <v>131.55099999999999</v>
+      </c>
+      <c r="CM4" s="1">
+        <v>122.336</v>
+      </c>
+      <c r="CN4" s="1">
+        <v>159.99799999999999</v>
+      </c>
+      <c r="CO4" s="1">
+        <v>135.964</v>
+      </c>
+      <c r="CP4" s="1">
+        <v>136.494</v>
+      </c>
+      <c r="CQ4" s="1">
+        <v>147.001</v>
+      </c>
+      <c r="CR4" s="1">
+        <v>132.39099999999999</v>
+      </c>
+      <c r="CS4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU4" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV4" s="1">
+        <v>0.67232000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
         <v>10</v>
       </c>
-      <c r="E1" s="1">
+      <c r="C5" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>151.779</v>
+      </c>
+      <c r="F5" s="1">
+        <v>152.80099999999999</v>
+      </c>
+      <c r="G5" s="1">
+        <v>152.41999999999999</v>
+      </c>
+      <c r="H5" s="1">
+        <v>147.82900000000001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>150.77000000000001</v>
+      </c>
+      <c r="J5" s="1">
+        <v>154.33199999999999</v>
+      </c>
+      <c r="K5" s="1">
+        <v>144.309</v>
+      </c>
+      <c r="L5" s="1">
+        <v>149.79900000000001</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="1">
+        <v>151.52500000000001</v>
+      </c>
+      <c r="O5" s="1">
+        <v>148.035</v>
+      </c>
+      <c r="P5" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>145.38800000000001</v>
+      </c>
+      <c r="R5" s="1">
+        <v>150.79300000000001</v>
+      </c>
+      <c r="S5" s="1">
+        <v>195.00299999999999</v>
+      </c>
+      <c r="T5" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="U5" s="1">
+        <v>150.49100000000001</v>
+      </c>
+      <c r="V5" s="1">
+        <v>151.232</v>
+      </c>
+      <c r="W5" s="1">
+        <v>152.607</v>
+      </c>
+      <c r="X5" s="1">
+        <v>115.074</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>150.94900000000001</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>152.501</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>186.578</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>147.20400000000001</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>153.62799999999999</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>147.61699999999999</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>165.39699999999999</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>152.41800000000001</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>154.429</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>137.62799999999999</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>147.54900000000001</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>144.21600000000001</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>151.06299999999999</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>151.989</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>154.43299999999999</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>146.65600000000001</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>152.078</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>155.386</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>160.608</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>150.74</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>147.60300000000001</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>174.07599999999999</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>146.94999999999999</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>157.6</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>160.92699999999999</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>145.47999999999999</v>
+      </c>
+      <c r="AZ5" s="1">
+        <v>153.93</v>
+      </c>
+      <c r="BA5" s="1">
+        <v>152.99</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>159.34399999999999</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>148.077</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>147.94</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>175.40600000000001</v>
+      </c>
+      <c r="BF5" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="BG5" s="1">
+        <v>147.67699999999999</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>327.29000000000002</v>
+      </c>
+      <c r="BI5" s="1">
+        <v>152.357</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>160.34899999999999</v>
+      </c>
+      <c r="BK5" s="1">
+        <v>150.761</v>
+      </c>
+      <c r="BL5" s="1">
+        <v>150.47200000000001</v>
+      </c>
+      <c r="BM5" s="1">
+        <v>154.053</v>
+      </c>
+      <c r="BN5" s="1">
+        <v>150.29900000000001</v>
+      </c>
+      <c r="BO5" s="1">
+        <v>560.17399999999998</v>
+      </c>
+      <c r="BP5" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="BQ5" s="1">
+        <v>195.00299999999999</v>
+      </c>
+      <c r="BR5" s="1">
+        <v>149.376</v>
+      </c>
+      <c r="BS5" s="1">
+        <v>140.76499999999999</v>
+      </c>
+      <c r="BT5" s="1">
+        <v>149.40899999999999</v>
+      </c>
+      <c r="BU5" s="1">
+        <v>147.934</v>
+      </c>
+      <c r="BV5" s="1">
+        <v>153.00800000000001</v>
+      </c>
+      <c r="BW5" s="1">
+        <v>94.675700000000006</v>
+      </c>
+      <c r="BX5" s="1">
+        <v>151.51300000000001</v>
+      </c>
+      <c r="BY5" s="1">
+        <v>149.375</v>
+      </c>
+      <c r="BZ5" s="1">
+        <v>153.39599999999999</v>
+      </c>
+      <c r="CA5" s="1">
+        <v>149.55000000000001</v>
+      </c>
+      <c r="CB5" s="1">
+        <v>150.29599999999999</v>
+      </c>
+      <c r="CC5" s="1">
+        <v>164.61</v>
+      </c>
+      <c r="CD5" s="1">
+        <v>149.47</v>
+      </c>
+      <c r="CE5" s="1">
+        <v>143.84800000000001</v>
+      </c>
+      <c r="CF5" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="CG5" s="1">
+        <v>139.92699999999999</v>
+      </c>
+      <c r="CH5" s="1">
+        <v>146.012</v>
+      </c>
+      <c r="CI5" s="1">
+        <v>148.857</v>
+      </c>
+      <c r="CJ5" s="1">
+        <v>148</v>
+      </c>
+      <c r="CK5" s="1">
+        <v>5.1534599999999999</v>
+      </c>
+      <c r="CL5" s="1">
+        <v>145.185</v>
+      </c>
+      <c r="CM5" s="1">
+        <v>145.64699999999999</v>
+      </c>
+      <c r="CN5" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO5" s="1">
+        <v>148.64699999999999</v>
+      </c>
+      <c r="CP5" s="1">
+        <v>148.55600000000001</v>
+      </c>
+      <c r="CQ5" s="1">
+        <v>166.86600000000001</v>
+      </c>
+      <c r="CR5" s="1">
+        <v>163.42699999999999</v>
+      </c>
+      <c r="CS5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU5" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV5" s="1">
+        <v>0.65132199999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.93333299999999997</v>
+      </c>
+      <c r="D6" s="1">
+        <v>6.6666699999999995E-2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>160.43799999999999</v>
+      </c>
+      <c r="F6" s="1">
+        <v>158.745</v>
+      </c>
+      <c r="G6" s="1">
+        <v>153.70500000000001</v>
+      </c>
+      <c r="H6" s="1">
+        <v>151.387</v>
+      </c>
+      <c r="I6" s="1">
+        <v>153.99</v>
+      </c>
+      <c r="J6" s="1">
+        <v>164.05</v>
+      </c>
+      <c r="K6" s="1">
+        <v>149.429</v>
+      </c>
+      <c r="L6" s="1">
+        <v>152.43199999999999</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N6" s="1">
+        <v>159.60599999999999</v>
+      </c>
+      <c r="O6" s="1">
+        <v>154.24600000000001</v>
+      </c>
+      <c r="P6" s="1">
+        <v>157.654</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>151.48699999999999</v>
+      </c>
+      <c r="R6" s="1">
+        <v>158.583</v>
+      </c>
+      <c r="S6" s="1">
+        <v>222.298</v>
+      </c>
+      <c r="T6" s="1">
+        <v>157.654</v>
+      </c>
+      <c r="U6" s="1">
+        <v>157.92500000000001</v>
+      </c>
+      <c r="V6" s="1">
+        <v>158.97499999999999</v>
+      </c>
+      <c r="W6" s="1">
+        <v>161.55099999999999</v>
+      </c>
+      <c r="X6" s="1">
+        <v>115.185</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>158.727</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>155.28899999999999</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>212.38900000000001</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>150.83699999999999</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>155.87100000000001</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>151.09700000000001</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>179.55500000000001</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>161.16499999999999</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>156.91900000000001</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>151.35</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>148.45699999999999</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>162.13300000000001</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>164.113</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>164.95</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>155.41</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>160.988</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>166.185</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>173.94900000000001</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>153.65600000000001</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>152.56299999999999</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>179.041</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>151.31800000000001</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>162.4</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>173.20599999999999</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>155.09399999999999</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>165.328</v>
+      </c>
+      <c r="BA6" s="1">
+        <v>154.971</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>167.96799999999999</v>
+      </c>
+      <c r="BC6" s="1">
+        <v>153.68299999999999</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>156.108</v>
+      </c>
+      <c r="BE6" s="1">
+        <v>197.726</v>
+      </c>
+      <c r="BF6" s="1">
+        <v>157.654</v>
+      </c>
+      <c r="BG6" s="1">
+        <v>151.77699999999999</v>
+      </c>
+      <c r="BH6" s="1">
+        <v>377.87900000000002</v>
+      </c>
+      <c r="BI6" s="1">
+        <v>161.19200000000001</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>173.91900000000001</v>
+      </c>
+      <c r="BK6" s="1">
+        <v>163.047</v>
+      </c>
+      <c r="BL6" s="1">
+        <v>157.87100000000001</v>
+      </c>
+      <c r="BM6" s="1">
+        <v>163.69900000000001</v>
+      </c>
+      <c r="BN6" s="1">
+        <v>157.66300000000001</v>
+      </c>
+      <c r="BO6" s="1">
+        <v>667.77800000000002</v>
+      </c>
+      <c r="BP6" s="1">
+        <v>157.654</v>
+      </c>
+      <c r="BQ6" s="1">
+        <v>222.298</v>
+      </c>
+      <c r="BR6" s="1">
+        <v>155.946</v>
+      </c>
+      <c r="BS6" s="1">
+        <v>147.02799999999999</v>
+      </c>
+      <c r="BT6" s="1">
+        <v>155.81800000000001</v>
+      </c>
+      <c r="BU6" s="1">
+        <v>153.20099999999999</v>
+      </c>
+      <c r="BV6" s="1">
+        <v>162.28700000000001</v>
+      </c>
+      <c r="BW6" s="1">
+        <v>94.902199999999993</v>
+      </c>
+      <c r="BX6" s="1">
+        <v>159.77799999999999</v>
+      </c>
+      <c r="BY6" s="1">
+        <v>156.16200000000001</v>
+      </c>
+      <c r="BZ6" s="1">
+        <v>158.501</v>
+      </c>
+      <c r="CA6" s="1">
+        <v>152.24199999999999</v>
+      </c>
+      <c r="CB6" s="1">
+        <v>157.65799999999999</v>
+      </c>
+      <c r="CC6" s="1">
+        <v>167.11699999999999</v>
+      </c>
+      <c r="CD6" s="1">
+        <v>152.00200000000001</v>
+      </c>
+      <c r="CE6" s="1">
+        <v>149.077</v>
+      </c>
+      <c r="CF6" s="1">
+        <v>157.654</v>
+      </c>
+      <c r="CG6" s="1">
+        <v>146.21100000000001</v>
+      </c>
+      <c r="CH6" s="1">
+        <v>150.59</v>
+      </c>
+      <c r="CI6" s="1">
+        <v>152.71899999999999</v>
+      </c>
+      <c r="CJ6" s="1">
+        <v>152</v>
+      </c>
+      <c r="CK6" s="1">
+        <v>5.45</v>
+      </c>
+      <c r="CL6" s="1">
+        <v>150.035</v>
+      </c>
+      <c r="CM6" s="1">
+        <v>160.61600000000001</v>
+      </c>
+      <c r="CN6" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO6" s="1">
+        <v>154.696</v>
+      </c>
+      <c r="CP6" s="1">
+        <v>152.577</v>
+      </c>
+      <c r="CQ6" s="1">
+        <v>178.07300000000001</v>
+      </c>
+      <c r="CR6" s="1">
+        <v>184.047</v>
+      </c>
+      <c r="CS6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU6" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV6" s="1">
+        <v>0.64473599999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="1">
+        <v>166.22800000000001</v>
+      </c>
+      <c r="F7" s="1">
+        <v>162.24100000000001</v>
+      </c>
+      <c r="G7" s="1">
+        <v>154.15700000000001</v>
+      </c>
+      <c r="H7" s="1">
+        <v>153.328</v>
+      </c>
+      <c r="I7" s="1">
+        <v>155.56399999999999</v>
+      </c>
+      <c r="J7" s="1">
+        <v>170.59800000000001</v>
+      </c>
+      <c r="K7" s="1">
+        <v>152.03</v>
+      </c>
+      <c r="L7" s="1">
+        <v>153.87899999999999</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="1">
+        <v>164.94900000000001</v>
+      </c>
+      <c r="O7" s="1">
+        <v>158.065</v>
+      </c>
+      <c r="P7" s="1">
+        <v>162.47499999999999</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>155.63300000000001</v>
+      </c>
+      <c r="R7" s="1">
+        <v>163.71700000000001</v>
+      </c>
+      <c r="S7" s="1">
+        <v>241.66399999999999</v>
+      </c>
+      <c r="T7" s="1">
+        <v>162.47499999999999</v>
+      </c>
+      <c r="U7" s="1">
+        <v>162.798</v>
+      </c>
+      <c r="V7" s="1">
+        <v>164.07499999999999</v>
+      </c>
+      <c r="W7" s="1">
+        <v>167.733</v>
+      </c>
+      <c r="X7" s="1">
+        <v>115.26</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>163.852</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>156.613</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>230.702</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>152.88200000000001</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>156.953</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>153.101</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>189.30699999999999</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>167.203</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>157.976</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>162.113</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>155.09399999999999</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>151.096</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>169.88399999999999</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>172.607</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>171.96199999999999</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>161.58600000000001</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>166.95500000000001</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>173.54599999999999</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>183.29</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>155.15199999999999</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>155.65299999999999</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>181.524</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>153.50899999999999</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>164.8</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>181.477</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>161.916</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>173.41399999999999</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>155.98599999999999</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>173.61600000000001</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>157.24199999999999</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>161.75399999999999</v>
+      </c>
+      <c r="BE7" s="1">
+        <v>215.26</v>
+      </c>
+      <c r="BF7" s="1">
+        <v>162.476</v>
+      </c>
+      <c r="BG7" s="1">
+        <v>153.83000000000001</v>
+      </c>
+      <c r="BH7" s="1">
+        <v>413.77300000000002</v>
+      </c>
+      <c r="BI7" s="1">
+        <v>167.05600000000001</v>
+      </c>
+      <c r="BJ7" s="1">
+        <v>183.45699999999999</v>
+      </c>
+      <c r="BK7" s="1">
+        <v>171.74799999999999</v>
+      </c>
+      <c r="BL7" s="1">
+        <v>162.71899999999999</v>
+      </c>
+      <c r="BM7" s="1">
+        <v>170.196</v>
+      </c>
+      <c r="BN7" s="1">
+        <v>162.48500000000001</v>
+      </c>
+      <c r="BO7" s="1">
+        <v>739.79100000000005</v>
+      </c>
+      <c r="BP7" s="1">
+        <v>162.47499999999999</v>
+      </c>
+      <c r="BQ7" s="1">
+        <v>241.66399999999999</v>
+      </c>
+      <c r="BR7" s="1">
+        <v>160.184</v>
+      </c>
+      <c r="BS7" s="1">
+        <v>150.21600000000001</v>
+      </c>
+      <c r="BT7" s="1">
+        <v>159.95400000000001</v>
+      </c>
+      <c r="BU7" s="1">
+        <v>156.53</v>
+      </c>
+      <c r="BV7" s="1">
+        <v>168.45500000000001</v>
+      </c>
+      <c r="BW7" s="1">
+        <v>94.958399999999997</v>
+      </c>
+      <c r="BX7" s="1">
+        <v>165.26300000000001</v>
+      </c>
+      <c r="BY7" s="1">
+        <v>160.624</v>
+      </c>
+      <c r="BZ7" s="1">
+        <v>161.33199999999999</v>
+      </c>
+      <c r="CA7" s="1">
+        <v>153.72800000000001</v>
+      </c>
+      <c r="CB7" s="1">
+        <v>162.47999999999999</v>
+      </c>
+      <c r="CC7" s="1">
+        <v>168.35400000000001</v>
+      </c>
+      <c r="CD7" s="1">
+        <v>153.505</v>
+      </c>
+      <c r="CE7" s="1">
+        <v>151.74799999999999</v>
+      </c>
+      <c r="CF7" s="1">
+        <v>162.47499999999999</v>
+      </c>
+      <c r="CG7" s="1">
+        <v>149.49600000000001</v>
+      </c>
+      <c r="CH7" s="1">
+        <v>152.90899999999999</v>
+      </c>
+      <c r="CI7" s="1">
+        <v>154.61600000000001</v>
+      </c>
+      <c r="CJ7" s="1">
+        <v>154</v>
+      </c>
+      <c r="CK7" s="1">
+        <v>5.6081300000000001</v>
+      </c>
+      <c r="CL7" s="1">
+        <v>152.50200000000001</v>
+      </c>
+      <c r="CM7" s="1">
+        <v>171.77199999999999</v>
+      </c>
+      <c r="CN7" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO7" s="1">
+        <v>158.56100000000001</v>
+      </c>
+      <c r="CP7" s="1">
+        <v>154.58699999999999</v>
+      </c>
+      <c r="CQ7" s="1">
+        <v>185.92</v>
+      </c>
+      <c r="CR7" s="1">
+        <v>200.01499999999999</v>
+      </c>
+      <c r="CS7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU7" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV7" s="1">
+        <v>0.64151400000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
         <v>25</v>
       </c>
-      <c r="F1" s="1">
+      <c r="C8" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="E8" s="1">
+        <v>170.554</v>
+      </c>
+      <c r="F8" s="1">
+        <v>164.61099999999999</v>
+      </c>
+      <c r="G8" s="1">
+        <v>154.36699999999999</v>
+      </c>
+      <c r="H8" s="1">
+        <v>154.57400000000001</v>
+      </c>
+      <c r="I8" s="1">
+        <v>156.495</v>
+      </c>
+      <c r="J8" s="1">
+        <v>175.51300000000001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>153.60400000000001</v>
+      </c>
+      <c r="L8" s="1">
+        <v>154.846</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="1">
+        <v>168.90700000000001</v>
+      </c>
+      <c r="O8" s="1">
+        <v>160.744</v>
+      </c>
+      <c r="P8" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>158.767</v>
+      </c>
+      <c r="R8" s="1">
+        <v>167.512</v>
+      </c>
+      <c r="S8" s="1">
+        <v>256.685</v>
+      </c>
+      <c r="T8" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="U8" s="1">
+        <v>166.386</v>
+      </c>
+      <c r="V8" s="1">
+        <v>167.84399999999999</v>
+      </c>
+      <c r="W8" s="1">
+        <v>172.46199999999999</v>
+      </c>
+      <c r="X8" s="1">
+        <v>115.315</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>167.64</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>157.37700000000001</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>244.90700000000001</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>154.227</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>157.589</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>154.44399999999999</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>196.73099999999999</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>171.82</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>158.53899999999999</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>171.08600000000001</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>157.154</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>152.97499999999999</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>175.85400000000001</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>179.15100000000001</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>177.18</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>166.36600000000001</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>171.41499999999999</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>179.114</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>190.48400000000001</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>156.07900000000001</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>157.85300000000001</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>183.01400000000001</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>154.82599999999999</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>166.24</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>187.673</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>167.20699999999999</v>
+      </c>
+      <c r="AZ8" s="1">
+        <v>179.68700000000001</v>
+      </c>
+      <c r="BA8" s="1">
+        <v>156.62299999999999</v>
+      </c>
+      <c r="BB8" s="1">
+        <v>177.773</v>
+      </c>
+      <c r="BC8" s="1">
+        <v>159.809</v>
+      </c>
+      <c r="BD8" s="1">
+        <v>166.07300000000001</v>
+      </c>
+      <c r="BE8" s="1">
+        <v>229.92400000000001</v>
+      </c>
+      <c r="BF8" s="1">
+        <v>166.02500000000001</v>
+      </c>
+      <c r="BG8" s="1">
+        <v>155.06299999999999</v>
+      </c>
+      <c r="BH8" s="1">
+        <v>441.61399999999998</v>
+      </c>
+      <c r="BI8" s="1">
+        <v>171.41</v>
+      </c>
+      <c r="BJ8" s="1">
+        <v>190.82300000000001</v>
+      </c>
+      <c r="BK8" s="1">
+        <v>178.49199999999999</v>
+      </c>
+      <c r="BL8" s="1">
+        <v>166.28800000000001</v>
+      </c>
+      <c r="BM8" s="1">
+        <v>175.07</v>
+      </c>
+      <c r="BN8" s="1">
+        <v>166.035</v>
+      </c>
+      <c r="BO8" s="1">
+        <v>793.58500000000004</v>
+      </c>
+      <c r="BP8" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="BQ8" s="1">
+        <v>256.685</v>
+      </c>
+      <c r="BR8" s="1">
+        <v>163.27099999999999</v>
+      </c>
+      <c r="BS8" s="1">
+        <v>152.14599999999999</v>
+      </c>
+      <c r="BT8" s="1">
+        <v>162.97</v>
+      </c>
+      <c r="BU8" s="1">
+        <v>158.922</v>
+      </c>
+      <c r="BV8" s="1">
+        <v>173.03800000000001</v>
+      </c>
+      <c r="BW8" s="1">
+        <v>94.978700000000003</v>
+      </c>
+      <c r="BX8" s="1">
+        <v>169.33699999999999</v>
+      </c>
+      <c r="BY8" s="1">
+        <v>163.916</v>
+      </c>
+      <c r="BZ8" s="1">
+        <v>163.16900000000001</v>
+      </c>
+      <c r="CA8" s="1">
+        <v>154.71700000000001</v>
+      </c>
+      <c r="CB8" s="1">
+        <v>166.029</v>
+      </c>
+      <c r="CC8" s="1">
+        <v>169.09100000000001</v>
+      </c>
+      <c r="CD8" s="1">
+        <v>154.53100000000001</v>
+      </c>
+      <c r="CE8" s="1">
+        <v>153.37</v>
+      </c>
+      <c r="CF8" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="CG8" s="1">
+        <v>151.51599999999999</v>
+      </c>
+      <c r="CH8" s="1">
+        <v>154.31100000000001</v>
+      </c>
+      <c r="CI8" s="1">
+        <v>155.739</v>
+      </c>
+      <c r="CJ8" s="1">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="CK8" s="1">
+        <v>5.7056800000000001</v>
+      </c>
+      <c r="CL8" s="1">
+        <v>153.99199999999999</v>
+      </c>
+      <c r="CM8" s="1">
+        <v>180.70599999999999</v>
+      </c>
+      <c r="CN8" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO8" s="1">
+        <v>161.35900000000001</v>
+      </c>
+      <c r="CP8" s="1">
+        <v>155.79300000000001</v>
+      </c>
+      <c r="CQ8" s="1">
+        <v>191.965</v>
+      </c>
+      <c r="CR8" s="1">
+        <v>213.25200000000001</v>
+      </c>
+      <c r="CS8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU8" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV8" s="1">
+        <v>0.63960300000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
         <v>50</v>
       </c>
-      <c r="G1" s="1">
+      <c r="C9" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="E9" s="1">
+        <v>183.245</v>
+      </c>
+      <c r="F9" s="1">
+        <v>170.44399999999999</v>
+      </c>
+      <c r="G9" s="1">
+        <v>154.64699999999999</v>
+      </c>
+      <c r="H9" s="1">
+        <v>157.386</v>
+      </c>
+      <c r="I9" s="1">
+        <v>158.31200000000001</v>
+      </c>
+      <c r="J9" s="1">
+        <v>190.035</v>
+      </c>
+      <c r="K9" s="1">
+        <v>156.78200000000001</v>
+      </c>
+      <c r="L9" s="1">
+        <v>157.32400000000001</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="1">
+        <v>180.363</v>
+      </c>
+      <c r="O9" s="1">
+        <v>167.75700000000001</v>
+      </c>
+      <c r="P9" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>168.15199999999999</v>
+      </c>
+      <c r="R9" s="1">
+        <v>178.459</v>
+      </c>
+      <c r="S9" s="1">
+        <v>303.346</v>
+      </c>
+      <c r="T9" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="U9" s="1">
+        <v>176.67099999999999</v>
+      </c>
+      <c r="V9" s="1">
+        <v>178.70400000000001</v>
+      </c>
+      <c r="W9" s="1">
+        <v>186.911</v>
+      </c>
+      <c r="X9" s="1">
+        <v>115.47499999999999</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>178.56100000000001</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>158.81399999999999</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>289.03100000000001</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>157.37899999999999</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>158.828</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>157.727</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>219.161</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>185.917</v>
+      </c>
+      <c r="AG9" s="1">
         <v>100</v>
       </c>
+      <c r="AH9" s="1">
+        <v>159.46899999999999</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>202.71700000000001</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>162.74600000000001</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>158.07400000000001</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>194.24600000000001</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>199.31399999999999</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>192.34399999999999</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>181.184</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>184.517</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>195.78100000000001</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>212.648</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>158.08099999999999</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>163.81299999999999</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>185.994</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>157.46600000000001</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>169.12</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>205.86600000000001</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>183.643</v>
+      </c>
+      <c r="AZ9" s="1">
+        <v>199.17099999999999</v>
+      </c>
+      <c r="BA9" s="1">
+        <v>158.05799999999999</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>189.679</v>
+      </c>
+      <c r="BC9" s="1">
+        <v>166.91900000000001</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>179.26900000000001</v>
+      </c>
+      <c r="BE9" s="1">
+        <v>282.14100000000002</v>
+      </c>
+      <c r="BF9" s="1">
+        <v>176.18799999999999</v>
+      </c>
+      <c r="BG9" s="1">
+        <v>157.53</v>
+      </c>
+      <c r="BH9" s="1">
+        <v>528.09699999999998</v>
+      </c>
+      <c r="BI9" s="1">
+        <v>184.035</v>
+      </c>
+      <c r="BJ9" s="1">
+        <v>213.62700000000001</v>
+      </c>
+      <c r="BK9" s="1">
+        <v>199.428</v>
+      </c>
+      <c r="BL9" s="1">
+        <v>176.51499999999999</v>
+      </c>
+      <c r="BM9" s="1">
+        <v>189.458</v>
+      </c>
+      <c r="BN9" s="1">
+        <v>176.20099999999999</v>
+      </c>
+      <c r="BO9" s="1">
+        <v>951.298</v>
+      </c>
+      <c r="BP9" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="BQ9" s="1">
+        <v>303.346</v>
+      </c>
+      <c r="BR9" s="1">
+        <v>171.96</v>
+      </c>
+      <c r="BS9" s="1">
+        <v>156.047</v>
+      </c>
+      <c r="BT9" s="1">
+        <v>171.48099999999999</v>
+      </c>
+      <c r="BU9" s="1">
+        <v>165.52099999999999</v>
+      </c>
+      <c r="BV9" s="1">
+        <v>186.34</v>
+      </c>
+      <c r="BW9" s="1">
+        <v>94.997600000000006</v>
+      </c>
+      <c r="BX9" s="1">
+        <v>181.179</v>
+      </c>
+      <c r="BY9" s="1">
+        <v>173.37700000000001</v>
+      </c>
+      <c r="BZ9" s="1">
+        <v>167.36500000000001</v>
+      </c>
+      <c r="CA9" s="1">
+        <v>157.19800000000001</v>
+      </c>
+      <c r="CB9" s="1">
+        <v>176.19200000000001</v>
+      </c>
+      <c r="CC9" s="1">
+        <v>170.553</v>
+      </c>
+      <c r="CD9" s="1">
+        <v>157.07599999999999</v>
+      </c>
+      <c r="CE9" s="1">
+        <v>156.655</v>
+      </c>
+      <c r="CF9" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="CG9" s="1">
+        <v>155.67400000000001</v>
+      </c>
+      <c r="CH9" s="1">
+        <v>157.13900000000001</v>
+      </c>
+      <c r="CI9" s="1">
+        <v>157.93799999999999</v>
+      </c>
+      <c r="CJ9" s="1">
+        <v>157.6</v>
+      </c>
+      <c r="CK9" s="1">
+        <v>5.9053800000000001</v>
+      </c>
+      <c r="CL9" s="1">
+        <v>156.99</v>
+      </c>
+      <c r="CM9" s="1">
+        <v>209.87899999999999</v>
+      </c>
+      <c r="CN9" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO9" s="1">
+        <v>169.161</v>
+      </c>
+      <c r="CP9" s="1">
+        <v>158.20500000000001</v>
+      </c>
+      <c r="CQ9" s="1">
+        <v>210.584</v>
+      </c>
+      <c r="CR9" s="1">
+        <v>259.79399999999998</v>
+      </c>
+      <c r="CS9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU9" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV9" s="1">
+        <v>0.63583000000000001</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A2" s="1">
-        <v>2502023</v>
-      </c>
-      <c r="B2" s="1">
-        <v>103</v>
-      </c>
-      <c r="C2" s="1">
-        <v>132</v>
-      </c>
-      <c r="D2" s="1">
-        <v>155</v>
-      </c>
-      <c r="E2" s="1">
-        <v>184</v>
-      </c>
-      <c r="F2" s="1">
-        <v>205</v>
-      </c>
-      <c r="G2" s="1">
-        <v>226</v>
+    <row r="10" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>75</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.98666699999999996</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.3333299999999999E-2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>190.24600000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>173.011</v>
+      </c>
+      <c r="G10" s="1">
+        <v>154.69900000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>158.49600000000001</v>
+      </c>
+      <c r="I10" s="1">
+        <v>158.899</v>
+      </c>
+      <c r="J10" s="1">
+        <v>198.10499999999999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>157.85</v>
+      </c>
+      <c r="L10" s="1">
+        <v>158.56100000000001</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N10" s="1">
+        <v>186.584</v>
+      </c>
+      <c r="O10" s="1">
+        <v>171.107</v>
+      </c>
+      <c r="P10" s="1">
+        <v>181.64</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>173.45099999999999</v>
+      </c>
+      <c r="R10" s="1">
+        <v>184.38</v>
+      </c>
+      <c r="S10" s="1">
+        <v>330.64100000000002</v>
+      </c>
+      <c r="T10" s="1">
+        <v>181.64</v>
+      </c>
+      <c r="U10" s="1">
+        <v>182.19499999999999</v>
+      </c>
+      <c r="V10" s="1">
+        <v>184.57400000000001</v>
+      </c>
+      <c r="W10" s="1">
+        <v>195.256</v>
+      </c>
+      <c r="X10" s="1">
+        <v>115.562</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>184.46600000000001</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>159.255</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>314.84199999999998</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>158.684</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>159.22999999999999</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>159.17500000000001</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>231.92</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>194.054</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>159.70699999999999</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>224.08</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>165.57400000000001</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>160.65199999999999</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>204.935</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>211.036</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>200.59899999999999</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>189.84399999999999</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>191.755</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>205.17400000000001</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>225.53100000000001</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>158.846</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>166.816</v>
+      </c>
+      <c r="AU10" s="1">
+        <v>186.99199999999999</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>158.34899999999999</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>170.08</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>215.875</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>193.25700000000001</v>
+      </c>
+      <c r="AZ10" s="1">
+        <v>210.56800000000001</v>
+      </c>
+      <c r="BA10" s="1">
+        <v>158.64699999999999</v>
+      </c>
+      <c r="BB10" s="1">
+        <v>196.06700000000001</v>
+      </c>
+      <c r="BC10" s="1">
+        <v>170.59399999999999</v>
+      </c>
+      <c r="BD10" s="1">
+        <v>186.89099999999999</v>
+      </c>
+      <c r="BE10" s="1">
+        <v>318.01600000000002</v>
+      </c>
+      <c r="BF10" s="1">
+        <v>181.64099999999999</v>
+      </c>
+      <c r="BG10" s="1">
+        <v>158.35300000000001</v>
+      </c>
+      <c r="BH10" s="1">
+        <v>578.68600000000004</v>
+      </c>
+      <c r="BI10" s="1">
+        <v>190.9</v>
+      </c>
+      <c r="BJ10" s="1">
+        <v>226.959</v>
+      </c>
+      <c r="BK10" s="1">
+        <v>211.67099999999999</v>
+      </c>
+      <c r="BL10" s="1">
+        <v>182.00399999999999</v>
+      </c>
+      <c r="BM10" s="1">
+        <v>197.44399999999999</v>
+      </c>
+      <c r="BN10" s="1">
+        <v>181.65600000000001</v>
+      </c>
+      <c r="BO10" s="1">
+        <v>1038.1600000000001</v>
+      </c>
+      <c r="BP10" s="1">
+        <v>181.64</v>
+      </c>
+      <c r="BQ10" s="1">
+        <v>330.64100000000002</v>
+      </c>
+      <c r="BR10" s="1">
+        <v>176.53100000000001</v>
+      </c>
+      <c r="BS10" s="1">
+        <v>157.35900000000001</v>
+      </c>
+      <c r="BT10" s="1">
+        <v>175.977</v>
+      </c>
+      <c r="BU10" s="1">
+        <v>168.91900000000001</v>
+      </c>
+      <c r="BV10" s="1">
+        <v>193.57599999999999</v>
+      </c>
+      <c r="BW10" s="1">
+        <v>94.999600000000001</v>
+      </c>
+      <c r="BX10" s="1">
+        <v>187.642</v>
+      </c>
+      <c r="BY10" s="1">
+        <v>178.47200000000001</v>
+      </c>
+      <c r="BZ10" s="1">
+        <v>169.042</v>
+      </c>
+      <c r="CA10" s="1">
+        <v>158.375</v>
+      </c>
+      <c r="CB10" s="1">
+        <v>181.64599999999999</v>
+      </c>
+      <c r="CC10" s="1">
+        <v>171.03700000000001</v>
+      </c>
+      <c r="CD10" s="1">
+        <v>158.203</v>
+      </c>
+      <c r="CE10" s="1">
+        <v>157.76300000000001</v>
+      </c>
+      <c r="CF10" s="1">
+        <v>181.64</v>
+      </c>
+      <c r="CG10" s="1">
+        <v>157.09700000000001</v>
+      </c>
+      <c r="CH10" s="1">
+        <v>158.089</v>
+      </c>
+      <c r="CI10" s="1">
+        <v>158.65</v>
+      </c>
+      <c r="CJ10" s="1">
+        <v>158.4</v>
+      </c>
+      <c r="CK10" s="1">
+        <v>5.9729099999999997</v>
+      </c>
+      <c r="CL10" s="1">
+        <v>157.99199999999999</v>
+      </c>
+      <c r="CM10" s="1">
+        <v>227.83</v>
+      </c>
+      <c r="CN10" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO10" s="1">
+        <v>173.22300000000001</v>
+      </c>
+      <c r="CP10" s="1">
+        <v>159.00899999999999</v>
+      </c>
+      <c r="CQ10" s="1">
+        <v>221.40700000000001</v>
+      </c>
+      <c r="CR10" s="1">
+        <v>291.38200000000001</v>
+      </c>
+      <c r="CS10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU10" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV10" s="1">
+        <v>0.63458700000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A3" s="1">
-        <v>2502026</v>
-      </c>
-      <c r="B3" s="1">
-        <v>107</v>
-      </c>
-      <c r="C3" s="1">
-        <v>133</v>
-      </c>
-      <c r="D3" s="1">
-        <v>154</v>
-      </c>
-      <c r="E3" s="1">
-        <v>181</v>
-      </c>
-      <c r="F3" s="1">
-        <v>201</v>
-      </c>
-      <c r="G3" s="1">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A4" s="1">
-        <v>2502028</v>
-      </c>
-      <c r="B4" s="1">
-        <v>111</v>
-      </c>
-      <c r="C4" s="1">
-        <v>149</v>
-      </c>
-      <c r="D4" s="1">
-        <v>179</v>
-      </c>
-      <c r="E4" s="1">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1">
-        <v>247</v>
-      </c>
-      <c r="G4" s="1">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A5" s="1">
-        <v>2502069</v>
-      </c>
-      <c r="B5" s="1">
-        <v>92</v>
-      </c>
-      <c r="C5" s="1">
-        <v>117</v>
-      </c>
-      <c r="D5" s="1">
-        <v>137</v>
-      </c>
-      <c r="E5" s="1">
-        <v>162</v>
-      </c>
-      <c r="F5" s="1">
-        <v>180</v>
-      </c>
-      <c r="G5" s="1">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A6" s="1">
-        <v>2802008</v>
-      </c>
-      <c r="B6" s="1">
-        <v>102</v>
-      </c>
-      <c r="C6" s="1">
-        <v>136</v>
-      </c>
-      <c r="D6" s="1">
-        <v>164</v>
-      </c>
-      <c r="E6" s="1">
-        <v>199</v>
-      </c>
-      <c r="F6" s="1">
-        <v>225</v>
-      </c>
-      <c r="G6" s="1">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A7" s="1">
-        <v>2802023</v>
-      </c>
-      <c r="B7" s="1">
-        <v>102</v>
-      </c>
-      <c r="C7" s="1">
-        <v>136</v>
-      </c>
-      <c r="D7" s="1">
-        <v>165</v>
-      </c>
-      <c r="E7" s="1">
-        <v>201</v>
-      </c>
-      <c r="F7" s="1">
-        <v>227</v>
-      </c>
-      <c r="G7" s="1">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A8" s="1">
-        <v>2802044</v>
-      </c>
-      <c r="B8" s="1">
-        <v>92</v>
-      </c>
-      <c r="C8" s="1">
-        <v>114</v>
-      </c>
-      <c r="D8" s="1">
-        <v>132</v>
-      </c>
-      <c r="E8" s="1">
-        <v>155</v>
-      </c>
-      <c r="F8" s="1">
-        <v>172</v>
-      </c>
-      <c r="G8" s="1">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A9" s="1">
-        <v>2802060</v>
-      </c>
-      <c r="B9" s="1">
-        <v>91</v>
-      </c>
-      <c r="C9" s="1">
-        <v>111</v>
-      </c>
-      <c r="D9" s="1">
-        <v>127</v>
-      </c>
-      <c r="E9" s="1">
-        <v>148</v>
-      </c>
-      <c r="F9" s="1">
-        <v>163</v>
-      </c>
-      <c r="G9" s="1">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
-      <c r="A10" s="1">
-        <v>2802508</v>
-      </c>
-      <c r="B10" s="1">
-        <v>100</v>
-      </c>
-      <c r="C10" s="1">
-        <v>121</v>
-      </c>
-      <c r="D10" s="1">
-        <v>138</v>
-      </c>
-      <c r="E10" s="1">
-        <v>159</v>
-      </c>
-      <c r="F10" s="1">
-        <v>175</v>
-      </c>
-      <c r="G10" s="1">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:100" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
-        <v>2802509</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>100</v>
       </c>
       <c r="C11" s="1">
-        <v>117</v>
+        <v>0.99</v>
       </c>
       <c r="D11" s="1">
-        <v>130</v>
+        <v>0.01</v>
       </c>
       <c r="E11" s="1">
-        <v>148</v>
+        <v>195.06</v>
       </c>
       <c r="F11" s="1">
-        <v>161</v>
+        <v>174.53800000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>174</v>
+        <v>154.71700000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <v>159.114</v>
+      </c>
+      <c r="I11" s="1">
+        <v>159.18700000000001</v>
+      </c>
+      <c r="J11" s="1">
+        <v>203.67599999999999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>158.386</v>
+      </c>
+      <c r="L11" s="1">
+        <v>159.386</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N11" s="1">
+        <v>190.821</v>
+      </c>
+      <c r="O11" s="1">
+        <v>173.20599999999999</v>
+      </c>
+      <c r="P11" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>177.143</v>
+      </c>
+      <c r="R11" s="1">
+        <v>188.404</v>
+      </c>
+      <c r="S11" s="1">
+        <v>350.00700000000001</v>
+      </c>
+      <c r="T11" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="U11" s="1">
+        <v>185.934</v>
+      </c>
+      <c r="V11" s="1">
+        <v>188.56100000000001</v>
+      </c>
+      <c r="W11" s="1">
+        <v>201.148</v>
+      </c>
+      <c r="X11" s="1">
+        <v>115.622</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>188.47800000000001</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>159.464</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>333.15600000000001</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>159.43199999999999</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>159.42699999999999</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>160.041</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>240.839</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>199.798</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>159.80699999999999</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>240.62899999999999</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>167.423</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>162.339</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>212.501</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>219.33199999999999</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>206.22200000000001</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>195.98699999999999</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>196.73400000000001</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>211.71</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>234.648</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>159.268</v>
+      </c>
+      <c r="AT11" s="1">
+        <v>168.773</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>187.5</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>158.79</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>170.56</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>222.733</v>
+      </c>
+      <c r="AY11" s="1">
+        <v>200.07900000000001</v>
+      </c>
+      <c r="AZ11" s="1">
+        <v>218.655</v>
+      </c>
+      <c r="BA11" s="1">
+        <v>158.99199999999999</v>
+      </c>
+      <c r="BB11" s="1">
+        <v>200.38800000000001</v>
+      </c>
+      <c r="BC11" s="1">
+        <v>173.02799999999999</v>
+      </c>
+      <c r="BD11" s="1">
+        <v>192.27199999999999</v>
+      </c>
+      <c r="BE11" s="1">
+        <v>346.2</v>
+      </c>
+      <c r="BF11" s="1">
+        <v>185.32900000000001</v>
+      </c>
+      <c r="BG11" s="1">
+        <v>158.76499999999999</v>
+      </c>
+      <c r="BH11" s="1">
+        <v>614.58000000000004</v>
+      </c>
+      <c r="BI11" s="1">
+        <v>195.57499999999999</v>
+      </c>
+      <c r="BJ11" s="1">
+        <v>236.429</v>
+      </c>
+      <c r="BK11" s="1">
+        <v>220.357</v>
+      </c>
+      <c r="BL11" s="1">
+        <v>185.71899999999999</v>
+      </c>
+      <c r="BM11" s="1">
+        <v>202.95099999999999</v>
+      </c>
+      <c r="BN11" s="1">
+        <v>185.346</v>
+      </c>
+      <c r="BO11" s="1">
+        <v>1097.8</v>
+      </c>
+      <c r="BP11" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="BQ11" s="1">
+        <v>350.00700000000001</v>
+      </c>
+      <c r="BR11" s="1">
+        <v>179.58600000000001</v>
+      </c>
+      <c r="BS11" s="1">
+        <v>158.017</v>
+      </c>
+      <c r="BT11" s="1">
+        <v>178.99100000000001</v>
+      </c>
+      <c r="BU11" s="1">
+        <v>171.16399999999999</v>
+      </c>
+      <c r="BV11" s="1">
+        <v>198.50700000000001</v>
+      </c>
+      <c r="BW11" s="1">
+        <v>95.000100000000003</v>
+      </c>
+      <c r="BX11" s="1">
+        <v>192.05500000000001</v>
+      </c>
+      <c r="BY11" s="1">
+        <v>181.923</v>
+      </c>
+      <c r="BZ11" s="1">
+        <v>169.98</v>
+      </c>
+      <c r="CA11" s="1">
+        <v>159.12700000000001</v>
+      </c>
+      <c r="CB11" s="1">
+        <v>185.334</v>
+      </c>
+      <c r="CC11" s="1">
+        <v>171.27799999999999</v>
+      </c>
+      <c r="CD11" s="1">
+        <v>158.875</v>
+      </c>
+      <c r="CE11" s="1">
+        <v>158.32</v>
+      </c>
+      <c r="CF11" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="CG11" s="1">
+        <v>157.815</v>
+      </c>
+      <c r="CH11" s="1">
+        <v>158.565</v>
+      </c>
+      <c r="CI11" s="1">
+        <v>159</v>
+      </c>
+      <c r="CJ11" s="1">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="CK11" s="1">
+        <v>6.00678</v>
+      </c>
+      <c r="CL11" s="1">
+        <v>158.494</v>
+      </c>
+      <c r="CM11" s="1">
+        <v>240.91900000000001</v>
+      </c>
+      <c r="CN11" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO11" s="1">
+        <v>175.923</v>
+      </c>
+      <c r="CP11" s="1">
+        <v>159.411</v>
+      </c>
+      <c r="CQ11" s="1">
+        <v>229.06700000000001</v>
+      </c>
+      <c r="CR11" s="1">
+        <v>316.03300000000002</v>
+      </c>
+      <c r="CS11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU11" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV11" s="1">
+        <v>0.63396799999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:100" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
-        <v>2803504</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="C12" s="1">
-        <v>112</v>
+        <v>0.995</v>
       </c>
       <c r="D12" s="1">
-        <v>131</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="E12" s="1">
-        <v>155</v>
+        <v>206.22399999999999</v>
       </c>
       <c r="F12" s="1">
-        <v>173</v>
+        <v>177.422</v>
       </c>
       <c r="G12" s="1">
-        <v>190</v>
+        <v>154.73500000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>160.18700000000001</v>
+      </c>
+      <c r="I12" s="1">
+        <v>159.608</v>
+      </c>
+      <c r="J12" s="1">
+        <v>216.65199999999999</v>
+      </c>
+      <c r="K12" s="1">
+        <v>159.19200000000001</v>
+      </c>
+      <c r="L12" s="1">
+        <v>161.268</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" s="1">
+        <v>200.52099999999999</v>
+      </c>
+      <c r="O12" s="1">
+        <v>177.47499999999999</v>
+      </c>
+      <c r="P12" s="1">
+        <v>193.69399999999999</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>185.852</v>
+      </c>
+      <c r="R12" s="1">
+        <v>197.58799999999999</v>
+      </c>
+      <c r="S12" s="1">
+        <v>396.66699999999997</v>
+      </c>
+      <c r="T12" s="1">
+        <v>193.69399999999999</v>
+      </c>
+      <c r="U12" s="1">
+        <v>194.41900000000001</v>
+      </c>
+      <c r="V12" s="1">
+        <v>197.655</v>
+      </c>
+      <c r="W12" s="1">
+        <v>215.28200000000001</v>
+      </c>
+      <c r="X12" s="1">
+        <v>115.758</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>197.63200000000001</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>159.75800000000001</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>377.28</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>160.77600000000001</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>159.72</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>161.70500000000001</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>261.94499999999999</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>213.57400000000001</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>159.93</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>285.65300000000002</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>171.44399999999999</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>166.005</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>230.69</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>239.27600000000001</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>219.084</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>210.786</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>208.28899999999999</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>227.09200000000001</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>256.56799999999998</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>160.00700000000001</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>173.006</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>188.327</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>159.453</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>171.28</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>238.529</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>216.51400000000001</v>
+      </c>
+      <c r="AZ12" s="1">
+        <v>238.13900000000001</v>
+      </c>
+      <c r="BA12" s="1">
+        <v>159.64400000000001</v>
+      </c>
+      <c r="BB12" s="1">
+        <v>210.18799999999999</v>
+      </c>
+      <c r="BC12" s="1">
+        <v>178.39699999999999</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>205.18</v>
+      </c>
+      <c r="BE12" s="1">
+        <v>424.78500000000003</v>
+      </c>
+      <c r="BF12" s="1">
+        <v>193.696</v>
+      </c>
+      <c r="BG12" s="1">
+        <v>159.38200000000001</v>
+      </c>
+      <c r="BH12" s="1">
+        <v>701.06299999999999</v>
+      </c>
+      <c r="BI12" s="1">
+        <v>206.27199999999999</v>
+      </c>
+      <c r="BJ12" s="1">
+        <v>259.315</v>
+      </c>
+      <c r="BK12" s="1">
+        <v>241.28399999999999</v>
+      </c>
+      <c r="BL12" s="1">
+        <v>194.14699999999999</v>
+      </c>
+      <c r="BM12" s="1">
+        <v>215.76300000000001</v>
+      </c>
+      <c r="BN12" s="1">
+        <v>193.715</v>
+      </c>
+      <c r="BO12" s="1">
+        <v>1235.74</v>
+      </c>
+      <c r="BP12" s="1">
+        <v>193.69399999999999</v>
+      </c>
+      <c r="BQ12" s="1">
+        <v>396.66699999999997</v>
+      </c>
+      <c r="BR12" s="1">
+        <v>186.40899999999999</v>
+      </c>
+      <c r="BS12" s="1">
+        <v>159.00700000000001</v>
+      </c>
+      <c r="BT12" s="1">
+        <v>185.75399999999999</v>
+      </c>
+      <c r="BU12" s="1">
+        <v>176.10900000000001</v>
+      </c>
+      <c r="BV12" s="1">
+        <v>209.78800000000001</v>
+      </c>
+      <c r="BW12" s="1">
+        <v>95.000399999999999</v>
+      </c>
+      <c r="BX12" s="1">
+        <v>202.19800000000001</v>
+      </c>
+      <c r="BY12" s="1">
+        <v>189.77</v>
+      </c>
+      <c r="BZ12" s="1">
+        <v>171.61699999999999</v>
+      </c>
+      <c r="CA12" s="1">
+        <v>160.72800000000001</v>
+      </c>
+      <c r="CB12" s="1">
+        <v>193.70099999999999</v>
+      </c>
+      <c r="CC12" s="1">
+        <v>171.64</v>
+      </c>
+      <c r="CD12" s="1">
+        <v>160.148</v>
+      </c>
+      <c r="CE12" s="1">
+        <v>159.15799999999999</v>
+      </c>
+      <c r="CF12" s="1">
+        <v>193.69399999999999</v>
+      </c>
+      <c r="CG12" s="1">
+        <v>158.90199999999999</v>
+      </c>
+      <c r="CH12" s="1">
+        <v>159.28200000000001</v>
+      </c>
+      <c r="CI12" s="1">
+        <v>159.51499999999999</v>
+      </c>
+      <c r="CJ12" s="1">
+        <v>159.4</v>
+      </c>
+      <c r="CK12" s="1">
+        <v>6.0576800000000004</v>
+      </c>
+      <c r="CL12" s="1">
+        <v>159.24700000000001</v>
+      </c>
+      <c r="CM12" s="1">
+        <v>273.52</v>
+      </c>
+      <c r="CN12" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO12" s="1">
+        <v>181.91399999999999</v>
+      </c>
+      <c r="CP12" s="1">
+        <v>160.01499999999999</v>
+      </c>
+      <c r="CQ12" s="1">
+        <v>247.482</v>
+      </c>
+      <c r="CR12" s="1">
+        <v>384.17099999999999</v>
+      </c>
+      <c r="CS12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU12" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV12" s="1">
+        <v>0.63304199999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:100" x14ac:dyDescent="0.6">
       <c r="A13" s="1">
-        <v>2804031</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>98</v>
+        <v>250</v>
       </c>
       <c r="C13" s="1">
-        <v>120</v>
+        <v>0.996</v>
       </c>
       <c r="D13" s="1">
-        <v>138</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E13" s="1">
-        <v>161</v>
+        <v>209.70500000000001</v>
       </c>
       <c r="F13" s="1">
-        <v>178</v>
+        <v>178.15600000000001</v>
       </c>
       <c r="G13" s="1">
-        <v>195</v>
+        <v>154.73699999999999</v>
+      </c>
+      <c r="H13" s="1">
+        <v>160.43700000000001</v>
+      </c>
+      <c r="I13" s="1">
+        <v>159.69</v>
+      </c>
+      <c r="J13" s="1">
+        <v>220.71199999999999</v>
+      </c>
+      <c r="K13" s="1">
+        <v>159.35300000000001</v>
+      </c>
+      <c r="L13" s="1">
+        <v>161.85400000000001</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N13" s="1">
+        <v>203.50899999999999</v>
+      </c>
+      <c r="O13" s="1">
+        <v>178.64500000000001</v>
+      </c>
+      <c r="P13" s="1">
+        <v>196.251</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>188.607</v>
+      </c>
+      <c r="R13" s="1">
+        <v>200.41</v>
+      </c>
+      <c r="S13" s="1">
+        <v>411.68900000000002</v>
+      </c>
+      <c r="T13" s="1">
+        <v>196.25</v>
+      </c>
+      <c r="U13" s="1">
+        <v>197.01400000000001</v>
+      </c>
+      <c r="V13" s="1">
+        <v>200.44800000000001</v>
+      </c>
+      <c r="W13" s="1">
+        <v>219.81899999999999</v>
+      </c>
+      <c r="X13" s="1">
+        <v>115.8</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>200.44499999999999</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>159.81200000000001</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>391.48500000000001</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>161.102</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>159.77699999999999</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>162.13800000000001</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>268.63900000000001</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>217.99600000000001</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>159.94900000000001</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>301.80799999999999</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>172.62700000000001</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>167.083</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>236.53800000000001</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>245.68799999999999</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>223.041</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>215.55</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>211.893</v>
+      </c>
+      <c r="AQ13" s="1">
+        <v>231.95</v>
+      </c>
+      <c r="AR13" s="1">
+        <v>263.61500000000001</v>
+      </c>
+      <c r="AS13" s="1">
+        <v>160.18299999999999</v>
+      </c>
+      <c r="AT13" s="1">
+        <v>174.244</v>
+      </c>
+      <c r="AU13" s="1">
+        <v>188.52099999999999</v>
+      </c>
+      <c r="AV13" s="1">
+        <v>159.58600000000001</v>
+      </c>
+      <c r="AW13" s="1">
+        <v>171.42400000000001</v>
+      </c>
+      <c r="AX13" s="1">
+        <v>243.41800000000001</v>
+      </c>
+      <c r="AY13" s="1">
+        <v>221.80600000000001</v>
+      </c>
+      <c r="AZ13" s="1">
+        <v>244.41200000000001</v>
+      </c>
+      <c r="BA13" s="1">
+        <v>159.81399999999999</v>
+      </c>
+      <c r="BB13" s="1">
+        <v>213.18299999999999</v>
+      </c>
+      <c r="BC13" s="1">
+        <v>179.99799999999999</v>
+      </c>
+      <c r="BD13" s="1">
+        <v>209.32400000000001</v>
+      </c>
+      <c r="BE13" s="1">
+        <v>453.69799999999998</v>
+      </c>
+      <c r="BF13" s="1">
+        <v>196.25299999999999</v>
+      </c>
+      <c r="BG13" s="1">
+        <v>159.506</v>
+      </c>
+      <c r="BH13" s="1">
+        <v>728.904</v>
+      </c>
+      <c r="BI13" s="1">
+        <v>209.565</v>
+      </c>
+      <c r="BJ13" s="1">
+        <v>266.70699999999999</v>
+      </c>
+      <c r="BK13" s="1">
+        <v>248.02099999999999</v>
+      </c>
+      <c r="BL13" s="1">
+        <v>196.72300000000001</v>
+      </c>
+      <c r="BM13" s="1">
+        <v>219.767</v>
+      </c>
+      <c r="BN13" s="1">
+        <v>196.27199999999999</v>
+      </c>
+      <c r="BO13" s="1">
+        <v>1278.6199999999999</v>
+      </c>
+      <c r="BP13" s="1">
+        <v>196.251</v>
+      </c>
+      <c r="BQ13" s="1">
+        <v>411.68900000000002</v>
+      </c>
+      <c r="BR13" s="1">
+        <v>188.464</v>
+      </c>
+      <c r="BS13" s="1">
+        <v>159.20500000000001</v>
+      </c>
+      <c r="BT13" s="1">
+        <v>187.80199999999999</v>
+      </c>
+      <c r="BU13" s="1">
+        <v>177.58099999999999</v>
+      </c>
+      <c r="BV13" s="1">
+        <v>213.26</v>
+      </c>
+      <c r="BW13" s="1">
+        <v>95.000399999999999</v>
+      </c>
+      <c r="BX13" s="1">
+        <v>205.334</v>
+      </c>
+      <c r="BY13" s="1">
+        <v>192.17099999999999</v>
+      </c>
+      <c r="BZ13" s="1">
+        <v>172.001</v>
+      </c>
+      <c r="CA13" s="1">
+        <v>161.19399999999999</v>
+      </c>
+      <c r="CB13" s="1">
+        <v>196.25800000000001</v>
+      </c>
+      <c r="CC13" s="1">
+        <v>171.71199999999999</v>
+      </c>
+      <c r="CD13" s="1">
+        <v>160.47200000000001</v>
+      </c>
+      <c r="CE13" s="1">
+        <v>159.32599999999999</v>
+      </c>
+      <c r="CF13" s="1">
+        <v>196.251</v>
+      </c>
+      <c r="CG13" s="1">
+        <v>159.12100000000001</v>
+      </c>
+      <c r="CH13" s="1">
+        <v>159.42500000000001</v>
+      </c>
+      <c r="CI13" s="1">
+        <v>159.61500000000001</v>
+      </c>
+      <c r="CJ13" s="1">
+        <v>159.52000000000001</v>
+      </c>
+      <c r="CK13" s="1">
+        <v>6.0678700000000001</v>
+      </c>
+      <c r="CL13" s="1">
+        <v>159.398</v>
+      </c>
+      <c r="CM13" s="1">
+        <v>284.30599999999998</v>
+      </c>
+      <c r="CN13" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO13" s="1">
+        <v>183.709</v>
+      </c>
+      <c r="CP13" s="1">
+        <v>160.13499999999999</v>
+      </c>
+      <c r="CQ13" s="1">
+        <v>253.40199999999999</v>
+      </c>
+      <c r="CR13" s="1">
+        <v>409.05700000000002</v>
+      </c>
+      <c r="CS13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU13" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV13" s="1">
+        <v>0.63285800000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:100" x14ac:dyDescent="0.6">
       <c r="A14" s="1">
-        <v>2804035</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>96</v>
+        <v>500</v>
       </c>
       <c r="C14" s="1">
-        <v>119</v>
+        <v>0.998</v>
       </c>
       <c r="D14" s="1">
-        <v>138</v>
+        <v>2E-3</v>
       </c>
       <c r="E14" s="1">
-        <v>161</v>
+        <v>220.22499999999999</v>
       </c>
       <c r="F14" s="1">
-        <v>178</v>
+        <v>179.976</v>
       </c>
       <c r="G14" s="1">
-        <v>196</v>
+        <v>154.74</v>
+      </c>
+      <c r="H14" s="1">
+        <v>161.01300000000001</v>
+      </c>
+      <c r="I14" s="1">
+        <v>159.851</v>
+      </c>
+      <c r="J14" s="1">
+        <v>233.02</v>
+      </c>
+      <c r="K14" s="1">
+        <v>159.67699999999999</v>
+      </c>
+      <c r="L14" s="1">
+        <v>163.648</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1">
+        <v>212.43899999999999</v>
+      </c>
+      <c r="O14" s="1">
+        <v>181.75899999999999</v>
+      </c>
+      <c r="P14" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>197.042</v>
+      </c>
+      <c r="R14" s="1">
+        <v>208.82300000000001</v>
+      </c>
+      <c r="S14" s="1">
+        <v>458.34899999999999</v>
+      </c>
+      <c r="T14" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="U14" s="1">
+        <v>204.714</v>
+      </c>
+      <c r="V14" s="1">
+        <v>208.77</v>
+      </c>
+      <c r="W14" s="1">
+        <v>233.892</v>
+      </c>
+      <c r="X14" s="1">
+        <v>115.925</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>208.82599999999999</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>159.91499999999999</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>435.60899999999998</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>161.875</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>159.89099999999999</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>163.23599999999999</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>289.17</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>231.709</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>159.982</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>357.63799999999998</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>176.017</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>170.17500000000001</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>254.68700000000001</v>
+      </c>
+      <c r="AM14" s="1">
+        <v>265.589</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>234.83799999999999</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>230.34700000000001</v>
+      </c>
+      <c r="AP14" s="1">
+        <v>222.78899999999999</v>
+      </c>
+      <c r="AQ14" s="1">
+        <v>246.79599999999999</v>
+      </c>
+      <c r="AR14" s="1">
+        <v>285.48700000000002</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>160.601</v>
+      </c>
+      <c r="AT14" s="1">
+        <v>177.77199999999999</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>189.01</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>159.852</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>171.71199999999999</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>258.06799999999998</v>
+      </c>
+      <c r="AY14" s="1">
+        <v>238.24100000000001</v>
+      </c>
+      <c r="AZ14" s="1">
+        <v>263.89600000000002</v>
+      </c>
+      <c r="BA14" s="1">
+        <v>160.25299999999999</v>
+      </c>
+      <c r="BB14" s="1">
+        <v>222.065</v>
+      </c>
+      <c r="BC14" s="1">
+        <v>184.64</v>
+      </c>
+      <c r="BD14" s="1">
+        <v>222.17599999999999</v>
+      </c>
+      <c r="BE14" s="1">
+        <v>556.66</v>
+      </c>
+      <c r="BF14" s="1">
+        <v>203.83500000000001</v>
+      </c>
+      <c r="BG14" s="1">
+        <v>159.75299999999999</v>
+      </c>
+      <c r="BH14" s="1">
+        <v>815.38699999999994</v>
+      </c>
+      <c r="BI14" s="1">
+        <v>219.39099999999999</v>
+      </c>
+      <c r="BJ14" s="1">
+        <v>289.76400000000001</v>
+      </c>
+      <c r="BK14" s="1">
+        <v>268.94799999999998</v>
+      </c>
+      <c r="BL14" s="1">
+        <v>204.36600000000001</v>
+      </c>
+      <c r="BM14" s="1">
+        <v>231.886</v>
+      </c>
+      <c r="BN14" s="1">
+        <v>203.857</v>
+      </c>
+      <c r="BO14" s="1">
+        <v>1407.83</v>
+      </c>
+      <c r="BP14" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="BQ14" s="1">
+        <v>458.34899999999999</v>
+      </c>
+      <c r="BR14" s="1">
+        <v>194.47900000000001</v>
+      </c>
+      <c r="BS14" s="1">
+        <v>159.602</v>
+      </c>
+      <c r="BT14" s="1">
+        <v>193.82599999999999</v>
+      </c>
+      <c r="BU14" s="1">
+        <v>181.846</v>
+      </c>
+      <c r="BV14" s="1">
+        <v>223.62100000000001</v>
+      </c>
+      <c r="BW14" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="BX14" s="1">
+        <v>214.733</v>
+      </c>
+      <c r="BY14" s="1">
+        <v>199.30500000000001</v>
+      </c>
+      <c r="BZ14" s="1">
+        <v>172.88499999999999</v>
+      </c>
+      <c r="CA14" s="1">
+        <v>162.523</v>
+      </c>
+      <c r="CB14" s="1">
+        <v>203.84</v>
+      </c>
+      <c r="CC14" s="1">
+        <v>171.85599999999999</v>
+      </c>
+      <c r="CD14" s="1">
+        <v>161.27699999999999</v>
+      </c>
+      <c r="CE14" s="1">
+        <v>159.66300000000001</v>
+      </c>
+      <c r="CF14" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="CG14" s="1">
+        <v>159.56</v>
+      </c>
+      <c r="CH14" s="1">
+        <v>159.71199999999999</v>
+      </c>
+      <c r="CI14" s="1">
+        <v>159.81299999999999</v>
+      </c>
+      <c r="CJ14" s="1">
+        <v>159.76</v>
+      </c>
+      <c r="CK14" s="1">
+        <v>6.0882500000000004</v>
+      </c>
+      <c r="CL14" s="1">
+        <v>159.69900000000001</v>
+      </c>
+      <c r="CM14" s="1">
+        <v>318.60000000000002</v>
+      </c>
+      <c r="CN14" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO14" s="1">
+        <v>188.93600000000001</v>
+      </c>
+      <c r="CP14" s="1">
+        <v>160.376</v>
+      </c>
+      <c r="CQ14" s="1">
+        <v>271.77600000000001</v>
+      </c>
+      <c r="CR14" s="1">
+        <v>497.04</v>
+      </c>
+      <c r="CS14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU14" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV14" s="1">
+        <v>0.63248899999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>750</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.99866699999999997</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1.33333E-3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>226.19900000000001</v>
+      </c>
+      <c r="F15" s="1">
+        <v>180.78100000000001</v>
+      </c>
+      <c r="G15" s="1">
+        <v>154.74</v>
+      </c>
+      <c r="H15" s="1">
+        <v>161.244</v>
+      </c>
+      <c r="I15" s="1">
+        <v>159.90199999999999</v>
+      </c>
+      <c r="J15" s="1">
+        <v>240.03</v>
+      </c>
+      <c r="K15" s="1">
+        <v>159.78399999999999</v>
+      </c>
+      <c r="L15" s="1">
+        <v>164.68700000000001</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N15" s="1">
+        <v>217.44399999999999</v>
+      </c>
+      <c r="O15" s="1">
+        <v>183.268</v>
+      </c>
+      <c r="P15" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>201.90100000000001</v>
+      </c>
+      <c r="R15" s="1">
+        <v>213.524</v>
+      </c>
+      <c r="S15" s="1">
+        <v>485.64400000000001</v>
+      </c>
+      <c r="T15" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="U15" s="1">
+        <v>208.995</v>
+      </c>
+      <c r="V15" s="1">
+        <v>213.417</v>
+      </c>
+      <c r="W15" s="1">
+        <v>242.113</v>
+      </c>
+      <c r="X15" s="1">
+        <v>115.994</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>213.50800000000001</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>159.947</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>461.42</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>162.19800000000001</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>159.928</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>163.738</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>301.017</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>239.721</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>159.99</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>394.56099999999998</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>177.83</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>171.828</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>265.29700000000003</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>277.22399999999999</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>241.429</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>239.00299999999999</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>228.98</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>255.33099999999999</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>298.274</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>160.77799999999999</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>179.642</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>189.25</v>
+      </c>
+      <c r="AV15" s="1">
+        <v>159.94</v>
+      </c>
+      <c r="AW15" s="1">
+        <v>171.80799999999999</v>
+      </c>
+      <c r="AX15" s="1">
+        <v>266.298</v>
+      </c>
+      <c r="AY15" s="1">
+        <v>247.85599999999999</v>
+      </c>
+      <c r="AZ15" s="1">
+        <v>275.29300000000001</v>
+      </c>
+      <c r="BA15" s="1">
+        <v>160.46100000000001</v>
+      </c>
+      <c r="BB15" s="1">
+        <v>226.999</v>
+      </c>
+      <c r="BC15" s="1">
+        <v>187.15199999999999</v>
+      </c>
+      <c r="BD15" s="1">
+        <v>229.685</v>
+      </c>
+      <c r="BE15" s="1">
+        <v>627.39800000000002</v>
+      </c>
+      <c r="BF15" s="1">
+        <v>208.047</v>
+      </c>
+      <c r="BG15" s="1">
+        <v>159.83500000000001</v>
+      </c>
+      <c r="BH15" s="1">
+        <v>865.976</v>
+      </c>
+      <c r="BI15" s="1">
+        <v>224.887</v>
+      </c>
+      <c r="BJ15" s="1">
+        <v>303.32</v>
+      </c>
+      <c r="BK15" s="1">
+        <v>281.19</v>
+      </c>
+      <c r="BL15" s="1">
+        <v>208.614</v>
+      </c>
+      <c r="BM15" s="1">
+        <v>238.779</v>
+      </c>
+      <c r="BN15" s="1">
+        <v>208.071</v>
+      </c>
+      <c r="BO15" s="1">
+        <v>1480.91</v>
+      </c>
+      <c r="BP15" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="BQ15" s="1">
+        <v>485.64400000000001</v>
+      </c>
+      <c r="BR15" s="1">
+        <v>197.76900000000001</v>
+      </c>
+      <c r="BS15" s="1">
+        <v>159.73500000000001</v>
+      </c>
+      <c r="BT15" s="1">
+        <v>197.143</v>
+      </c>
+      <c r="BU15" s="1">
+        <v>184.154</v>
+      </c>
+      <c r="BV15" s="1">
+        <v>229.41499999999999</v>
+      </c>
+      <c r="BW15" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="BX15" s="1">
+        <v>220.02099999999999</v>
+      </c>
+      <c r="BY15" s="1">
+        <v>203.274</v>
+      </c>
+      <c r="BZ15" s="1">
+        <v>173.24100000000001</v>
+      </c>
+      <c r="CA15" s="1">
+        <v>163.23400000000001</v>
+      </c>
+      <c r="CB15" s="1">
+        <v>208.05199999999999</v>
+      </c>
+      <c r="CC15" s="1">
+        <v>171.904</v>
+      </c>
+      <c r="CD15" s="1">
+        <v>161.63300000000001</v>
+      </c>
+      <c r="CE15" s="1">
+        <v>159.77500000000001</v>
+      </c>
+      <c r="CF15" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="CG15" s="1">
+        <v>159.70599999999999</v>
+      </c>
+      <c r="CH15" s="1">
+        <v>159.80799999999999</v>
+      </c>
+      <c r="CI15" s="1">
+        <v>159.87700000000001</v>
+      </c>
+      <c r="CJ15" s="1">
+        <v>159.84</v>
+      </c>
+      <c r="CK15" s="1">
+        <v>6.0950499999999996</v>
+      </c>
+      <c r="CL15" s="1">
+        <v>159.79900000000001</v>
+      </c>
+      <c r="CM15" s="1">
+        <v>339.16199999999998</v>
+      </c>
+      <c r="CN15" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO15" s="1">
+        <v>191.78100000000001</v>
+      </c>
+      <c r="CP15" s="1">
+        <v>160.45699999999999</v>
+      </c>
+      <c r="CQ15" s="1">
+        <v>282.51799999999997</v>
+      </c>
+      <c r="CR15" s="1">
+        <v>556.99699999999996</v>
+      </c>
+      <c r="CS15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU15" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV15" s="1">
+        <v>0.63236599999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:100" x14ac:dyDescent="0.6">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.999</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>230.36799999999999</v>
+      </c>
+      <c r="F16" s="1">
+        <v>181.262</v>
+      </c>
+      <c r="G16" s="1">
+        <v>154.74100000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>161.37299999999999</v>
+      </c>
+      <c r="I16" s="1">
+        <v>159.928</v>
+      </c>
+      <c r="J16" s="1">
+        <v>244.93</v>
+      </c>
+      <c r="K16" s="1">
+        <v>159.83799999999999</v>
+      </c>
+      <c r="L16" s="1">
+        <v>165.422</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N16" s="1">
+        <v>220.90700000000001</v>
+      </c>
+      <c r="O16" s="1">
+        <v>184.22</v>
+      </c>
+      <c r="P16" s="1">
+        <v>210.94399999999999</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>205.32</v>
+      </c>
+      <c r="R16" s="1">
+        <v>216.773</v>
+      </c>
+      <c r="S16" s="1">
+        <v>505.01</v>
+      </c>
+      <c r="T16" s="1">
+        <v>210.94300000000001</v>
+      </c>
+      <c r="U16" s="1">
+        <v>211.94300000000001</v>
+      </c>
+      <c r="V16" s="1">
+        <v>216.62799999999999</v>
+      </c>
+      <c r="W16" s="1">
+        <v>247.94399999999999</v>
+      </c>
+      <c r="X16" s="1">
+        <v>116.042</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>216.74299999999999</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>159.96199999999999</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>479.73399999999998</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>162.38300000000001</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>159.946</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>164.04499999999999</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>309.358</v>
+      </c>
+      <c r="AF16" s="1">
+        <v>245.40199999999999</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>100</v>
+      </c>
+      <c r="AH16" s="1">
+        <v>159.99299999999999</v>
+      </c>
+      <c r="AI16" s="1">
+        <v>422.81599999999997</v>
+      </c>
+      <c r="AJ16" s="1">
+        <v>179.04900000000001</v>
+      </c>
+      <c r="AK16" s="1">
+        <v>172.94</v>
+      </c>
+      <c r="AL16" s="1">
+        <v>272.82299999999998</v>
+      </c>
+      <c r="AM16" s="1">
+        <v>285.476</v>
+      </c>
+      <c r="AN16" s="1">
+        <v>245.98</v>
+      </c>
+      <c r="AO16" s="1">
+        <v>245.14500000000001</v>
+      </c>
+      <c r="AP16" s="1">
+        <v>233.3</v>
+      </c>
+      <c r="AQ16" s="1">
+        <v>261.33</v>
+      </c>
+      <c r="AR16" s="1">
+        <v>307.34399999999999</v>
+      </c>
+      <c r="AS16" s="1">
+        <v>160.88200000000001</v>
+      </c>
+      <c r="AT16" s="1">
+        <v>180.89500000000001</v>
+      </c>
+      <c r="AU16" s="1">
+        <v>189.40799999999999</v>
+      </c>
+      <c r="AV16" s="1">
+        <v>159.98500000000001</v>
+      </c>
+      <c r="AW16" s="1">
+        <v>171.85599999999999</v>
+      </c>
+      <c r="AX16" s="1">
+        <v>271.99900000000002</v>
+      </c>
+      <c r="AY16" s="1">
+        <v>254.67699999999999</v>
+      </c>
+      <c r="AZ16" s="1">
+        <v>283.38</v>
+      </c>
+      <c r="BA16" s="1">
+        <v>160.59200000000001</v>
+      </c>
+      <c r="BB16" s="1">
+        <v>230.39599999999999</v>
+      </c>
+      <c r="BC16" s="1">
+        <v>188.85599999999999</v>
+      </c>
+      <c r="BD16" s="1">
+        <v>235.01</v>
+      </c>
+      <c r="BE16" s="1">
+        <v>682.97199999999998</v>
+      </c>
+      <c r="BF16" s="1">
+        <v>210.946</v>
+      </c>
+      <c r="BG16" s="1">
+        <v>159.876</v>
+      </c>
+      <c r="BH16" s="1">
+        <v>901.87</v>
+      </c>
+      <c r="BI16" s="1">
+        <v>228.685</v>
+      </c>
+      <c r="BJ16" s="1">
+        <v>312.971</v>
+      </c>
+      <c r="BK16" s="1">
+        <v>289.875</v>
+      </c>
+      <c r="BL16" s="1">
+        <v>211.53899999999999</v>
+      </c>
+      <c r="BM16" s="1">
+        <v>243.59100000000001</v>
+      </c>
+      <c r="BN16" s="1">
+        <v>210.97200000000001</v>
+      </c>
+      <c r="BO16" s="1">
+        <v>1531.77</v>
+      </c>
+      <c r="BP16" s="1">
+        <v>210.94399999999999</v>
+      </c>
+      <c r="BQ16" s="1">
+        <v>505.01</v>
+      </c>
+      <c r="BR16" s="1">
+        <v>200.012</v>
+      </c>
+      <c r="BS16" s="1">
+        <v>159.80099999999999</v>
+      </c>
+      <c r="BT16" s="1">
+        <v>199.41499999999999</v>
+      </c>
+      <c r="BU16" s="1">
+        <v>185.71799999999999</v>
+      </c>
+      <c r="BV16" s="1">
+        <v>233.41900000000001</v>
+      </c>
+      <c r="BW16" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="BX16" s="1">
+        <v>223.68799999999999</v>
+      </c>
+      <c r="BY16" s="1">
+        <v>206.00899999999999</v>
+      </c>
+      <c r="BZ16" s="1">
+        <v>173.441</v>
+      </c>
+      <c r="CA16" s="1">
+        <v>163.71299999999999</v>
+      </c>
+      <c r="CB16" s="1">
+        <v>210.952</v>
+      </c>
+      <c r="CC16" s="1">
+        <v>171.928</v>
+      </c>
+      <c r="CD16" s="1">
+        <v>161.846</v>
+      </c>
+      <c r="CE16" s="1">
+        <v>159.83099999999999</v>
+      </c>
+      <c r="CF16" s="1">
+        <v>210.94399999999999</v>
+      </c>
+      <c r="CG16" s="1">
+        <v>159.78</v>
+      </c>
+      <c r="CH16" s="1">
+        <v>159.85599999999999</v>
+      </c>
+      <c r="CI16" s="1">
+        <v>159.90899999999999</v>
+      </c>
+      <c r="CJ16" s="1">
+        <v>159.88</v>
+      </c>
+      <c r="CK16" s="1">
+        <v>6.0984400000000001</v>
+      </c>
+      <c r="CL16" s="1">
+        <v>159.84899999999999</v>
+      </c>
+      <c r="CM16" s="1">
+        <v>353.95299999999997</v>
+      </c>
+      <c r="CN16" s="1">
+        <v>160</v>
+      </c>
+      <c r="CO16" s="1">
+        <v>193.71600000000001</v>
+      </c>
+      <c r="CP16" s="1">
+        <v>160.49700000000001</v>
+      </c>
+      <c r="CQ16" s="1">
+        <v>290.13799999999998</v>
+      </c>
+      <c r="CR16" s="1">
+        <v>603.86300000000006</v>
+      </c>
+      <c r="CS16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CT16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CU16" s="1">
+        <v>41</v>
+      </c>
+      <c r="CV16" s="1">
+        <v>0.63230500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/tool/PMP/old/PMP_Sample.xlsx
+++ b/tool/PMP/old/PMP_Sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E813EEE7-D9D6-45FA-B251-5789A582DB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6A63C6-7690-46E5-B257-92536452891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="105">
   <si>
     <t>Year / Station</t>
   </si>
@@ -211,18 +211,12 @@
     <t>logistic</t>
   </si>
   <si>
-    <t>loglaplace</t>
-  </si>
-  <si>
     <t>lognorm</t>
   </si>
   <si>
     <t>loguniform</t>
   </si>
   <si>
-    <t>lomax</t>
-  </si>
-  <si>
     <t>maxwell</t>
   </si>
   <si>
@@ -241,9 +235,6 @@
     <t>nct</t>
   </si>
   <si>
-    <t>ncx2</t>
-  </si>
-  <si>
     <t>norm</t>
   </si>
   <si>
@@ -274,9 +265,6 @@
     <t>rice</t>
   </si>
   <si>
-    <t>semicircular</t>
-  </si>
-  <si>
     <t>skewnorm</t>
   </si>
   <si>
@@ -349,9 +337,6 @@
     <t>zzgumbel</t>
   </si>
   <si>
-    <t>zzloggumbel</t>
-  </si>
-  <si>
     <t>Tr</t>
   </si>
   <si>
@@ -359,6 +344,15 @@
   </si>
   <si>
     <t>R.HydroTools-Gumbel</t>
+  </si>
+  <si>
+    <t>R.HydroTools-Beta</t>
+  </si>
+  <si>
+    <t>R.HydroTools-Johnsonsb</t>
+  </si>
+  <si>
+    <t>R.HydroTools-Anglit</t>
   </si>
 </sst>
 </file>
@@ -440,37 +434,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -674,6 +638,303 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020230-R.HydroTools-Beta</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>PMP!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!$P$4:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>116.04600000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140.715</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150.77000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>156.495</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>158.31200000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>159.18700000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B4A2-4502-9742-A60DED037D90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!$Q$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020230-R.HydroTools-Johnsonsb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>PMP!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!$Q$4:$Q$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>118.82899999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>141.88900000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150.74</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>156.07900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>158.08099999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>159.268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B4A2-4502-9742-A60DED037D90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!$R$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>-R.HydroTools-Anglit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>PMP!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!$R$4:$R$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>114.28700000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138.881</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>152.80099999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>164.61099999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170.44399999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>174.53800000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-B4A2-4502-9742-A60DED037D90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -737,6 +998,7 @@
         <c:axId val="489674880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1426,12 +1688,12 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>117311</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>182217</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>82826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>45554</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>426555</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>33130</xdr:rowOff>
     </xdr:to>
@@ -3766,7 +4028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EEC4ED-A2A6-48CB-9363-E12F4E5CCB23}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
@@ -3774,51 +4036,60 @@
     <col min="16" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B2" s="2">
         <v>2502023</v>
       </c>
@@ -3861,17 +4132,23 @@
       <c r="O2" s="2">
         <v>25020230</v>
       </c>
+      <c r="P2" s="2">
+        <v>25020230</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>25020230</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT(B2,"-",B1)</f>
         <v>2502023-Excel-Gumbel</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f t="shared" ref="C3:O3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
+        <f t="shared" ref="C3:R3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
         <v>2502026-Excel-Gumbel</v>
       </c>
       <c r="D3" s="2" t="str">
@@ -3922,8 +4199,20 @@
         <f t="shared" si="0"/>
         <v>25020230-R.HydroTools-Gumbel</v>
       </c>
+      <c r="P3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>25020230-R.HydroTools-Beta</v>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>25020230-R.HydroTools-Johnsonsb</v>
+      </c>
+      <c r="R3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>-R.HydroTools-Anglit</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.6">
       <c r="A4" s="3">
         <v>2.33</v>
       </c>
@@ -3969,8 +4258,17 @@
       <c r="O4" s="3">
         <v>122.61199999999999</v>
       </c>
+      <c r="P4" s="1">
+        <v>116.04600000000001</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>118.82899999999999</v>
+      </c>
+      <c r="R4" s="1">
+        <v>114.28700000000001</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>5</v>
       </c>
@@ -4016,8 +4314,17 @@
       <c r="O5" s="3">
         <v>147.001</v>
       </c>
+      <c r="P5" s="1">
+        <v>140.715</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>141.88900000000001</v>
+      </c>
+      <c r="R5" s="1">
+        <v>138.881</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.6">
       <c r="A6" s="3">
         <v>10</v>
       </c>
@@ -4063,8 +4370,17 @@
       <c r="O6" s="3">
         <v>166.86600000000001</v>
       </c>
+      <c r="P6" s="1">
+        <v>150.77000000000001</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>150.74</v>
+      </c>
+      <c r="R6" s="1">
+        <v>152.80099999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>25</v>
       </c>
@@ -4110,8 +4426,17 @@
       <c r="O7" s="3">
         <v>191.965</v>
       </c>
+      <c r="P7" s="1">
+        <v>156.495</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>156.07900000000001</v>
+      </c>
+      <c r="R7" s="1">
+        <v>164.61099999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.6">
       <c r="A8" s="3">
         <v>50</v>
       </c>
@@ -4157,8 +4482,17 @@
       <c r="O8" s="3">
         <v>210.584</v>
       </c>
+      <c r="P8" s="1">
+        <v>158.31200000000001</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>158.08099999999999</v>
+      </c>
+      <c r="R8" s="1">
+        <v>170.44399999999999</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>100</v>
       </c>
@@ -4203,6 +4537,15 @@
       </c>
       <c r="O9" s="3">
         <v>229.06700000000001</v>
+      </c>
+      <c r="P9" s="1">
+        <v>159.18700000000001</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>159.268</v>
+      </c>
+      <c r="R9" s="1">
+        <v>174.53800000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4213,13 +4556,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC3BD22-A60D-404D-A6C3-12A1448027F8}">
-  <dimension ref="A1:CV16"/>
+  <dimension ref="A1:CQ16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4491,37 +4834,22 @@
         <v>90</v>
       </c>
       <c r="CM1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CN1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="CQ1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>98</v>
-      </c>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -4691,139 +5019,124 @@
         <v>107.31699999999999</v>
       </c>
       <c r="BE2" s="1">
-        <v>109</v>
+        <v>107.31699999999999</v>
       </c>
       <c r="BF2" s="1">
+        <v>99.021100000000004</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>104.449</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>100.69</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>100.03</v>
+      </c>
+      <c r="BJ2" s="1">
+        <v>107.346</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>104.224</v>
+      </c>
+      <c r="BL2" s="1">
+        <v>107.31399999999999</v>
+      </c>
+      <c r="BM2" s="1">
         <v>107.31699999999999</v>
       </c>
-      <c r="BG2" s="1">
-        <v>99.021100000000004</v>
-      </c>
-      <c r="BH2" s="1">
-        <v>126.483</v>
-      </c>
-      <c r="BI2" s="1">
-        <v>104.449</v>
-      </c>
-      <c r="BJ2" s="1">
-        <v>100.69</v>
-      </c>
-      <c r="BK2" s="1">
-        <v>100.03</v>
-      </c>
-      <c r="BL2" s="1">
-        <v>107.346</v>
-      </c>
-      <c r="BM2" s="1">
-        <v>104.224</v>
-      </c>
       <c r="BN2" s="1">
-        <v>107.31399999999999</v>
+        <v>86.660600000000002</v>
       </c>
       <c r="BO2" s="1">
-        <v>-11.0053</v>
+        <v>108.60899999999999</v>
       </c>
       <c r="BP2" s="1">
+        <v>78.021199999999993</v>
+      </c>
+      <c r="BQ2" s="1">
+        <v>109.31</v>
+      </c>
+      <c r="BR2" s="1">
+        <v>111.61499999999999</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>103.432</v>
+      </c>
+      <c r="BT2" s="1">
+        <v>67.500200000000007</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>105.86199999999999</v>
+      </c>
+      <c r="BV2" s="1">
+        <v>110.85899999999999</v>
+      </c>
+      <c r="BW2" s="1">
+        <v>116.589</v>
+      </c>
+      <c r="BX2" s="1">
         <v>107.31699999999999</v>
       </c>
-      <c r="BQ2" s="1">
-        <v>86.660600000000002</v>
-      </c>
-      <c r="BR2" s="1">
-        <v>108.60899999999999</v>
-      </c>
-      <c r="BS2" s="1">
-        <v>78.021199999999993</v>
-      </c>
-      <c r="BT2" s="1">
-        <v>109.31</v>
-      </c>
-      <c r="BU2" s="1">
-        <v>111.61499999999999</v>
-      </c>
-      <c r="BV2" s="1">
-        <v>103.432</v>
-      </c>
-      <c r="BW2" s="1">
-        <v>67.500200000000007</v>
-      </c>
-      <c r="BX2" s="1">
-        <v>105.86199999999999</v>
-      </c>
       <c r="BY2" s="1">
-        <v>110.85899999999999</v>
+        <v>129.82300000000001</v>
       </c>
       <c r="BZ2" s="1">
-        <v>107.31699999999999</v>
+        <v>116.613</v>
       </c>
       <c r="CA2" s="1">
-        <v>116.589</v>
+        <v>90.456699999999998</v>
       </c>
       <c r="CB2" s="1">
         <v>107.31699999999999</v>
       </c>
       <c r="CC2" s="1">
-        <v>129.82300000000001</v>
+        <v>84.0655</v>
       </c>
       <c r="CD2" s="1">
-        <v>116.613</v>
+        <v>95.730099999999993</v>
       </c>
       <c r="CE2" s="1">
-        <v>90.456699999999998</v>
+        <v>100</v>
       </c>
       <c r="CF2" s="1">
-        <v>107.31699999999999</v>
+        <v>100</v>
       </c>
       <c r="CG2" s="1">
-        <v>84.0655</v>
+        <v>2.96705</v>
       </c>
       <c r="CH2" s="1">
-        <v>95.730099999999993</v>
+        <v>97.678100000000001</v>
       </c>
       <c r="CI2" s="1">
-        <v>100</v>
+        <v>96.446799999999996</v>
       </c>
       <c r="CJ2" s="1">
-        <v>100</v>
+        <v>159.721</v>
       </c>
       <c r="CK2" s="1">
-        <v>2.96705</v>
+        <v>109.47199999999999</v>
       </c>
       <c r="CL2" s="1">
-        <v>97.678100000000001</v>
+        <v>100.309</v>
       </c>
       <c r="CM2" s="1">
-        <v>96.446799999999996</v>
-      </c>
-      <c r="CN2" s="1">
-        <v>159.721</v>
-      </c>
-      <c r="CO2" s="1">
-        <v>109.47199999999999</v>
+        <v>116.998</v>
+      </c>
+      <c r="CN2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO2" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP2" s="1">
-        <v>100.309</v>
+        <v>41</v>
       </c>
       <c r="CQ2" s="1">
-        <v>116.998</v>
-      </c>
-      <c r="CR2" s="1">
-        <v>96.317999999999998</v>
-      </c>
-      <c r="CS2" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU2" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV2" s="1">
         <v>0.75</v>
       </c>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -4993,139 +5306,124 @@
         <v>112.589</v>
       </c>
       <c r="BE3" s="1">
-        <v>114.03700000000001</v>
+        <v>113.301</v>
       </c>
       <c r="BF3" s="1">
+        <v>107.56100000000001</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>110.666</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>107.348</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>105.279</v>
+      </c>
+      <c r="BJ3" s="1">
+        <v>113.34399999999999</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>110.51</v>
+      </c>
+      <c r="BL3" s="1">
+        <v>113.3</v>
+      </c>
+      <c r="BM3" s="1">
         <v>113.301</v>
       </c>
-      <c r="BG3" s="1">
-        <v>107.56100000000001</v>
-      </c>
-      <c r="BH3" s="1">
-        <v>145.53800000000001</v>
-      </c>
-      <c r="BI3" s="1">
-        <v>110.666</v>
-      </c>
-      <c r="BJ3" s="1">
-        <v>107.348</v>
-      </c>
-      <c r="BK3" s="1">
-        <v>105.279</v>
-      </c>
-      <c r="BL3" s="1">
-        <v>113.34399999999999</v>
-      </c>
-      <c r="BM3" s="1">
-        <v>110.51</v>
-      </c>
       <c r="BN3" s="1">
-        <v>113.3</v>
+        <v>96.941400000000002</v>
       </c>
       <c r="BO3" s="1">
-        <v>62.697800000000001</v>
+        <v>114.536</v>
       </c>
       <c r="BP3" s="1">
+        <v>87.360100000000003</v>
+      </c>
+      <c r="BQ3" s="1">
+        <v>115.205</v>
+      </c>
+      <c r="BR3" s="1">
+        <v>117.34699999999999</v>
+      </c>
+      <c r="BS3" s="1">
+        <v>109.741</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>75.443899999999999</v>
+      </c>
+      <c r="BU3" s="1">
+        <v>111.96</v>
+      </c>
+      <c r="BV3" s="1">
+        <v>116.053</v>
+      </c>
+      <c r="BW3" s="1">
+        <v>123.045</v>
+      </c>
+      <c r="BX3" s="1">
+        <v>113.30200000000001</v>
+      </c>
+      <c r="BY3" s="1">
+        <v>136.79499999999999</v>
+      </c>
+      <c r="BZ3" s="1">
+        <v>123.19799999999999</v>
+      </c>
+      <c r="CA3" s="1">
+        <v>98.857299999999995</v>
+      </c>
+      <c r="CB3" s="1">
         <v>113.301</v>
       </c>
-      <c r="BQ3" s="1">
-        <v>96.941400000000002</v>
-      </c>
-      <c r="BR3" s="1">
-        <v>114.536</v>
-      </c>
-      <c r="BS3" s="1">
-        <v>87.360100000000003</v>
-      </c>
-      <c r="BT3" s="1">
-        <v>115.205</v>
-      </c>
-      <c r="BU3" s="1">
-        <v>117.34699999999999</v>
-      </c>
-      <c r="BV3" s="1">
-        <v>109.741</v>
-      </c>
-      <c r="BW3" s="1">
-        <v>75.443899999999999</v>
-      </c>
-      <c r="BX3" s="1">
-        <v>111.96</v>
-      </c>
-      <c r="BY3" s="1">
-        <v>116.053</v>
-      </c>
-      <c r="BZ3" s="1">
-        <v>114.79300000000001</v>
-      </c>
-      <c r="CA3" s="1">
-        <v>123.045</v>
-      </c>
-      <c r="CB3" s="1">
-        <v>113.30200000000001</v>
-      </c>
       <c r="CC3" s="1">
-        <v>136.79499999999999</v>
+        <v>92.069800000000001</v>
       </c>
       <c r="CD3" s="1">
-        <v>123.19799999999999</v>
+        <v>104.181</v>
       </c>
       <c r="CE3" s="1">
-        <v>98.857299999999995</v>
+        <v>108.786</v>
       </c>
       <c r="CF3" s="1">
-        <v>113.301</v>
+        <v>108.498</v>
       </c>
       <c r="CG3" s="1">
-        <v>92.069800000000001</v>
+        <v>3.2704300000000002</v>
       </c>
       <c r="CH3" s="1">
-        <v>104.181</v>
+        <v>105.13500000000001</v>
       </c>
       <c r="CI3" s="1">
-        <v>108.786</v>
+        <v>100.371</v>
       </c>
       <c r="CJ3" s="1">
-        <v>108.498</v>
+        <v>159.89500000000001</v>
       </c>
       <c r="CK3" s="1">
-        <v>3.2704300000000002</v>
+        <v>115.33799999999999</v>
       </c>
       <c r="CL3" s="1">
-        <v>105.13500000000001</v>
+        <v>108.851</v>
       </c>
       <c r="CM3" s="1">
-        <v>100.371</v>
-      </c>
-      <c r="CN3" s="1">
-        <v>159.89500000000001</v>
-      </c>
-      <c r="CO3" s="1">
-        <v>115.33799999999999</v>
+        <v>122.61199999999999</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO3" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP3" s="1">
-        <v>108.851</v>
+        <v>41</v>
       </c>
       <c r="CQ3" s="1">
-        <v>122.61199999999999</v>
-      </c>
-      <c r="CR3" s="1">
-        <v>102.22499999999999</v>
-      </c>
-      <c r="CS3" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU3" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV3" s="1">
         <v>0.729209</v>
       </c>
     </row>
-    <row r="4" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -5163,7 +5461,7 @@
         <v>142.167</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N4" s="1">
         <v>135.61000000000001</v>
@@ -5295,139 +5593,124 @@
         <v>132.947</v>
       </c>
       <c r="BE4" s="1">
-        <v>142.91900000000001</v>
+        <v>135.54</v>
       </c>
       <c r="BF4" s="1">
+        <v>135.41800000000001</v>
+      </c>
+      <c r="BG4" s="1">
+        <v>135.136</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>136.44300000000001</v>
+      </c>
+      <c r="BI4" s="1">
+        <v>129.59200000000001</v>
+      </c>
+      <c r="BJ4" s="1">
+        <v>135.654</v>
+      </c>
+      <c r="BK4" s="1">
+        <v>135.71</v>
+      </c>
+      <c r="BL4" s="1">
+        <v>135.54300000000001</v>
+      </c>
+      <c r="BM4" s="1">
         <v>135.54</v>
       </c>
-      <c r="BG4" s="1">
-        <v>135.41800000000001</v>
-      </c>
-      <c r="BH4" s="1">
-        <v>240.80699999999999</v>
-      </c>
-      <c r="BI4" s="1">
-        <v>135.136</v>
-      </c>
-      <c r="BJ4" s="1">
-        <v>136.44300000000001</v>
-      </c>
-      <c r="BK4" s="1">
-        <v>129.59200000000001</v>
-      </c>
-      <c r="BL4" s="1">
-        <v>135.654</v>
-      </c>
-      <c r="BM4" s="1">
-        <v>135.71</v>
-      </c>
       <c r="BN4" s="1">
-        <v>135.54300000000001</v>
+        <v>148.34299999999999</v>
       </c>
       <c r="BO4" s="1">
-        <v>353.13299999999998</v>
+        <v>135.85</v>
       </c>
       <c r="BP4" s="1">
+        <v>122.88800000000001</v>
+      </c>
+      <c r="BQ4" s="1">
+        <v>136.196</v>
+      </c>
+      <c r="BR4" s="1">
+        <v>136.63200000000001</v>
+      </c>
+      <c r="BS4" s="1">
+        <v>134.999</v>
+      </c>
+      <c r="BT4" s="1">
+        <v>92.534199999999998</v>
+      </c>
+      <c r="BU4" s="1">
+        <v>135.34899999999999</v>
+      </c>
+      <c r="BV4" s="1">
+        <v>135.899</v>
+      </c>
+      <c r="BW4" s="1">
+        <v>141.84700000000001</v>
+      </c>
+      <c r="BX4" s="1">
+        <v>135.542</v>
+      </c>
+      <c r="BY4" s="1">
+        <v>156.798</v>
+      </c>
+      <c r="BZ4" s="1">
+        <v>142.09</v>
+      </c>
+      <c r="CA4" s="1">
+        <v>128.99100000000001</v>
+      </c>
+      <c r="CB4" s="1">
         <v>135.54</v>
       </c>
-      <c r="BQ4" s="1">
-        <v>148.34299999999999</v>
-      </c>
-      <c r="BR4" s="1">
-        <v>135.85</v>
-      </c>
-      <c r="BS4" s="1">
-        <v>122.88800000000001</v>
-      </c>
-      <c r="BT4" s="1">
-        <v>136.196</v>
-      </c>
-      <c r="BU4" s="1">
-        <v>136.63200000000001</v>
-      </c>
-      <c r="BV4" s="1">
-        <v>134.999</v>
-      </c>
-      <c r="BW4" s="1">
-        <v>92.534199999999998</v>
-      </c>
-      <c r="BX4" s="1">
-        <v>135.34899999999999</v>
-      </c>
-      <c r="BY4" s="1">
-        <v>135.899</v>
-      </c>
-      <c r="BZ4" s="1">
-        <v>140.30500000000001</v>
-      </c>
-      <c r="CA4" s="1">
-        <v>141.84700000000001</v>
-      </c>
-      <c r="CB4" s="1">
-        <v>135.542</v>
-      </c>
       <c r="CC4" s="1">
-        <v>156.798</v>
+        <v>123.018</v>
       </c>
       <c r="CD4" s="1">
-        <v>142.09</v>
+        <v>132.72300000000001</v>
       </c>
       <c r="CE4" s="1">
-        <v>128.99100000000001</v>
+        <v>136.93799999999999</v>
       </c>
       <c r="CF4" s="1">
-        <v>135.54</v>
+        <v>136</v>
       </c>
       <c r="CG4" s="1">
-        <v>123.018</v>
+        <v>4.4239699999999997</v>
       </c>
       <c r="CH4" s="1">
-        <v>132.72300000000001</v>
+        <v>131.55099999999999</v>
       </c>
       <c r="CI4" s="1">
-        <v>136.93799999999999</v>
+        <v>122.336</v>
       </c>
       <c r="CJ4" s="1">
-        <v>136</v>
+        <v>159.99799999999999</v>
       </c>
       <c r="CK4" s="1">
-        <v>4.4239699999999997</v>
+        <v>135.964</v>
       </c>
       <c r="CL4" s="1">
-        <v>131.55099999999999</v>
+        <v>136.494</v>
       </c>
       <c r="CM4" s="1">
-        <v>122.336</v>
-      </c>
-      <c r="CN4" s="1">
-        <v>159.99799999999999</v>
-      </c>
-      <c r="CO4" s="1">
-        <v>135.964</v>
+        <v>147.001</v>
+      </c>
+      <c r="CN4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO4" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP4" s="1">
-        <v>136.494</v>
+        <v>41</v>
       </c>
       <c r="CQ4" s="1">
-        <v>147.001</v>
-      </c>
-      <c r="CR4" s="1">
-        <v>132.39099999999999</v>
-      </c>
-      <c r="CS4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU4" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV4" s="1">
         <v>0.67232000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -5465,7 +5748,7 @@
         <v>149.79900000000001</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N5" s="1">
         <v>151.52500000000001</v>
@@ -5597,139 +5880,124 @@
         <v>147.94</v>
       </c>
       <c r="BE5" s="1">
-        <v>175.40600000000001</v>
+        <v>150.292</v>
       </c>
       <c r="BF5" s="1">
+        <v>147.67699999999999</v>
+      </c>
+      <c r="BG5" s="1">
+        <v>152.357</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>160.34899999999999</v>
+      </c>
+      <c r="BI5" s="1">
+        <v>150.761</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>150.47200000000001</v>
+      </c>
+      <c r="BK5" s="1">
+        <v>154.053</v>
+      </c>
+      <c r="BL5" s="1">
+        <v>150.29900000000001</v>
+      </c>
+      <c r="BM5" s="1">
         <v>150.292</v>
       </c>
-      <c r="BG5" s="1">
-        <v>147.67699999999999</v>
-      </c>
-      <c r="BH5" s="1">
-        <v>327.29000000000002</v>
-      </c>
-      <c r="BI5" s="1">
-        <v>152.357</v>
-      </c>
-      <c r="BJ5" s="1">
-        <v>160.34899999999999</v>
-      </c>
-      <c r="BK5" s="1">
-        <v>150.761</v>
-      </c>
-      <c r="BL5" s="1">
-        <v>150.47200000000001</v>
-      </c>
-      <c r="BM5" s="1">
-        <v>154.053</v>
-      </c>
       <c r="BN5" s="1">
-        <v>150.29900000000001</v>
+        <v>195.00299999999999</v>
       </c>
       <c r="BO5" s="1">
-        <v>560.17399999999998</v>
+        <v>149.376</v>
       </c>
       <c r="BP5" s="1">
+        <v>140.76499999999999</v>
+      </c>
+      <c r="BQ5" s="1">
+        <v>149.40899999999999</v>
+      </c>
+      <c r="BR5" s="1">
+        <v>147.934</v>
+      </c>
+      <c r="BS5" s="1">
+        <v>153.00800000000001</v>
+      </c>
+      <c r="BT5" s="1">
+        <v>94.675700000000006</v>
+      </c>
+      <c r="BU5" s="1">
+        <v>151.51300000000001</v>
+      </c>
+      <c r="BV5" s="1">
+        <v>149.375</v>
+      </c>
+      <c r="BW5" s="1">
+        <v>149.55000000000001</v>
+      </c>
+      <c r="BX5" s="1">
+        <v>150.29599999999999</v>
+      </c>
+      <c r="BY5" s="1">
+        <v>164.61</v>
+      </c>
+      <c r="BZ5" s="1">
+        <v>149.47</v>
+      </c>
+      <c r="CA5" s="1">
+        <v>143.84800000000001</v>
+      </c>
+      <c r="CB5" s="1">
         <v>150.292</v>
       </c>
-      <c r="BQ5" s="1">
-        <v>195.00299999999999</v>
-      </c>
-      <c r="BR5" s="1">
-        <v>149.376</v>
-      </c>
-      <c r="BS5" s="1">
-        <v>140.76499999999999</v>
-      </c>
-      <c r="BT5" s="1">
-        <v>149.40899999999999</v>
-      </c>
-      <c r="BU5" s="1">
-        <v>147.934</v>
-      </c>
-      <c r="BV5" s="1">
-        <v>153.00800000000001</v>
-      </c>
-      <c r="BW5" s="1">
-        <v>94.675700000000006</v>
-      </c>
-      <c r="BX5" s="1">
-        <v>151.51300000000001</v>
-      </c>
-      <c r="BY5" s="1">
-        <v>149.375</v>
-      </c>
-      <c r="BZ5" s="1">
-        <v>153.39599999999999</v>
-      </c>
-      <c r="CA5" s="1">
-        <v>149.55000000000001</v>
-      </c>
-      <c r="CB5" s="1">
-        <v>150.29599999999999</v>
-      </c>
       <c r="CC5" s="1">
-        <v>164.61</v>
+        <v>139.92699999999999</v>
       </c>
       <c r="CD5" s="1">
-        <v>149.47</v>
+        <v>146.012</v>
       </c>
       <c r="CE5" s="1">
-        <v>143.84800000000001</v>
+        <v>148.857</v>
       </c>
       <c r="CF5" s="1">
-        <v>150.292</v>
+        <v>148</v>
       </c>
       <c r="CG5" s="1">
-        <v>139.92699999999999</v>
+        <v>5.1534599999999999</v>
       </c>
       <c r="CH5" s="1">
-        <v>146.012</v>
+        <v>145.185</v>
       </c>
       <c r="CI5" s="1">
-        <v>148.857</v>
+        <v>145.64699999999999</v>
       </c>
       <c r="CJ5" s="1">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="CK5" s="1">
-        <v>5.1534599999999999</v>
+        <v>148.64699999999999</v>
       </c>
       <c r="CL5" s="1">
-        <v>145.185</v>
+        <v>148.55600000000001</v>
       </c>
       <c r="CM5" s="1">
-        <v>145.64699999999999</v>
-      </c>
-      <c r="CN5" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO5" s="1">
-        <v>148.64699999999999</v>
+        <v>166.86600000000001</v>
+      </c>
+      <c r="CN5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO5" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP5" s="1">
-        <v>148.55600000000001</v>
+        <v>41</v>
       </c>
       <c r="CQ5" s="1">
-        <v>166.86600000000001</v>
-      </c>
-      <c r="CR5" s="1">
-        <v>163.42699999999999</v>
-      </c>
-      <c r="CS5" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT5" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU5" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV5" s="1">
         <v>0.65132199999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5767,7 +6035,7 @@
         <v>152.43199999999999</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N6" s="1">
         <v>159.60599999999999</v>
@@ -5899,139 +6167,124 @@
         <v>156.108</v>
       </c>
       <c r="BE6" s="1">
-        <v>197.726</v>
+        <v>157.654</v>
       </c>
       <c r="BF6" s="1">
+        <v>151.77699999999999</v>
+      </c>
+      <c r="BG6" s="1">
+        <v>161.19200000000001</v>
+      </c>
+      <c r="BH6" s="1">
+        <v>173.91900000000001</v>
+      </c>
+      <c r="BI6" s="1">
+        <v>163.047</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>157.87100000000001</v>
+      </c>
+      <c r="BK6" s="1">
+        <v>163.69900000000001</v>
+      </c>
+      <c r="BL6" s="1">
+        <v>157.66300000000001</v>
+      </c>
+      <c r="BM6" s="1">
         <v>157.654</v>
       </c>
-      <c r="BG6" s="1">
-        <v>151.77699999999999</v>
-      </c>
-      <c r="BH6" s="1">
-        <v>377.87900000000002</v>
-      </c>
-      <c r="BI6" s="1">
-        <v>161.19200000000001</v>
-      </c>
-      <c r="BJ6" s="1">
-        <v>173.91900000000001</v>
-      </c>
-      <c r="BK6" s="1">
-        <v>163.047</v>
-      </c>
-      <c r="BL6" s="1">
-        <v>157.87100000000001</v>
-      </c>
-      <c r="BM6" s="1">
-        <v>163.69900000000001</v>
-      </c>
       <c r="BN6" s="1">
-        <v>157.66300000000001</v>
+        <v>222.298</v>
       </c>
       <c r="BO6" s="1">
-        <v>667.77800000000002</v>
+        <v>155.946</v>
       </c>
       <c r="BP6" s="1">
+        <v>147.02799999999999</v>
+      </c>
+      <c r="BQ6" s="1">
+        <v>155.81800000000001</v>
+      </c>
+      <c r="BR6" s="1">
+        <v>153.20099999999999</v>
+      </c>
+      <c r="BS6" s="1">
+        <v>162.28700000000001</v>
+      </c>
+      <c r="BT6" s="1">
+        <v>94.902199999999993</v>
+      </c>
+      <c r="BU6" s="1">
+        <v>159.77799999999999</v>
+      </c>
+      <c r="BV6" s="1">
+        <v>156.16200000000001</v>
+      </c>
+      <c r="BW6" s="1">
+        <v>152.24199999999999</v>
+      </c>
+      <c r="BX6" s="1">
+        <v>157.65799999999999</v>
+      </c>
+      <c r="BY6" s="1">
+        <v>167.11699999999999</v>
+      </c>
+      <c r="BZ6" s="1">
+        <v>152.00200000000001</v>
+      </c>
+      <c r="CA6" s="1">
+        <v>149.077</v>
+      </c>
+      <c r="CB6" s="1">
         <v>157.654</v>
       </c>
-      <c r="BQ6" s="1">
-        <v>222.298</v>
-      </c>
-      <c r="BR6" s="1">
-        <v>155.946</v>
-      </c>
-      <c r="BS6" s="1">
-        <v>147.02799999999999</v>
-      </c>
-      <c r="BT6" s="1">
-        <v>155.81800000000001</v>
-      </c>
-      <c r="BU6" s="1">
-        <v>153.20099999999999</v>
-      </c>
-      <c r="BV6" s="1">
-        <v>162.28700000000001</v>
-      </c>
-      <c r="BW6" s="1">
-        <v>94.902199999999993</v>
-      </c>
-      <c r="BX6" s="1">
-        <v>159.77799999999999</v>
-      </c>
-      <c r="BY6" s="1">
-        <v>156.16200000000001</v>
-      </c>
-      <c r="BZ6" s="1">
-        <v>158.501</v>
-      </c>
-      <c r="CA6" s="1">
-        <v>152.24199999999999</v>
-      </c>
-      <c r="CB6" s="1">
-        <v>157.65799999999999</v>
-      </c>
       <c r="CC6" s="1">
-        <v>167.11699999999999</v>
+        <v>146.21100000000001</v>
       </c>
       <c r="CD6" s="1">
-        <v>152.00200000000001</v>
+        <v>150.59</v>
       </c>
       <c r="CE6" s="1">
-        <v>149.077</v>
+        <v>152.71899999999999</v>
       </c>
       <c r="CF6" s="1">
-        <v>157.654</v>
+        <v>152</v>
       </c>
       <c r="CG6" s="1">
-        <v>146.21100000000001</v>
+        <v>5.45</v>
       </c>
       <c r="CH6" s="1">
-        <v>150.59</v>
+        <v>150.035</v>
       </c>
       <c r="CI6" s="1">
-        <v>152.71899999999999</v>
+        <v>160.61600000000001</v>
       </c>
       <c r="CJ6" s="1">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="CK6" s="1">
-        <v>5.45</v>
+        <v>154.696</v>
       </c>
       <c r="CL6" s="1">
-        <v>150.035</v>
+        <v>152.577</v>
       </c>
       <c r="CM6" s="1">
-        <v>160.61600000000001</v>
-      </c>
-      <c r="CN6" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO6" s="1">
-        <v>154.696</v>
+        <v>178.07300000000001</v>
+      </c>
+      <c r="CN6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO6" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP6" s="1">
-        <v>152.577</v>
+        <v>41</v>
       </c>
       <c r="CQ6" s="1">
-        <v>178.07300000000001</v>
-      </c>
-      <c r="CR6" s="1">
-        <v>184.047</v>
-      </c>
-      <c r="CS6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT6" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU6" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV6" s="1">
         <v>0.64473599999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -6069,7 +6322,7 @@
         <v>153.87899999999999</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N7" s="1">
         <v>164.94900000000001</v>
@@ -6201,139 +6454,124 @@
         <v>161.75399999999999</v>
       </c>
       <c r="BE7" s="1">
-        <v>215.26</v>
+        <v>162.476</v>
       </c>
       <c r="BF7" s="1">
-        <v>162.476</v>
+        <v>153.83000000000001</v>
       </c>
       <c r="BG7" s="1">
-        <v>153.83000000000001</v>
+        <v>167.05600000000001</v>
       </c>
       <c r="BH7" s="1">
-        <v>413.77300000000002</v>
+        <v>183.45699999999999</v>
       </c>
       <c r="BI7" s="1">
-        <v>167.05600000000001</v>
+        <v>171.74799999999999</v>
       </c>
       <c r="BJ7" s="1">
-        <v>183.45699999999999</v>
+        <v>162.71899999999999</v>
       </c>
       <c r="BK7" s="1">
-        <v>171.74799999999999</v>
+        <v>170.196</v>
       </c>
       <c r="BL7" s="1">
-        <v>162.71899999999999</v>
+        <v>162.48500000000001</v>
       </c>
       <c r="BM7" s="1">
-        <v>170.196</v>
+        <v>162.47499999999999</v>
       </c>
       <c r="BN7" s="1">
-        <v>162.48500000000001</v>
+        <v>241.66399999999999</v>
       </c>
       <c r="BO7" s="1">
-        <v>739.79100000000005</v>
+        <v>160.184</v>
       </c>
       <c r="BP7" s="1">
+        <v>150.21600000000001</v>
+      </c>
+      <c r="BQ7" s="1">
+        <v>159.95400000000001</v>
+      </c>
+      <c r="BR7" s="1">
+        <v>156.53</v>
+      </c>
+      <c r="BS7" s="1">
+        <v>168.45500000000001</v>
+      </c>
+      <c r="BT7" s="1">
+        <v>94.958399999999997</v>
+      </c>
+      <c r="BU7" s="1">
+        <v>165.26300000000001</v>
+      </c>
+      <c r="BV7" s="1">
+        <v>160.624</v>
+      </c>
+      <c r="BW7" s="1">
+        <v>153.72800000000001</v>
+      </c>
+      <c r="BX7" s="1">
+        <v>162.47999999999999</v>
+      </c>
+      <c r="BY7" s="1">
+        <v>168.35400000000001</v>
+      </c>
+      <c r="BZ7" s="1">
+        <v>153.505</v>
+      </c>
+      <c r="CA7" s="1">
+        <v>151.74799999999999</v>
+      </c>
+      <c r="CB7" s="1">
         <v>162.47499999999999</v>
       </c>
-      <c r="BQ7" s="1">
-        <v>241.66399999999999</v>
-      </c>
-      <c r="BR7" s="1">
-        <v>160.184</v>
-      </c>
-      <c r="BS7" s="1">
-        <v>150.21600000000001</v>
-      </c>
-      <c r="BT7" s="1">
-        <v>159.95400000000001</v>
-      </c>
-      <c r="BU7" s="1">
-        <v>156.53</v>
-      </c>
-      <c r="BV7" s="1">
-        <v>168.45500000000001</v>
-      </c>
-      <c r="BW7" s="1">
-        <v>94.958399999999997</v>
-      </c>
-      <c r="BX7" s="1">
-        <v>165.26300000000001</v>
-      </c>
-      <c r="BY7" s="1">
-        <v>160.624</v>
-      </c>
-      <c r="BZ7" s="1">
-        <v>161.33199999999999</v>
-      </c>
-      <c r="CA7" s="1">
-        <v>153.72800000000001</v>
-      </c>
-      <c r="CB7" s="1">
-        <v>162.47999999999999</v>
-      </c>
       <c r="CC7" s="1">
-        <v>168.35400000000001</v>
+        <v>149.49600000000001</v>
       </c>
       <c r="CD7" s="1">
-        <v>153.505</v>
+        <v>152.90899999999999</v>
       </c>
       <c r="CE7" s="1">
-        <v>151.74799999999999</v>
+        <v>154.61600000000001</v>
       </c>
       <c r="CF7" s="1">
-        <v>162.47499999999999</v>
+        <v>154</v>
       </c>
       <c r="CG7" s="1">
-        <v>149.49600000000001</v>
+        <v>5.6081300000000001</v>
       </c>
       <c r="CH7" s="1">
-        <v>152.90899999999999</v>
+        <v>152.50200000000001</v>
       </c>
       <c r="CI7" s="1">
-        <v>154.61600000000001</v>
+        <v>171.77199999999999</v>
       </c>
       <c r="CJ7" s="1">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="CK7" s="1">
-        <v>5.6081300000000001</v>
+        <v>158.56100000000001</v>
       </c>
       <c r="CL7" s="1">
-        <v>152.50200000000001</v>
+        <v>154.58699999999999</v>
       </c>
       <c r="CM7" s="1">
-        <v>171.77199999999999</v>
-      </c>
-      <c r="CN7" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO7" s="1">
-        <v>158.56100000000001</v>
+        <v>185.92</v>
+      </c>
+      <c r="CN7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO7" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP7" s="1">
-        <v>154.58699999999999</v>
+        <v>41</v>
       </c>
       <c r="CQ7" s="1">
-        <v>185.92</v>
-      </c>
-      <c r="CR7" s="1">
-        <v>200.01499999999999</v>
-      </c>
-      <c r="CS7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU7" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV7" s="1">
         <v>0.64151400000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -6371,7 +6609,7 @@
         <v>154.846</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N8" s="1">
         <v>168.90700000000001</v>
@@ -6503,139 +6741,124 @@
         <v>166.07300000000001</v>
       </c>
       <c r="BE8" s="1">
-        <v>229.92400000000001</v>
+        <v>166.02500000000001</v>
       </c>
       <c r="BF8" s="1">
-        <v>166.02500000000001</v>
+        <v>155.06299999999999</v>
       </c>
       <c r="BG8" s="1">
-        <v>155.06299999999999</v>
+        <v>171.41</v>
       </c>
       <c r="BH8" s="1">
-        <v>441.61399999999998</v>
+        <v>190.82300000000001</v>
       </c>
       <c r="BI8" s="1">
-        <v>171.41</v>
+        <v>178.49199999999999</v>
       </c>
       <c r="BJ8" s="1">
-        <v>190.82300000000001</v>
+        <v>166.28800000000001</v>
       </c>
       <c r="BK8" s="1">
-        <v>178.49199999999999</v>
+        <v>175.07</v>
       </c>
       <c r="BL8" s="1">
-        <v>166.28800000000001</v>
+        <v>166.035</v>
       </c>
       <c r="BM8" s="1">
-        <v>175.07</v>
+        <v>166.024</v>
       </c>
       <c r="BN8" s="1">
-        <v>166.035</v>
+        <v>256.685</v>
       </c>
       <c r="BO8" s="1">
-        <v>793.58500000000004</v>
+        <v>163.27099999999999</v>
       </c>
       <c r="BP8" s="1">
+        <v>152.14599999999999</v>
+      </c>
+      <c r="BQ8" s="1">
+        <v>162.97</v>
+      </c>
+      <c r="BR8" s="1">
+        <v>158.922</v>
+      </c>
+      <c r="BS8" s="1">
+        <v>173.03800000000001</v>
+      </c>
+      <c r="BT8" s="1">
+        <v>94.978700000000003</v>
+      </c>
+      <c r="BU8" s="1">
+        <v>169.33699999999999</v>
+      </c>
+      <c r="BV8" s="1">
+        <v>163.916</v>
+      </c>
+      <c r="BW8" s="1">
+        <v>154.71700000000001</v>
+      </c>
+      <c r="BX8" s="1">
+        <v>166.029</v>
+      </c>
+      <c r="BY8" s="1">
+        <v>169.09100000000001</v>
+      </c>
+      <c r="BZ8" s="1">
+        <v>154.53100000000001</v>
+      </c>
+      <c r="CA8" s="1">
+        <v>153.37</v>
+      </c>
+      <c r="CB8" s="1">
         <v>166.024</v>
       </c>
-      <c r="BQ8" s="1">
-        <v>256.685</v>
-      </c>
-      <c r="BR8" s="1">
-        <v>163.27099999999999</v>
-      </c>
-      <c r="BS8" s="1">
-        <v>152.14599999999999</v>
-      </c>
-      <c r="BT8" s="1">
-        <v>162.97</v>
-      </c>
-      <c r="BU8" s="1">
-        <v>158.922</v>
-      </c>
-      <c r="BV8" s="1">
-        <v>173.03800000000001</v>
-      </c>
-      <c r="BW8" s="1">
-        <v>94.978700000000003</v>
-      </c>
-      <c r="BX8" s="1">
-        <v>169.33699999999999</v>
-      </c>
-      <c r="BY8" s="1">
-        <v>163.916</v>
-      </c>
-      <c r="BZ8" s="1">
-        <v>163.16900000000001</v>
-      </c>
-      <c r="CA8" s="1">
-        <v>154.71700000000001</v>
-      </c>
-      <c r="CB8" s="1">
-        <v>166.029</v>
-      </c>
       <c r="CC8" s="1">
-        <v>169.09100000000001</v>
+        <v>151.51599999999999</v>
       </c>
       <c r="CD8" s="1">
-        <v>154.53100000000001</v>
+        <v>154.31100000000001</v>
       </c>
       <c r="CE8" s="1">
-        <v>153.37</v>
+        <v>155.739</v>
       </c>
       <c r="CF8" s="1">
-        <v>166.024</v>
+        <v>155.19999999999999</v>
       </c>
       <c r="CG8" s="1">
-        <v>151.51599999999999</v>
+        <v>5.7056800000000001</v>
       </c>
       <c r="CH8" s="1">
-        <v>154.31100000000001</v>
+        <v>153.99199999999999</v>
       </c>
       <c r="CI8" s="1">
-        <v>155.739</v>
+        <v>180.70599999999999</v>
       </c>
       <c r="CJ8" s="1">
-        <v>155.19999999999999</v>
+        <v>160</v>
       </c>
       <c r="CK8" s="1">
-        <v>5.7056800000000001</v>
+        <v>161.35900000000001</v>
       </c>
       <c r="CL8" s="1">
-        <v>153.99199999999999</v>
+        <v>155.79300000000001</v>
       </c>
       <c r="CM8" s="1">
-        <v>180.70599999999999</v>
-      </c>
-      <c r="CN8" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO8" s="1">
-        <v>161.35900000000001</v>
+        <v>191.965</v>
+      </c>
+      <c r="CN8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO8" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP8" s="1">
-        <v>155.79300000000001</v>
+        <v>41</v>
       </c>
       <c r="CQ8" s="1">
-        <v>191.965</v>
-      </c>
-      <c r="CR8" s="1">
-        <v>213.25200000000001</v>
-      </c>
-      <c r="CS8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU8" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV8" s="1">
         <v>0.63960300000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -6673,7 +6896,7 @@
         <v>157.32400000000001</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N9" s="1">
         <v>180.363</v>
@@ -6805,139 +7028,124 @@
         <v>179.26900000000001</v>
       </c>
       <c r="BE9" s="1">
-        <v>282.14100000000002</v>
+        <v>176.18799999999999</v>
       </c>
       <c r="BF9" s="1">
-        <v>176.18799999999999</v>
+        <v>157.53</v>
       </c>
       <c r="BG9" s="1">
-        <v>157.53</v>
+        <v>184.035</v>
       </c>
       <c r="BH9" s="1">
-        <v>528.09699999999998</v>
+        <v>213.62700000000001</v>
       </c>
       <c r="BI9" s="1">
-        <v>184.035</v>
+        <v>199.428</v>
       </c>
       <c r="BJ9" s="1">
-        <v>213.62700000000001</v>
+        <v>176.51499999999999</v>
       </c>
       <c r="BK9" s="1">
-        <v>199.428</v>
+        <v>189.458</v>
       </c>
       <c r="BL9" s="1">
-        <v>176.51499999999999</v>
+        <v>176.20099999999999</v>
       </c>
       <c r="BM9" s="1">
-        <v>189.458</v>
+        <v>176.18700000000001</v>
       </c>
       <c r="BN9" s="1">
-        <v>176.20099999999999</v>
+        <v>303.346</v>
       </c>
       <c r="BO9" s="1">
-        <v>951.298</v>
+        <v>171.96</v>
       </c>
       <c r="BP9" s="1">
+        <v>156.047</v>
+      </c>
+      <c r="BQ9" s="1">
+        <v>171.48099999999999</v>
+      </c>
+      <c r="BR9" s="1">
+        <v>165.52099999999999</v>
+      </c>
+      <c r="BS9" s="1">
+        <v>186.34</v>
+      </c>
+      <c r="BT9" s="1">
+        <v>94.997600000000006</v>
+      </c>
+      <c r="BU9" s="1">
+        <v>181.179</v>
+      </c>
+      <c r="BV9" s="1">
+        <v>173.37700000000001</v>
+      </c>
+      <c r="BW9" s="1">
+        <v>157.19800000000001</v>
+      </c>
+      <c r="BX9" s="1">
+        <v>176.19200000000001</v>
+      </c>
+      <c r="BY9" s="1">
+        <v>170.553</v>
+      </c>
+      <c r="BZ9" s="1">
+        <v>157.07599999999999</v>
+      </c>
+      <c r="CA9" s="1">
+        <v>156.655</v>
+      </c>
+      <c r="CB9" s="1">
         <v>176.18700000000001</v>
       </c>
-      <c r="BQ9" s="1">
-        <v>303.346</v>
-      </c>
-      <c r="BR9" s="1">
-        <v>171.96</v>
-      </c>
-      <c r="BS9" s="1">
-        <v>156.047</v>
-      </c>
-      <c r="BT9" s="1">
-        <v>171.48099999999999</v>
-      </c>
-      <c r="BU9" s="1">
-        <v>165.52099999999999</v>
-      </c>
-      <c r="BV9" s="1">
-        <v>186.34</v>
-      </c>
-      <c r="BW9" s="1">
-        <v>94.997600000000006</v>
-      </c>
-      <c r="BX9" s="1">
-        <v>181.179</v>
-      </c>
-      <c r="BY9" s="1">
-        <v>173.37700000000001</v>
-      </c>
-      <c r="BZ9" s="1">
-        <v>167.36500000000001</v>
-      </c>
-      <c r="CA9" s="1">
-        <v>157.19800000000001</v>
-      </c>
-      <c r="CB9" s="1">
-        <v>176.19200000000001</v>
-      </c>
       <c r="CC9" s="1">
-        <v>170.553</v>
+        <v>155.67400000000001</v>
       </c>
       <c r="CD9" s="1">
-        <v>157.07599999999999</v>
+        <v>157.13900000000001</v>
       </c>
       <c r="CE9" s="1">
-        <v>156.655</v>
+        <v>157.93799999999999</v>
       </c>
       <c r="CF9" s="1">
-        <v>176.18700000000001</v>
+        <v>157.6</v>
       </c>
       <c r="CG9" s="1">
-        <v>155.67400000000001</v>
+        <v>5.9053800000000001</v>
       </c>
       <c r="CH9" s="1">
-        <v>157.13900000000001</v>
+        <v>156.99</v>
       </c>
       <c r="CI9" s="1">
-        <v>157.93799999999999</v>
+        <v>209.87899999999999</v>
       </c>
       <c r="CJ9" s="1">
-        <v>157.6</v>
+        <v>160</v>
       </c>
       <c r="CK9" s="1">
-        <v>5.9053800000000001</v>
+        <v>169.161</v>
       </c>
       <c r="CL9" s="1">
-        <v>156.99</v>
+        <v>158.20500000000001</v>
       </c>
       <c r="CM9" s="1">
-        <v>209.87899999999999</v>
-      </c>
-      <c r="CN9" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO9" s="1">
-        <v>169.161</v>
+        <v>210.584</v>
+      </c>
+      <c r="CN9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO9" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP9" s="1">
-        <v>158.20500000000001</v>
+        <v>41</v>
       </c>
       <c r="CQ9" s="1">
-        <v>210.584</v>
-      </c>
-      <c r="CR9" s="1">
-        <v>259.79399999999998</v>
-      </c>
-      <c r="CS9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT9" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU9" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV9" s="1">
         <v>0.63583000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6975,7 +7183,7 @@
         <v>158.56100000000001</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N10" s="1">
         <v>186.584</v>
@@ -7107,139 +7315,124 @@
         <v>186.89099999999999</v>
       </c>
       <c r="BE10" s="1">
-        <v>318.01600000000002</v>
+        <v>181.64099999999999</v>
       </c>
       <c r="BF10" s="1">
-        <v>181.64099999999999</v>
+        <v>158.35300000000001</v>
       </c>
       <c r="BG10" s="1">
-        <v>158.35300000000001</v>
+        <v>190.9</v>
       </c>
       <c r="BH10" s="1">
-        <v>578.68600000000004</v>
+        <v>226.959</v>
       </c>
       <c r="BI10" s="1">
-        <v>190.9</v>
+        <v>211.67099999999999</v>
       </c>
       <c r="BJ10" s="1">
-        <v>226.959</v>
+        <v>182.00399999999999</v>
       </c>
       <c r="BK10" s="1">
-        <v>211.67099999999999</v>
+        <v>197.44399999999999</v>
       </c>
       <c r="BL10" s="1">
-        <v>182.00399999999999</v>
+        <v>181.65600000000001</v>
       </c>
       <c r="BM10" s="1">
-        <v>197.44399999999999</v>
+        <v>181.64</v>
       </c>
       <c r="BN10" s="1">
-        <v>181.65600000000001</v>
+        <v>330.64100000000002</v>
       </c>
       <c r="BO10" s="1">
-        <v>1038.1600000000001</v>
+        <v>176.53100000000001</v>
       </c>
       <c r="BP10" s="1">
+        <v>157.35900000000001</v>
+      </c>
+      <c r="BQ10" s="1">
+        <v>175.977</v>
+      </c>
+      <c r="BR10" s="1">
+        <v>168.91900000000001</v>
+      </c>
+      <c r="BS10" s="1">
+        <v>193.57599999999999</v>
+      </c>
+      <c r="BT10" s="1">
+        <v>94.999600000000001</v>
+      </c>
+      <c r="BU10" s="1">
+        <v>187.642</v>
+      </c>
+      <c r="BV10" s="1">
+        <v>178.47200000000001</v>
+      </c>
+      <c r="BW10" s="1">
+        <v>158.375</v>
+      </c>
+      <c r="BX10" s="1">
+        <v>181.64599999999999</v>
+      </c>
+      <c r="BY10" s="1">
+        <v>171.03700000000001</v>
+      </c>
+      <c r="BZ10" s="1">
+        <v>158.203</v>
+      </c>
+      <c r="CA10" s="1">
+        <v>157.76300000000001</v>
+      </c>
+      <c r="CB10" s="1">
         <v>181.64</v>
       </c>
-      <c r="BQ10" s="1">
-        <v>330.64100000000002</v>
-      </c>
-      <c r="BR10" s="1">
-        <v>176.53100000000001</v>
-      </c>
-      <c r="BS10" s="1">
-        <v>157.35900000000001</v>
-      </c>
-      <c r="BT10" s="1">
-        <v>175.977</v>
-      </c>
-      <c r="BU10" s="1">
-        <v>168.91900000000001</v>
-      </c>
-      <c r="BV10" s="1">
-        <v>193.57599999999999</v>
-      </c>
-      <c r="BW10" s="1">
-        <v>94.999600000000001</v>
-      </c>
-      <c r="BX10" s="1">
-        <v>187.642</v>
-      </c>
-      <c r="BY10" s="1">
-        <v>178.47200000000001</v>
-      </c>
-      <c r="BZ10" s="1">
-        <v>169.042</v>
-      </c>
-      <c r="CA10" s="1">
-        <v>158.375</v>
-      </c>
-      <c r="CB10" s="1">
-        <v>181.64599999999999</v>
-      </c>
       <c r="CC10" s="1">
-        <v>171.03700000000001</v>
+        <v>157.09700000000001</v>
       </c>
       <c r="CD10" s="1">
-        <v>158.203</v>
+        <v>158.089</v>
       </c>
       <c r="CE10" s="1">
-        <v>157.76300000000001</v>
+        <v>158.65</v>
       </c>
       <c r="CF10" s="1">
-        <v>181.64</v>
+        <v>158.4</v>
       </c>
       <c r="CG10" s="1">
-        <v>157.09700000000001</v>
+        <v>5.9729099999999997</v>
       </c>
       <c r="CH10" s="1">
-        <v>158.089</v>
+        <v>157.99199999999999</v>
       </c>
       <c r="CI10" s="1">
-        <v>158.65</v>
+        <v>227.83</v>
       </c>
       <c r="CJ10" s="1">
-        <v>158.4</v>
+        <v>160</v>
       </c>
       <c r="CK10" s="1">
-        <v>5.9729099999999997</v>
+        <v>173.22300000000001</v>
       </c>
       <c r="CL10" s="1">
-        <v>157.99199999999999</v>
+        <v>159.00899999999999</v>
       </c>
       <c r="CM10" s="1">
-        <v>227.83</v>
-      </c>
-      <c r="CN10" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO10" s="1">
-        <v>173.22300000000001</v>
+        <v>221.40700000000001</v>
+      </c>
+      <c r="CN10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO10" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP10" s="1">
-        <v>159.00899999999999</v>
+        <v>41</v>
       </c>
       <c r="CQ10" s="1">
-        <v>221.40700000000001</v>
-      </c>
-      <c r="CR10" s="1">
-        <v>291.38200000000001</v>
-      </c>
-      <c r="CS10" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT10" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU10" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV10" s="1">
         <v>0.63458700000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -7277,7 +7470,7 @@
         <v>159.386</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N11" s="1">
         <v>190.821</v>
@@ -7409,139 +7602,124 @@
         <v>192.27199999999999</v>
       </c>
       <c r="BE11" s="1">
-        <v>346.2</v>
+        <v>185.32900000000001</v>
       </c>
       <c r="BF11" s="1">
-        <v>185.32900000000001</v>
+        <v>158.76499999999999</v>
       </c>
       <c r="BG11" s="1">
-        <v>158.76499999999999</v>
+        <v>195.57499999999999</v>
       </c>
       <c r="BH11" s="1">
-        <v>614.58000000000004</v>
+        <v>236.429</v>
       </c>
       <c r="BI11" s="1">
-        <v>195.57499999999999</v>
+        <v>220.357</v>
       </c>
       <c r="BJ11" s="1">
-        <v>236.429</v>
+        <v>185.71899999999999</v>
       </c>
       <c r="BK11" s="1">
-        <v>220.357</v>
+        <v>202.95099999999999</v>
       </c>
       <c r="BL11" s="1">
-        <v>185.71899999999999</v>
+        <v>185.346</v>
       </c>
       <c r="BM11" s="1">
-        <v>202.95099999999999</v>
+        <v>185.328</v>
       </c>
       <c r="BN11" s="1">
-        <v>185.346</v>
+        <v>350.00700000000001</v>
       </c>
       <c r="BO11" s="1">
-        <v>1097.8</v>
+        <v>179.58600000000001</v>
       </c>
       <c r="BP11" s="1">
+        <v>158.017</v>
+      </c>
+      <c r="BQ11" s="1">
+        <v>178.99100000000001</v>
+      </c>
+      <c r="BR11" s="1">
+        <v>171.16399999999999</v>
+      </c>
+      <c r="BS11" s="1">
+        <v>198.50700000000001</v>
+      </c>
+      <c r="BT11" s="1">
+        <v>95.000100000000003</v>
+      </c>
+      <c r="BU11" s="1">
+        <v>192.05500000000001</v>
+      </c>
+      <c r="BV11" s="1">
+        <v>181.923</v>
+      </c>
+      <c r="BW11" s="1">
+        <v>159.12700000000001</v>
+      </c>
+      <c r="BX11" s="1">
+        <v>185.334</v>
+      </c>
+      <c r="BY11" s="1">
+        <v>171.27799999999999</v>
+      </c>
+      <c r="BZ11" s="1">
+        <v>158.875</v>
+      </c>
+      <c r="CA11" s="1">
+        <v>158.32</v>
+      </c>
+      <c r="CB11" s="1">
         <v>185.328</v>
       </c>
-      <c r="BQ11" s="1">
-        <v>350.00700000000001</v>
-      </c>
-      <c r="BR11" s="1">
-        <v>179.58600000000001</v>
-      </c>
-      <c r="BS11" s="1">
-        <v>158.017</v>
-      </c>
-      <c r="BT11" s="1">
-        <v>178.99100000000001</v>
-      </c>
-      <c r="BU11" s="1">
-        <v>171.16399999999999</v>
-      </c>
-      <c r="BV11" s="1">
-        <v>198.50700000000001</v>
-      </c>
-      <c r="BW11" s="1">
-        <v>95.000100000000003</v>
-      </c>
-      <c r="BX11" s="1">
-        <v>192.05500000000001</v>
-      </c>
-      <c r="BY11" s="1">
-        <v>181.923</v>
-      </c>
-      <c r="BZ11" s="1">
-        <v>169.98</v>
-      </c>
-      <c r="CA11" s="1">
-        <v>159.12700000000001</v>
-      </c>
-      <c r="CB11" s="1">
-        <v>185.334</v>
-      </c>
       <c r="CC11" s="1">
-        <v>171.27799999999999</v>
+        <v>157.815</v>
       </c>
       <c r="CD11" s="1">
-        <v>158.875</v>
+        <v>158.565</v>
       </c>
       <c r="CE11" s="1">
-        <v>158.32</v>
+        <v>159</v>
       </c>
       <c r="CF11" s="1">
-        <v>185.328</v>
+        <v>158.80000000000001</v>
       </c>
       <c r="CG11" s="1">
-        <v>157.815</v>
+        <v>6.00678</v>
       </c>
       <c r="CH11" s="1">
-        <v>158.565</v>
+        <v>158.494</v>
       </c>
       <c r="CI11" s="1">
-        <v>159</v>
+        <v>240.91900000000001</v>
       </c>
       <c r="CJ11" s="1">
-        <v>158.80000000000001</v>
+        <v>160</v>
       </c>
       <c r="CK11" s="1">
-        <v>6.00678</v>
+        <v>175.923</v>
       </c>
       <c r="CL11" s="1">
-        <v>158.494</v>
+        <v>159.411</v>
       </c>
       <c r="CM11" s="1">
-        <v>240.91900000000001</v>
-      </c>
-      <c r="CN11" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO11" s="1">
-        <v>175.923</v>
+        <v>229.06700000000001</v>
+      </c>
+      <c r="CN11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO11" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP11" s="1">
-        <v>159.411</v>
+        <v>41</v>
       </c>
       <c r="CQ11" s="1">
-        <v>229.06700000000001</v>
-      </c>
-      <c r="CR11" s="1">
-        <v>316.03300000000002</v>
-      </c>
-      <c r="CS11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU11" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV11" s="1">
         <v>0.63396799999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -7579,7 +7757,7 @@
         <v>161.268</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N12" s="1">
         <v>200.52099999999999</v>
@@ -7711,139 +7889,124 @@
         <v>205.18</v>
       </c>
       <c r="BE12" s="1">
-        <v>424.78500000000003</v>
+        <v>193.696</v>
       </c>
       <c r="BF12" s="1">
-        <v>193.696</v>
+        <v>159.38200000000001</v>
       </c>
       <c r="BG12" s="1">
-        <v>159.38200000000001</v>
+        <v>206.27199999999999</v>
       </c>
       <c r="BH12" s="1">
-        <v>701.06299999999999</v>
+        <v>259.315</v>
       </c>
       <c r="BI12" s="1">
-        <v>206.27199999999999</v>
+        <v>241.28399999999999</v>
       </c>
       <c r="BJ12" s="1">
-        <v>259.315</v>
+        <v>194.14699999999999</v>
       </c>
       <c r="BK12" s="1">
-        <v>241.28399999999999</v>
+        <v>215.76300000000001</v>
       </c>
       <c r="BL12" s="1">
-        <v>194.14699999999999</v>
+        <v>193.715</v>
       </c>
       <c r="BM12" s="1">
-        <v>215.76300000000001</v>
+        <v>193.69399999999999</v>
       </c>
       <c r="BN12" s="1">
-        <v>193.715</v>
+        <v>396.66699999999997</v>
       </c>
       <c r="BO12" s="1">
-        <v>1235.74</v>
+        <v>186.40899999999999</v>
       </c>
       <c r="BP12" s="1">
+        <v>159.00700000000001</v>
+      </c>
+      <c r="BQ12" s="1">
+        <v>185.75399999999999</v>
+      </c>
+      <c r="BR12" s="1">
+        <v>176.10900000000001</v>
+      </c>
+      <c r="BS12" s="1">
+        <v>209.78800000000001</v>
+      </c>
+      <c r="BT12" s="1">
+        <v>95.000399999999999</v>
+      </c>
+      <c r="BU12" s="1">
+        <v>202.19800000000001</v>
+      </c>
+      <c r="BV12" s="1">
+        <v>189.77</v>
+      </c>
+      <c r="BW12" s="1">
+        <v>160.72800000000001</v>
+      </c>
+      <c r="BX12" s="1">
+        <v>193.70099999999999</v>
+      </c>
+      <c r="BY12" s="1">
+        <v>171.64</v>
+      </c>
+      <c r="BZ12" s="1">
+        <v>160.148</v>
+      </c>
+      <c r="CA12" s="1">
+        <v>159.15799999999999</v>
+      </c>
+      <c r="CB12" s="1">
         <v>193.69399999999999</v>
       </c>
-      <c r="BQ12" s="1">
-        <v>396.66699999999997</v>
-      </c>
-      <c r="BR12" s="1">
-        <v>186.40899999999999</v>
-      </c>
-      <c r="BS12" s="1">
-        <v>159.00700000000001</v>
-      </c>
-      <c r="BT12" s="1">
-        <v>185.75399999999999</v>
-      </c>
-      <c r="BU12" s="1">
-        <v>176.10900000000001</v>
-      </c>
-      <c r="BV12" s="1">
-        <v>209.78800000000001</v>
-      </c>
-      <c r="BW12" s="1">
-        <v>95.000399999999999</v>
-      </c>
-      <c r="BX12" s="1">
-        <v>202.19800000000001</v>
-      </c>
-      <c r="BY12" s="1">
-        <v>189.77</v>
-      </c>
-      <c r="BZ12" s="1">
-        <v>171.61699999999999</v>
-      </c>
-      <c r="CA12" s="1">
-        <v>160.72800000000001</v>
-      </c>
-      <c r="CB12" s="1">
-        <v>193.70099999999999</v>
-      </c>
       <c r="CC12" s="1">
-        <v>171.64</v>
+        <v>158.90199999999999</v>
       </c>
       <c r="CD12" s="1">
-        <v>160.148</v>
+        <v>159.28200000000001</v>
       </c>
       <c r="CE12" s="1">
-        <v>159.15799999999999</v>
+        <v>159.51499999999999</v>
       </c>
       <c r="CF12" s="1">
-        <v>193.69399999999999</v>
+        <v>159.4</v>
       </c>
       <c r="CG12" s="1">
-        <v>158.90199999999999</v>
+        <v>6.0576800000000004</v>
       </c>
       <c r="CH12" s="1">
-        <v>159.28200000000001</v>
+        <v>159.24700000000001</v>
       </c>
       <c r="CI12" s="1">
-        <v>159.51499999999999</v>
+        <v>273.52</v>
       </c>
       <c r="CJ12" s="1">
-        <v>159.4</v>
+        <v>160</v>
       </c>
       <c r="CK12" s="1">
-        <v>6.0576800000000004</v>
+        <v>181.91399999999999</v>
       </c>
       <c r="CL12" s="1">
-        <v>159.24700000000001</v>
+        <v>160.01499999999999</v>
       </c>
       <c r="CM12" s="1">
-        <v>273.52</v>
-      </c>
-      <c r="CN12" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO12" s="1">
-        <v>181.91399999999999</v>
+        <v>247.482</v>
+      </c>
+      <c r="CN12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO12" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP12" s="1">
-        <v>160.01499999999999</v>
+        <v>41</v>
       </c>
       <c r="CQ12" s="1">
-        <v>247.482</v>
-      </c>
-      <c r="CR12" s="1">
-        <v>384.17099999999999</v>
-      </c>
-      <c r="CS12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT12" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU12" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV12" s="1">
         <v>0.63304199999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -7881,7 +8044,7 @@
         <v>161.85400000000001</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N13" s="1">
         <v>203.50899999999999</v>
@@ -8013,139 +8176,124 @@
         <v>209.32400000000001</v>
       </c>
       <c r="BE13" s="1">
-        <v>453.69799999999998</v>
+        <v>196.25299999999999</v>
       </c>
       <c r="BF13" s="1">
-        <v>196.25299999999999</v>
+        <v>159.506</v>
       </c>
       <c r="BG13" s="1">
-        <v>159.506</v>
+        <v>209.565</v>
       </c>
       <c r="BH13" s="1">
-        <v>728.904</v>
+        <v>266.70699999999999</v>
       </c>
       <c r="BI13" s="1">
-        <v>209.565</v>
+        <v>248.02099999999999</v>
       </c>
       <c r="BJ13" s="1">
-        <v>266.70699999999999</v>
+        <v>196.72300000000001</v>
       </c>
       <c r="BK13" s="1">
-        <v>248.02099999999999</v>
+        <v>219.767</v>
       </c>
       <c r="BL13" s="1">
-        <v>196.72300000000001</v>
+        <v>196.27199999999999</v>
       </c>
       <c r="BM13" s="1">
-        <v>219.767</v>
+        <v>196.251</v>
       </c>
       <c r="BN13" s="1">
-        <v>196.27199999999999</v>
+        <v>411.68900000000002</v>
       </c>
       <c r="BO13" s="1">
-        <v>1278.6199999999999</v>
+        <v>188.464</v>
       </c>
       <c r="BP13" s="1">
+        <v>159.20500000000001</v>
+      </c>
+      <c r="BQ13" s="1">
+        <v>187.80199999999999</v>
+      </c>
+      <c r="BR13" s="1">
+        <v>177.58099999999999</v>
+      </c>
+      <c r="BS13" s="1">
+        <v>213.26</v>
+      </c>
+      <c r="BT13" s="1">
+        <v>95.000399999999999</v>
+      </c>
+      <c r="BU13" s="1">
+        <v>205.334</v>
+      </c>
+      <c r="BV13" s="1">
+        <v>192.17099999999999</v>
+      </c>
+      <c r="BW13" s="1">
+        <v>161.19399999999999</v>
+      </c>
+      <c r="BX13" s="1">
+        <v>196.25800000000001</v>
+      </c>
+      <c r="BY13" s="1">
+        <v>171.71199999999999</v>
+      </c>
+      <c r="BZ13" s="1">
+        <v>160.47200000000001</v>
+      </c>
+      <c r="CA13" s="1">
+        <v>159.32599999999999</v>
+      </c>
+      <c r="CB13" s="1">
         <v>196.251</v>
       </c>
-      <c r="BQ13" s="1">
-        <v>411.68900000000002</v>
-      </c>
-      <c r="BR13" s="1">
-        <v>188.464</v>
-      </c>
-      <c r="BS13" s="1">
-        <v>159.20500000000001</v>
-      </c>
-      <c r="BT13" s="1">
-        <v>187.80199999999999</v>
-      </c>
-      <c r="BU13" s="1">
-        <v>177.58099999999999</v>
-      </c>
-      <c r="BV13" s="1">
-        <v>213.26</v>
-      </c>
-      <c r="BW13" s="1">
-        <v>95.000399999999999</v>
-      </c>
-      <c r="BX13" s="1">
-        <v>205.334</v>
-      </c>
-      <c r="BY13" s="1">
-        <v>192.17099999999999</v>
-      </c>
-      <c r="BZ13" s="1">
-        <v>172.001</v>
-      </c>
-      <c r="CA13" s="1">
-        <v>161.19399999999999</v>
-      </c>
-      <c r="CB13" s="1">
-        <v>196.25800000000001</v>
-      </c>
       <c r="CC13" s="1">
-        <v>171.71199999999999</v>
+        <v>159.12100000000001</v>
       </c>
       <c r="CD13" s="1">
-        <v>160.47200000000001</v>
+        <v>159.42500000000001</v>
       </c>
       <c r="CE13" s="1">
-        <v>159.32599999999999</v>
+        <v>159.61500000000001</v>
       </c>
       <c r="CF13" s="1">
-        <v>196.251</v>
+        <v>159.52000000000001</v>
       </c>
       <c r="CG13" s="1">
-        <v>159.12100000000001</v>
+        <v>6.0678700000000001</v>
       </c>
       <c r="CH13" s="1">
-        <v>159.42500000000001</v>
+        <v>159.398</v>
       </c>
       <c r="CI13" s="1">
-        <v>159.61500000000001</v>
+        <v>284.30599999999998</v>
       </c>
       <c r="CJ13" s="1">
-        <v>159.52000000000001</v>
+        <v>160</v>
       </c>
       <c r="CK13" s="1">
-        <v>6.0678700000000001</v>
+        <v>183.709</v>
       </c>
       <c r="CL13" s="1">
-        <v>159.398</v>
+        <v>160.13499999999999</v>
       </c>
       <c r="CM13" s="1">
-        <v>284.30599999999998</v>
-      </c>
-      <c r="CN13" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO13" s="1">
-        <v>183.709</v>
+        <v>253.40199999999999</v>
+      </c>
+      <c r="CN13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO13" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP13" s="1">
-        <v>160.13499999999999</v>
+        <v>41</v>
       </c>
       <c r="CQ13" s="1">
-        <v>253.40199999999999</v>
-      </c>
-      <c r="CR13" s="1">
-        <v>409.05700000000002</v>
-      </c>
-      <c r="CS13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU13" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV13" s="1">
         <v>0.63285800000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -8183,7 +8331,7 @@
         <v>163.648</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N14" s="1">
         <v>212.43899999999999</v>
@@ -8315,139 +8463,124 @@
         <v>222.17599999999999</v>
       </c>
       <c r="BE14" s="1">
-        <v>556.66</v>
+        <v>203.83500000000001</v>
       </c>
       <c r="BF14" s="1">
-        <v>203.83500000000001</v>
+        <v>159.75299999999999</v>
       </c>
       <c r="BG14" s="1">
-        <v>159.75299999999999</v>
+        <v>219.39099999999999</v>
       </c>
       <c r="BH14" s="1">
-        <v>815.38699999999994</v>
+        <v>289.76400000000001</v>
       </c>
       <c r="BI14" s="1">
-        <v>219.39099999999999</v>
+        <v>268.94799999999998</v>
       </c>
       <c r="BJ14" s="1">
-        <v>289.76400000000001</v>
+        <v>204.36600000000001</v>
       </c>
       <c r="BK14" s="1">
-        <v>268.94799999999998</v>
+        <v>231.886</v>
       </c>
       <c r="BL14" s="1">
-        <v>204.36600000000001</v>
+        <v>203.857</v>
       </c>
       <c r="BM14" s="1">
-        <v>231.886</v>
+        <v>203.83199999999999</v>
       </c>
       <c r="BN14" s="1">
-        <v>203.857</v>
+        <v>458.34899999999999</v>
       </c>
       <c r="BO14" s="1">
-        <v>1407.83</v>
+        <v>194.47900000000001</v>
       </c>
       <c r="BP14" s="1">
+        <v>159.602</v>
+      </c>
+      <c r="BQ14" s="1">
+        <v>193.82599999999999</v>
+      </c>
+      <c r="BR14" s="1">
+        <v>181.846</v>
+      </c>
+      <c r="BS14" s="1">
+        <v>223.62100000000001</v>
+      </c>
+      <c r="BT14" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="BU14" s="1">
+        <v>214.733</v>
+      </c>
+      <c r="BV14" s="1">
+        <v>199.30500000000001</v>
+      </c>
+      <c r="BW14" s="1">
+        <v>162.523</v>
+      </c>
+      <c r="BX14" s="1">
+        <v>203.84</v>
+      </c>
+      <c r="BY14" s="1">
+        <v>171.85599999999999</v>
+      </c>
+      <c r="BZ14" s="1">
+        <v>161.27699999999999</v>
+      </c>
+      <c r="CA14" s="1">
+        <v>159.66300000000001</v>
+      </c>
+      <c r="CB14" s="1">
         <v>203.83199999999999</v>
       </c>
-      <c r="BQ14" s="1">
-        <v>458.34899999999999</v>
-      </c>
-      <c r="BR14" s="1">
-        <v>194.47900000000001</v>
-      </c>
-      <c r="BS14" s="1">
-        <v>159.602</v>
-      </c>
-      <c r="BT14" s="1">
-        <v>193.82599999999999</v>
-      </c>
-      <c r="BU14" s="1">
-        <v>181.846</v>
-      </c>
-      <c r="BV14" s="1">
-        <v>223.62100000000001</v>
-      </c>
-      <c r="BW14" s="1">
-        <v>95.000500000000002</v>
-      </c>
-      <c r="BX14" s="1">
-        <v>214.733</v>
-      </c>
-      <c r="BY14" s="1">
-        <v>199.30500000000001</v>
-      </c>
-      <c r="BZ14" s="1">
-        <v>172.88499999999999</v>
-      </c>
-      <c r="CA14" s="1">
-        <v>162.523</v>
-      </c>
-      <c r="CB14" s="1">
-        <v>203.84</v>
-      </c>
       <c r="CC14" s="1">
-        <v>171.85599999999999</v>
+        <v>159.56</v>
       </c>
       <c r="CD14" s="1">
-        <v>161.27699999999999</v>
+        <v>159.71199999999999</v>
       </c>
       <c r="CE14" s="1">
-        <v>159.66300000000001</v>
+        <v>159.81299999999999</v>
       </c>
       <c r="CF14" s="1">
-        <v>203.83199999999999</v>
+        <v>159.76</v>
       </c>
       <c r="CG14" s="1">
-        <v>159.56</v>
+        <v>6.0882500000000004</v>
       </c>
       <c r="CH14" s="1">
-        <v>159.71199999999999</v>
+        <v>159.69900000000001</v>
       </c>
       <c r="CI14" s="1">
-        <v>159.81299999999999</v>
+        <v>318.60000000000002</v>
       </c>
       <c r="CJ14" s="1">
-        <v>159.76</v>
+        <v>160</v>
       </c>
       <c r="CK14" s="1">
-        <v>6.0882500000000004</v>
+        <v>188.93600000000001</v>
       </c>
       <c r="CL14" s="1">
-        <v>159.69900000000001</v>
+        <v>160.376</v>
       </c>
       <c r="CM14" s="1">
-        <v>318.60000000000002</v>
-      </c>
-      <c r="CN14" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO14" s="1">
-        <v>188.93600000000001</v>
+        <v>271.77600000000001</v>
+      </c>
+      <c r="CN14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO14" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP14" s="1">
-        <v>160.376</v>
+        <v>41</v>
       </c>
       <c r="CQ14" s="1">
-        <v>271.77600000000001</v>
-      </c>
-      <c r="CR14" s="1">
-        <v>497.04</v>
-      </c>
-      <c r="CS14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU14" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV14" s="1">
         <v>0.63248899999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -8485,7 +8618,7 @@
         <v>164.68700000000001</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N15" s="1">
         <v>217.44399999999999</v>
@@ -8617,139 +8750,124 @@
         <v>229.685</v>
       </c>
       <c r="BE15" s="1">
-        <v>627.39800000000002</v>
+        <v>208.047</v>
       </c>
       <c r="BF15" s="1">
-        <v>208.047</v>
+        <v>159.83500000000001</v>
       </c>
       <c r="BG15" s="1">
-        <v>159.83500000000001</v>
+        <v>224.887</v>
       </c>
       <c r="BH15" s="1">
-        <v>865.976</v>
+        <v>303.32</v>
       </c>
       <c r="BI15" s="1">
-        <v>224.887</v>
+        <v>281.19</v>
       </c>
       <c r="BJ15" s="1">
-        <v>303.32</v>
+        <v>208.614</v>
       </c>
       <c r="BK15" s="1">
-        <v>281.19</v>
+        <v>238.779</v>
       </c>
       <c r="BL15" s="1">
-        <v>208.614</v>
+        <v>208.071</v>
       </c>
       <c r="BM15" s="1">
-        <v>238.779</v>
+        <v>208.04400000000001</v>
       </c>
       <c r="BN15" s="1">
-        <v>208.071</v>
+        <v>485.64400000000001</v>
       </c>
       <c r="BO15" s="1">
-        <v>1480.91</v>
+        <v>197.76900000000001</v>
       </c>
       <c r="BP15" s="1">
+        <v>159.73500000000001</v>
+      </c>
+      <c r="BQ15" s="1">
+        <v>197.143</v>
+      </c>
+      <c r="BR15" s="1">
+        <v>184.154</v>
+      </c>
+      <c r="BS15" s="1">
+        <v>229.41499999999999</v>
+      </c>
+      <c r="BT15" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="BU15" s="1">
+        <v>220.02099999999999</v>
+      </c>
+      <c r="BV15" s="1">
+        <v>203.274</v>
+      </c>
+      <c r="BW15" s="1">
+        <v>163.23400000000001</v>
+      </c>
+      <c r="BX15" s="1">
+        <v>208.05199999999999</v>
+      </c>
+      <c r="BY15" s="1">
+        <v>171.904</v>
+      </c>
+      <c r="BZ15" s="1">
+        <v>161.63300000000001</v>
+      </c>
+      <c r="CA15" s="1">
+        <v>159.77500000000001</v>
+      </c>
+      <c r="CB15" s="1">
         <v>208.04400000000001</v>
       </c>
-      <c r="BQ15" s="1">
-        <v>485.64400000000001</v>
-      </c>
-      <c r="BR15" s="1">
-        <v>197.76900000000001</v>
-      </c>
-      <c r="BS15" s="1">
-        <v>159.73500000000001</v>
-      </c>
-      <c r="BT15" s="1">
-        <v>197.143</v>
-      </c>
-      <c r="BU15" s="1">
-        <v>184.154</v>
-      </c>
-      <c r="BV15" s="1">
-        <v>229.41499999999999</v>
-      </c>
-      <c r="BW15" s="1">
-        <v>95.000500000000002</v>
-      </c>
-      <c r="BX15" s="1">
-        <v>220.02099999999999</v>
-      </c>
-      <c r="BY15" s="1">
-        <v>203.274</v>
-      </c>
-      <c r="BZ15" s="1">
-        <v>173.24100000000001</v>
-      </c>
-      <c r="CA15" s="1">
-        <v>163.23400000000001</v>
-      </c>
-      <c r="CB15" s="1">
-        <v>208.05199999999999</v>
-      </c>
       <c r="CC15" s="1">
-        <v>171.904</v>
+        <v>159.70599999999999</v>
       </c>
       <c r="CD15" s="1">
-        <v>161.63300000000001</v>
+        <v>159.80799999999999</v>
       </c>
       <c r="CE15" s="1">
-        <v>159.77500000000001</v>
+        <v>159.87700000000001</v>
       </c>
       <c r="CF15" s="1">
-        <v>208.04400000000001</v>
+        <v>159.84</v>
       </c>
       <c r="CG15" s="1">
-        <v>159.70599999999999</v>
+        <v>6.0950499999999996</v>
       </c>
       <c r="CH15" s="1">
-        <v>159.80799999999999</v>
+        <v>159.79900000000001</v>
       </c>
       <c r="CI15" s="1">
-        <v>159.87700000000001</v>
+        <v>339.16199999999998</v>
       </c>
       <c r="CJ15" s="1">
-        <v>159.84</v>
+        <v>160</v>
       </c>
       <c r="CK15" s="1">
-        <v>6.0950499999999996</v>
+        <v>191.78100000000001</v>
       </c>
       <c r="CL15" s="1">
-        <v>159.79900000000001</v>
+        <v>160.45699999999999</v>
       </c>
       <c r="CM15" s="1">
-        <v>339.16199999999998</v>
-      </c>
-      <c r="CN15" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO15" s="1">
-        <v>191.78100000000001</v>
+        <v>282.51799999999997</v>
+      </c>
+      <c r="CN15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO15" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP15" s="1">
-        <v>160.45699999999999</v>
+        <v>41</v>
       </c>
       <c r="CQ15" s="1">
-        <v>282.51799999999997</v>
-      </c>
-      <c r="CR15" s="1">
-        <v>556.99699999999996</v>
-      </c>
-      <c r="CS15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU15" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV15" s="1">
         <v>0.63236599999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:95" x14ac:dyDescent="0.6">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -8787,7 +8905,7 @@
         <v>165.422</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="N16" s="1">
         <v>220.90700000000001</v>
@@ -8919,135 +9037,120 @@
         <v>235.01</v>
       </c>
       <c r="BE16" s="1">
-        <v>682.97199999999998</v>
+        <v>210.946</v>
       </c>
       <c r="BF16" s="1">
-        <v>210.946</v>
+        <v>159.876</v>
       </c>
       <c r="BG16" s="1">
-        <v>159.876</v>
+        <v>228.685</v>
       </c>
       <c r="BH16" s="1">
-        <v>901.87</v>
+        <v>312.971</v>
       </c>
       <c r="BI16" s="1">
-        <v>228.685</v>
+        <v>289.875</v>
       </c>
       <c r="BJ16" s="1">
-        <v>312.971</v>
+        <v>211.53899999999999</v>
       </c>
       <c r="BK16" s="1">
-        <v>289.875</v>
+        <v>243.59100000000001</v>
       </c>
       <c r="BL16" s="1">
-        <v>211.53899999999999</v>
+        <v>210.97200000000001</v>
       </c>
       <c r="BM16" s="1">
-        <v>243.59100000000001</v>
+        <v>210.94399999999999</v>
       </c>
       <c r="BN16" s="1">
-        <v>210.97200000000001</v>
+        <v>505.01</v>
       </c>
       <c r="BO16" s="1">
-        <v>1531.77</v>
+        <v>200.012</v>
       </c>
       <c r="BP16" s="1">
+        <v>159.80099999999999</v>
+      </c>
+      <c r="BQ16" s="1">
+        <v>199.41499999999999</v>
+      </c>
+      <c r="BR16" s="1">
+        <v>185.71799999999999</v>
+      </c>
+      <c r="BS16" s="1">
+        <v>233.41900000000001</v>
+      </c>
+      <c r="BT16" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="BU16" s="1">
+        <v>223.68799999999999</v>
+      </c>
+      <c r="BV16" s="1">
+        <v>206.00899999999999</v>
+      </c>
+      <c r="BW16" s="1">
+        <v>163.71299999999999</v>
+      </c>
+      <c r="BX16" s="1">
+        <v>210.952</v>
+      </c>
+      <c r="BY16" s="1">
+        <v>171.928</v>
+      </c>
+      <c r="BZ16" s="1">
+        <v>161.846</v>
+      </c>
+      <c r="CA16" s="1">
+        <v>159.83099999999999</v>
+      </c>
+      <c r="CB16" s="1">
         <v>210.94399999999999</v>
       </c>
-      <c r="BQ16" s="1">
-        <v>505.01</v>
-      </c>
-      <c r="BR16" s="1">
-        <v>200.012</v>
-      </c>
-      <c r="BS16" s="1">
-        <v>159.80099999999999</v>
-      </c>
-      <c r="BT16" s="1">
-        <v>199.41499999999999</v>
-      </c>
-      <c r="BU16" s="1">
-        <v>185.71799999999999</v>
-      </c>
-      <c r="BV16" s="1">
-        <v>233.41900000000001</v>
-      </c>
-      <c r="BW16" s="1">
-        <v>95.000500000000002</v>
-      </c>
-      <c r="BX16" s="1">
-        <v>223.68799999999999</v>
-      </c>
-      <c r="BY16" s="1">
-        <v>206.00899999999999</v>
-      </c>
-      <c r="BZ16" s="1">
-        <v>173.441</v>
-      </c>
-      <c r="CA16" s="1">
-        <v>163.71299999999999</v>
-      </c>
-      <c r="CB16" s="1">
-        <v>210.952</v>
-      </c>
       <c r="CC16" s="1">
-        <v>171.928</v>
+        <v>159.78</v>
       </c>
       <c r="CD16" s="1">
-        <v>161.846</v>
+        <v>159.85599999999999</v>
       </c>
       <c r="CE16" s="1">
-        <v>159.83099999999999</v>
+        <v>159.90899999999999</v>
       </c>
       <c r="CF16" s="1">
-        <v>210.94399999999999</v>
+        <v>159.88</v>
       </c>
       <c r="CG16" s="1">
-        <v>159.78</v>
+        <v>6.0984400000000001</v>
       </c>
       <c r="CH16" s="1">
-        <v>159.85599999999999</v>
+        <v>159.84899999999999</v>
       </c>
       <c r="CI16" s="1">
-        <v>159.90899999999999</v>
+        <v>353.95299999999997</v>
       </c>
       <c r="CJ16" s="1">
-        <v>159.88</v>
+        <v>160</v>
       </c>
       <c r="CK16" s="1">
-        <v>6.0984400000000001</v>
+        <v>193.71600000000001</v>
       </c>
       <c r="CL16" s="1">
-        <v>159.84899999999999</v>
+        <v>160.49700000000001</v>
       </c>
       <c r="CM16" s="1">
-        <v>353.95299999999997</v>
-      </c>
-      <c r="CN16" s="1">
-        <v>160</v>
-      </c>
-      <c r="CO16" s="1">
-        <v>193.71600000000001</v>
+        <v>290.13799999999998</v>
+      </c>
+      <c r="CN16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CO16" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="CP16" s="1">
-        <v>160.49700000000001</v>
+        <v>41</v>
       </c>
       <c r="CQ16" s="1">
-        <v>290.13799999999998</v>
-      </c>
-      <c r="CR16" s="1">
-        <v>603.86300000000006</v>
-      </c>
-      <c r="CS16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CT16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CU16" s="1">
-        <v>41</v>
-      </c>
-      <c r="CV16" s="1">
         <v>0.63230500000000001</v>
       </c>
     </row>

--- a/tool/PMP/old/PMP_Sample.xlsx
+++ b/tool/PMP/old/PMP_Sample.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29615"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874BAAC2-B1C1-461C-A058-7692153F291F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C883A926-EBD6-4A8E-A5DA-77A586E5BE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
   </bookViews>
   <sheets>
     <sheet name="Rain" sheetId="1" r:id="rId1"/>
     <sheet name="PMP" sheetId="2" r:id="rId2"/>
     <sheet name="25020230" sheetId="3" r:id="rId3"/>
+    <sheet name="BestFil" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,11 +40,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="145">
   <si>
     <t>Year / Station</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>semicircular</t>
+  </si>
+  <si>
+    <t>empirical_dist</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>25020230_1969_2009</t>
+  </si>
+  <si>
     <t>Tr</t>
   </si>
   <si>
@@ -59,6 +82,399 @@
   </si>
   <si>
     <t>R.HydroTools-Anglit</t>
+  </si>
+  <si>
+    <t>p_dist</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>deltao</t>
+  </si>
+  <si>
+    <t>eval</t>
+  </si>
+  <si>
+    <t>fit</t>
+  </si>
+  <si>
+    <t>loc</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>shape1</t>
+  </si>
+  <si>
+    <t>shape2</t>
+  </si>
+  <si>
+    <t>shape3</t>
+  </si>
+  <si>
+    <t>best_fit</t>
+  </si>
+  <si>
+    <t>best_fit_sort</t>
+  </si>
+  <si>
+    <t>emp_blom</t>
+  </si>
+  <si>
+    <t>Δo &gt; Δ</t>
+  </si>
+  <si>
+    <t>emp_california</t>
+  </si>
+  <si>
+    <t>emp_hazen</t>
+  </si>
+  <si>
+    <t>emp_weibull</t>
+  </si>
+  <si>
+    <t>emp_beard</t>
+  </si>
+  <si>
+    <t>emp_chegodayev</t>
+  </si>
+  <si>
+    <t>emp_tukey</t>
+  </si>
+  <si>
+    <t>emp_gringorten</t>
+  </si>
+  <si>
+    <t>emp_jenkinson</t>
+  </si>
+  <si>
+    <t>emp_cunnane</t>
+  </si>
+  <si>
+    <t>emp_adamowski</t>
+  </si>
+  <si>
+    <t>tr</t>
+  </si>
+  <si>
+    <t>prob_l</t>
+  </si>
+  <si>
+    <t>prob_g</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>anglit</t>
+  </si>
+  <si>
+    <t>arcsine</t>
+  </si>
+  <si>
+    <t>argus</t>
+  </si>
+  <si>
+    <t>betaprime</t>
+  </si>
+  <si>
+    <t>bradford</t>
+  </si>
+  <si>
+    <t>burr</t>
+  </si>
+  <si>
+    <t>burr12</t>
+  </si>
+  <si>
+    <t>cauchy</t>
+  </si>
+  <si>
+    <t>chi2</t>
+  </si>
+  <si>
+    <t>cosine</t>
+  </si>
+  <si>
+    <t>crystalball</t>
+  </si>
+  <si>
+    <t>dgamma</t>
+  </si>
+  <si>
+    <t>erlang</t>
+  </si>
+  <si>
+    <t>expon</t>
+  </si>
+  <si>
+    <t>exponnorm</t>
+  </si>
+  <si>
+    <t>exponpow</t>
+  </si>
+  <si>
+    <t>exponweib</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>fatiguelife</t>
+  </si>
+  <si>
+    <t>fisk</t>
+  </si>
+  <si>
+    <t>foldcauchy</t>
+  </si>
+  <si>
+    <t>foldnorm</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>gausshyper</t>
+  </si>
+  <si>
+    <t>genexpon</t>
+  </si>
+  <si>
+    <t>genextreme</t>
+  </si>
+  <si>
+    <t>gengamma</t>
+  </si>
+  <si>
+    <t>genhalflogistic</t>
+  </si>
+  <si>
+    <t>genhyperbolic</t>
+  </si>
+  <si>
+    <t>geninvgauss</t>
+  </si>
+  <si>
+    <t>genlogistic</t>
+  </si>
+  <si>
+    <t>gennorm</t>
+  </si>
+  <si>
+    <t>genpareto</t>
+  </si>
+  <si>
+    <t>gibrat</t>
+  </si>
+  <si>
+    <t>gompertz</t>
+  </si>
+  <si>
+    <t>gumbel_l</t>
+  </si>
+  <si>
+    <t>gumbel_r</t>
+  </si>
+  <si>
+    <t>halfcauchy</t>
+  </si>
+  <si>
+    <t>halfgennorm</t>
+  </si>
+  <si>
+    <t>halflogistic</t>
+  </si>
+  <si>
+    <t>halfnorm</t>
+  </si>
+  <si>
+    <t>hypsecant</t>
+  </si>
+  <si>
+    <t>invgamma</t>
+  </si>
+  <si>
+    <t>invgauss</t>
+  </si>
+  <si>
+    <t>invweibull</t>
+  </si>
+  <si>
+    <t>johnsonsb</t>
+  </si>
+  <si>
+    <t>johnsonsu</t>
+  </si>
+  <si>
+    <t>kappa3</t>
+  </si>
+  <si>
+    <t>kappa4</t>
+  </si>
+  <si>
+    <t>ksone</t>
+  </si>
+  <si>
+    <t>kstwobign</t>
+  </si>
+  <si>
+    <t>laplace</t>
+  </si>
+  <si>
+    <t>laplace_asymmetric</t>
+  </si>
+  <si>
+    <t>levy</t>
+  </si>
+  <si>
+    <t>levy_l</t>
+  </si>
+  <si>
+    <t>levy_stable</t>
+  </si>
+  <si>
+    <t>loggamma</t>
+  </si>
+  <si>
+    <t>logistic</t>
+  </si>
+  <si>
+    <t>loglaplace</t>
+  </si>
+  <si>
+    <t>lognorm</t>
+  </si>
+  <si>
+    <t>loguniform</t>
+  </si>
+  <si>
+    <t>lomax</t>
+  </si>
+  <si>
+    <t>maxwell</t>
+  </si>
+  <si>
+    <t>mielke</t>
+  </si>
+  <si>
+    <t>moyal</t>
+  </si>
+  <si>
+    <t>nakagami</t>
+  </si>
+  <si>
+    <t>ncf</t>
+  </si>
+  <si>
+    <t>nct</t>
+  </si>
+  <si>
+    <t>ncx2</t>
+  </si>
+  <si>
+    <t>norm</t>
+  </si>
+  <si>
+    <t>norminvgauss</t>
+  </si>
+  <si>
+    <t>pareto</t>
+  </si>
+  <si>
+    <t>pearson3</t>
+  </si>
+  <si>
+    <t>powerlaw</t>
+  </si>
+  <si>
+    <t>powerlognorm</t>
+  </si>
+  <si>
+    <t>powernorm</t>
+  </si>
+  <si>
+    <t>rayleigh</t>
+  </si>
+  <si>
+    <t>rdist</t>
+  </si>
+  <si>
+    <t>recipinvgauss</t>
+  </si>
+  <si>
+    <t>rel_breitwigner</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>skewcauchy</t>
+  </si>
+  <si>
+    <t>skewnorm</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>trapezoid</t>
+  </si>
+  <si>
+    <t>triang</t>
+  </si>
+  <si>
+    <t>truncexpon</t>
+  </si>
+  <si>
+    <t>truncnorm</t>
+  </si>
+  <si>
+    <t>truncpareto</t>
+  </si>
+  <si>
+    <t>truncweibull_min</t>
+  </si>
+  <si>
+    <t>tukeylambda</t>
+  </si>
+  <si>
+    <t>uniform</t>
+  </si>
+  <si>
+    <t>vonmises</t>
+  </si>
+  <si>
+    <t>vonmises_line</t>
+  </si>
+  <si>
+    <t>wald</t>
+  </si>
+  <si>
+    <t>weibull_max</t>
+  </si>
+  <si>
+    <t>weibull_min</t>
+  </si>
+  <si>
+    <t>wrapcauchy</t>
+  </si>
+  <si>
+    <t>zzgumbel</t>
+  </si>
+  <si>
+    <t>zzloggumbel</t>
+  </si>
+  <si>
+    <t>risk_rate</t>
+  </si>
+  <si>
+    <t>inf</t>
   </si>
 </sst>
 </file>
@@ -3744,55 +4160,55 @@
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.45">
@@ -3847,7 +4263,7 @@
     </row>
     <row r="3" spans="1:18" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT(B2,"-",B1)</f>
@@ -4262,7 +4678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC3BD22-A60D-404D-A6C3-12A1448027F8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:DG7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.73046875" style="1" bestFit="1" customWidth="1"/>
@@ -4303,7 +4719,7 @@
     <col min="47" max="49" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="8.9296875" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="16.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="9.46484375" style="1" bestFit="1" customWidth="1"/>
@@ -4342,7 +4758,2891 @@
     <col min="95" max="95" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
     <col min="96" max="16384" width="9.06640625" style="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2.33</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.57081499999999996</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.42918499999999998</v>
+      </c>
+      <c r="E2" s="1">
+        <v>111.379</v>
+      </c>
+      <c r="F2" s="1">
+        <v>114.28700000000001</v>
+      </c>
+      <c r="G2" s="1">
+        <v>117.78100000000001</v>
+      </c>
+      <c r="H2" s="1">
+        <v>118.01300000000001</v>
+      </c>
+      <c r="I2" s="1">
+        <v>116.04600000000001</v>
+      </c>
+      <c r="J2" s="1">
+        <v>110.43300000000001</v>
+      </c>
+      <c r="K2" s="1">
+        <v>99.137699999999995</v>
+      </c>
+      <c r="L2" s="1">
+        <v>122.631</v>
+      </c>
+      <c r="M2" s="1">
+        <v>88.101299999999995</v>
+      </c>
+      <c r="N2" s="1">
+        <v>115.01900000000001</v>
+      </c>
+      <c r="O2" s="1">
+        <v>112.31699999999999</v>
+      </c>
+      <c r="P2" s="1">
+        <v>111.833</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="R2" s="1">
+        <v>115.94199999999999</v>
+      </c>
+      <c r="S2" s="1">
+        <v>112.557</v>
+      </c>
+      <c r="T2" s="1">
+        <v>96.941400000000002</v>
+      </c>
+      <c r="U2" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="V2" s="1">
+        <v>40.029200000000003</v>
+      </c>
+      <c r="W2" s="1">
+        <v>45.6708</v>
+      </c>
+      <c r="X2" s="1">
+        <v>113.23399999999999</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>113.119</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>108.92</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>114.572</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>112.726</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>119.681</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>93.846199999999996</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>119.205</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>43.968699999999998</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>125.488</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>121.026</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>107.1</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>114.27800000000001</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>113.20699999999999</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>100.283</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>118.83499999999999</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>118.032</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>107.35299999999999</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>115.962</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>90.125500000000002</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>104.77</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>106.911</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>112.10599999999999</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>110.739</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>108.654</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>107.932</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>118.82899999999999</v>
+      </c>
+      <c r="BA2" s="1">
+        <v>117.621</v>
+      </c>
+      <c r="BB2" s="1">
+        <v>125.036</v>
+      </c>
+      <c r="BC2" s="1">
+        <v>104.84</v>
+      </c>
+      <c r="BD2" s="1">
+        <v>110.197</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>107.42100000000001</v>
+      </c>
+      <c r="BF2" s="1">
+        <v>110.938</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>112.983</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>163.108</v>
+      </c>
+      <c r="BI2" s="1">
+        <v>119.254</v>
+      </c>
+      <c r="BJ2" s="1">
+        <v>116.01</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>116.357</v>
+      </c>
+      <c r="BL2" s="1">
+        <v>112.589</v>
+      </c>
+      <c r="BM2" s="1">
+        <v>114.03700000000001</v>
+      </c>
+      <c r="BN2" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="BO2" s="1">
+        <v>107.56100000000001</v>
+      </c>
+      <c r="BP2" s="1">
+        <v>145.53800000000001</v>
+      </c>
+      <c r="BQ2" s="1">
+        <v>110.666</v>
+      </c>
+      <c r="BR2" s="1">
+        <v>107.348</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>105.279</v>
+      </c>
+      <c r="BT2" s="1">
+        <v>113.34399999999999</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>110.51</v>
+      </c>
+      <c r="BV2" s="1">
+        <v>113.3</v>
+      </c>
+      <c r="BW2" s="1">
+        <v>62.697800000000001</v>
+      </c>
+      <c r="BX2" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="BY2" s="1">
+        <v>118.297</v>
+      </c>
+      <c r="BZ2" s="1">
+        <v>96.941400000000002</v>
+      </c>
+      <c r="CA2" s="1">
+        <v>114.536</v>
+      </c>
+      <c r="CB2" s="1">
+        <v>87.360100000000003</v>
+      </c>
+      <c r="CC2" s="1">
+        <v>115.205</v>
+      </c>
+      <c r="CD2" s="1">
+        <v>117.34699999999999</v>
+      </c>
+      <c r="CE2" s="1">
+        <v>109.741</v>
+      </c>
+      <c r="CF2" s="1">
+        <v>75.443899999999999</v>
+      </c>
+      <c r="CG2" s="1">
+        <v>111.96</v>
+      </c>
+      <c r="CH2" s="1">
+        <v>134.995</v>
+      </c>
+      <c r="CI2" s="1">
+        <v>116.053</v>
+      </c>
+      <c r="CJ2" s="1">
+        <v>114.79300000000001</v>
+      </c>
+      <c r="CK2" s="1">
+        <v>124.33499999999999</v>
+      </c>
+      <c r="CL2" s="1">
+        <v>123.045</v>
+      </c>
+      <c r="CM2" s="1">
+        <v>113.30200000000001</v>
+      </c>
+      <c r="CN2" s="1">
+        <v>136.79499999999999</v>
+      </c>
+      <c r="CO2" s="1">
+        <v>123.19799999999999</v>
+      </c>
+      <c r="CP2" s="1">
+        <v>98.857299999999995</v>
+      </c>
+      <c r="CQ2" s="1">
+        <v>113.301</v>
+      </c>
+      <c r="CR2" s="1">
+        <v>92.069800000000001</v>
+      </c>
+      <c r="CS2" s="1">
+        <v>104.181</v>
+      </c>
+      <c r="CT2" s="1">
+        <v>108.786</v>
+      </c>
+      <c r="CU2" s="1">
+        <v>108.498</v>
+      </c>
+      <c r="CV2" s="1">
+        <v>3.2704300000000002</v>
+      </c>
+      <c r="CW2" s="1">
+        <v>105.13500000000001</v>
+      </c>
+      <c r="CX2" s="1">
+        <v>100.371</v>
+      </c>
+      <c r="CY2" s="1">
+        <v>159.89500000000001</v>
+      </c>
+      <c r="CZ2" s="1">
+        <v>115.33799999999999</v>
+      </c>
+      <c r="DA2" s="1">
+        <v>108.851</v>
+      </c>
+      <c r="DB2" s="1">
+        <v>122.61199999999999</v>
+      </c>
+      <c r="DC2" s="1">
+        <v>102.22499999999999</v>
+      </c>
+      <c r="DD2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF2" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG2" s="1">
+        <v>0.729209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>135.06899999999999</v>
+      </c>
+      <c r="F3" s="1">
+        <v>138.881</v>
+      </c>
+      <c r="G3" s="1">
+        <v>145.684</v>
+      </c>
+      <c r="H3" s="1">
+        <v>138.33000000000001</v>
+      </c>
+      <c r="I3" s="1">
+        <v>140.715</v>
+      </c>
+      <c r="J3" s="1">
+        <v>135.857</v>
+      </c>
+      <c r="K3" s="1">
+        <v>129.57900000000001</v>
+      </c>
+      <c r="L3" s="1">
+        <v>142.167</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" s="1">
+        <v>145.19300000000001</v>
+      </c>
+      <c r="O3" s="1">
+        <v>135.61000000000001</v>
+      </c>
+      <c r="P3" s="1">
+        <v>134.40100000000001</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="R3" s="1">
+        <v>133.84100000000001</v>
+      </c>
+      <c r="S3" s="1">
+        <v>135.364</v>
+      </c>
+      <c r="T3" s="1">
+        <v>148.34299999999999</v>
+      </c>
+      <c r="U3" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="V3" s="1">
+        <v>41.716700000000003</v>
+      </c>
+      <c r="W3" s="1">
+        <v>104.214</v>
+      </c>
+      <c r="X3" s="1">
+        <v>135.61199999999999</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>135.874</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>136.191</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>148.76599999999999</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>114.86</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>135.53399999999999</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>143.36600000000001</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>142.45400000000001</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>137.989</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>88.034800000000004</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>146.28700000000001</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>138.953</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>139.63499999999999</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>136.31800000000001</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>144.66399999999999</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>117.735</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>137.28</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>134.852</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>131.44300000000001</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>226.80600000000001</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>197.13200000000001</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>130.56700000000001</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>134.22300000000001</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>131.316</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>134.928</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>135.29599999999999</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>136.96299999999999</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>141.88900000000001</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>136.72200000000001</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>159.178</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>133.95500000000001</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>143.19999999999999</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>137.79900000000001</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>129.04400000000001</v>
+      </c>
+      <c r="BG3" s="1">
+        <v>134.446</v>
+      </c>
+      <c r="BH3" s="1">
+        <v>678.947</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>146.429</v>
+      </c>
+      <c r="BJ3" s="1">
+        <v>142.06200000000001</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>136.18199999999999</v>
+      </c>
+      <c r="BL3" s="1">
+        <v>132.947</v>
+      </c>
+      <c r="BM3" s="1">
+        <v>142.91900000000001</v>
+      </c>
+      <c r="BN3" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="BO3" s="1">
+        <v>135.41800000000001</v>
+      </c>
+      <c r="BP3" s="1">
+        <v>240.80699999999999</v>
+      </c>
+      <c r="BQ3" s="1">
+        <v>135.136</v>
+      </c>
+      <c r="BR3" s="1">
+        <v>136.44300000000001</v>
+      </c>
+      <c r="BS3" s="1">
+        <v>129.59200000000001</v>
+      </c>
+      <c r="BT3" s="1">
+        <v>135.654</v>
+      </c>
+      <c r="BU3" s="1">
+        <v>135.71</v>
+      </c>
+      <c r="BV3" s="1">
+        <v>135.54300000000001</v>
+      </c>
+      <c r="BW3" s="1">
+        <v>353.13299999999998</v>
+      </c>
+      <c r="BX3" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="BY3" s="1">
+        <v>137.071</v>
+      </c>
+      <c r="BZ3" s="1">
+        <v>148.34299999999999</v>
+      </c>
+      <c r="CA3" s="1">
+        <v>135.85</v>
+      </c>
+      <c r="CB3" s="1">
+        <v>122.88800000000001</v>
+      </c>
+      <c r="CC3" s="1">
+        <v>136.196</v>
+      </c>
+      <c r="CD3" s="1">
+        <v>136.63200000000001</v>
+      </c>
+      <c r="CE3" s="1">
+        <v>134.999</v>
+      </c>
+      <c r="CF3" s="1">
+        <v>92.534199999999998</v>
+      </c>
+      <c r="CG3" s="1">
+        <v>135.34899999999999</v>
+      </c>
+      <c r="CH3" s="1">
+        <v>141.33500000000001</v>
+      </c>
+      <c r="CI3" s="1">
+        <v>135.899</v>
+      </c>
+      <c r="CJ3" s="1">
+        <v>140.30500000000001</v>
+      </c>
+      <c r="CK3" s="1">
+        <v>142.142</v>
+      </c>
+      <c r="CL3" s="1">
+        <v>141.84700000000001</v>
+      </c>
+      <c r="CM3" s="1">
+        <v>135.542</v>
+      </c>
+      <c r="CN3" s="1">
+        <v>156.798</v>
+      </c>
+      <c r="CO3" s="1">
+        <v>142.09</v>
+      </c>
+      <c r="CP3" s="1">
+        <v>128.99100000000001</v>
+      </c>
+      <c r="CQ3" s="1">
+        <v>135.54</v>
+      </c>
+      <c r="CR3" s="1">
+        <v>123.018</v>
+      </c>
+      <c r="CS3" s="1">
+        <v>132.72300000000001</v>
+      </c>
+      <c r="CT3" s="1">
+        <v>136.93799999999999</v>
+      </c>
+      <c r="CU3" s="1">
+        <v>136</v>
+      </c>
+      <c r="CV3" s="1">
+        <v>4.4239699999999997</v>
+      </c>
+      <c r="CW3" s="1">
+        <v>131.55099999999999</v>
+      </c>
+      <c r="CX3" s="1">
+        <v>122.336</v>
+      </c>
+      <c r="CY3" s="1">
+        <v>159.99799999999999</v>
+      </c>
+      <c r="CZ3" s="1">
+        <v>135.964</v>
+      </c>
+      <c r="DA3" s="1">
+        <v>136.494</v>
+      </c>
+      <c r="DB3" s="1">
+        <v>147.001</v>
+      </c>
+      <c r="DC3" s="1">
+        <v>132.39099999999999</v>
+      </c>
+      <c r="DD3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF3" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG3" s="1">
+        <v>0.67232000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>151.779</v>
+      </c>
+      <c r="F4" s="1">
+        <v>152.80099999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>152.41999999999999</v>
+      </c>
+      <c r="H4" s="1">
+        <v>147.82900000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>150.77000000000001</v>
+      </c>
+      <c r="J4" s="1">
+        <v>154.33199999999999</v>
+      </c>
+      <c r="K4" s="1">
+        <v>144.309</v>
+      </c>
+      <c r="L4" s="1">
+        <v>149.79900000000001</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N4" s="1">
+        <v>189.827</v>
+      </c>
+      <c r="O4" s="1">
+        <v>151.52500000000001</v>
+      </c>
+      <c r="P4" s="1">
+        <v>148.035</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="R4" s="1">
+        <v>145.38800000000001</v>
+      </c>
+      <c r="S4" s="1">
+        <v>150.79300000000001</v>
+      </c>
+      <c r="T4" s="1">
+        <v>195.00299999999999</v>
+      </c>
+      <c r="U4" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="V4" s="1">
+        <v>52.665999999999997</v>
+      </c>
+      <c r="W4" s="1">
+        <v>319.39499999999998</v>
+      </c>
+      <c r="X4" s="1">
+        <v>150.49100000000001</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>151.232</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>152.607</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>223.83699999999999</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>115.074</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>150.94900000000001</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>152.501</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>186.578</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>147.20400000000001</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>240.56399999999999</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>153.62799999999999</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>147.61699999999999</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>165.39699999999999</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>152.41800000000001</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>154.429</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>137.62799999999999</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>147.54900000000001</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>144.21600000000001</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>151.06299999999999</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>423.226</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>352.58499999999998</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>151.989</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>154.43299999999999</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>146.65600000000001</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>152.078</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>155.386</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>160.608</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>150.74</v>
+      </c>
+      <c r="BA4" s="1">
+        <v>147.60300000000001</v>
+      </c>
+      <c r="BB4" s="1">
+        <v>174.07599999999999</v>
+      </c>
+      <c r="BC4" s="1">
+        <v>146.94999999999999</v>
+      </c>
+      <c r="BD4" s="1">
+        <v>157.6</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>160.92699999999999</v>
+      </c>
+      <c r="BF4" s="1">
+        <v>145.47999999999999</v>
+      </c>
+      <c r="BG4" s="1">
+        <v>153.93</v>
+      </c>
+      <c r="BH4" s="1">
+        <v>2654.45</v>
+      </c>
+      <c r="BI4" s="1">
+        <v>152.99</v>
+      </c>
+      <c r="BJ4" s="1">
+        <v>159.34399999999999</v>
+      </c>
+      <c r="BK4" s="1">
+        <v>148.077</v>
+      </c>
+      <c r="BL4" s="1">
+        <v>147.94</v>
+      </c>
+      <c r="BM4" s="1">
+        <v>175.40600000000001</v>
+      </c>
+      <c r="BN4" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="BO4" s="1">
+        <v>147.67699999999999</v>
+      </c>
+      <c r="BP4" s="1">
+        <v>327.29000000000002</v>
+      </c>
+      <c r="BQ4" s="1">
+        <v>152.357</v>
+      </c>
+      <c r="BR4" s="1">
+        <v>160.34899999999999</v>
+      </c>
+      <c r="BS4" s="1">
+        <v>150.761</v>
+      </c>
+      <c r="BT4" s="1">
+        <v>150.47200000000001</v>
+      </c>
+      <c r="BU4" s="1">
+        <v>154.053</v>
+      </c>
+      <c r="BV4" s="1">
+        <v>150.29900000000001</v>
+      </c>
+      <c r="BW4" s="1">
+        <v>560.17399999999998</v>
+      </c>
+      <c r="BX4" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="BY4" s="1">
+        <v>147.547</v>
+      </c>
+      <c r="BZ4" s="1">
+        <v>195.00299999999999</v>
+      </c>
+      <c r="CA4" s="1">
+        <v>149.376</v>
+      </c>
+      <c r="CB4" s="1">
+        <v>140.76499999999999</v>
+      </c>
+      <c r="CC4" s="1">
+        <v>149.40899999999999</v>
+      </c>
+      <c r="CD4" s="1">
+        <v>147.934</v>
+      </c>
+      <c r="CE4" s="1">
+        <v>153.00800000000001</v>
+      </c>
+      <c r="CF4" s="1">
+        <v>94.675700000000006</v>
+      </c>
+      <c r="CG4" s="1">
+        <v>151.51300000000001</v>
+      </c>
+      <c r="CH4" s="1">
+        <v>148.38800000000001</v>
+      </c>
+      <c r="CI4" s="1">
+        <v>149.375</v>
+      </c>
+      <c r="CJ4" s="1">
+        <v>153.39599999999999</v>
+      </c>
+      <c r="CK4" s="1">
+        <v>148.727</v>
+      </c>
+      <c r="CL4" s="1">
+        <v>149.55000000000001</v>
+      </c>
+      <c r="CM4" s="1">
+        <v>150.29599999999999</v>
+      </c>
+      <c r="CN4" s="1">
+        <v>164.61</v>
+      </c>
+      <c r="CO4" s="1">
+        <v>149.47</v>
+      </c>
+      <c r="CP4" s="1">
+        <v>143.84800000000001</v>
+      </c>
+      <c r="CQ4" s="1">
+        <v>150.292</v>
+      </c>
+      <c r="CR4" s="1">
+        <v>139.92699999999999</v>
+      </c>
+      <c r="CS4" s="1">
+        <v>146.012</v>
+      </c>
+      <c r="CT4" s="1">
+        <v>148.857</v>
+      </c>
+      <c r="CU4" s="1">
+        <v>148</v>
+      </c>
+      <c r="CV4" s="1">
+        <v>5.1534599999999999</v>
+      </c>
+      <c r="CW4" s="1">
+        <v>145.185</v>
+      </c>
+      <c r="CX4" s="1">
+        <v>145.64699999999999</v>
+      </c>
+      <c r="CY4" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ4" s="1">
+        <v>148.64699999999999</v>
+      </c>
+      <c r="DA4" s="1">
+        <v>148.55600000000001</v>
+      </c>
+      <c r="DB4" s="1">
+        <v>166.86600000000001</v>
+      </c>
+      <c r="DC4" s="1">
+        <v>163.42699999999999</v>
+      </c>
+      <c r="DD4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF4" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG4" s="1">
+        <v>0.65132199999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="E5" s="1">
+        <v>170.554</v>
+      </c>
+      <c r="F5" s="1">
+        <v>164.61099999999999</v>
+      </c>
+      <c r="G5" s="1">
+        <v>154.36699999999999</v>
+      </c>
+      <c r="H5" s="1">
+        <v>154.57400000000001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>156.495</v>
+      </c>
+      <c r="J5" s="1">
+        <v>175.51300000000001</v>
+      </c>
+      <c r="K5" s="1">
+        <v>153.60400000000001</v>
+      </c>
+      <c r="L5" s="1">
+        <v>154.846</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N5" s="1">
+        <v>316.75400000000002</v>
+      </c>
+      <c r="O5" s="1">
+        <v>168.90700000000001</v>
+      </c>
+      <c r="P5" s="1">
+        <v>160.744</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="R5" s="1">
+        <v>158.767</v>
+      </c>
+      <c r="S5" s="1">
+        <v>167.512</v>
+      </c>
+      <c r="T5" s="1">
+        <v>256.685</v>
+      </c>
+      <c r="U5" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="V5" s="1">
+        <v>109.09699999999999</v>
+      </c>
+      <c r="W5" s="1">
+        <v>1244.43</v>
+      </c>
+      <c r="X5" s="1">
+        <v>166.386</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>167.84399999999999</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>172.46199999999999</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>467.084</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>115.315</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>167.64</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>157.37700000000001</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>244.90700000000001</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>154.227</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>824.57600000000002</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>157.589</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>154.44399999999999</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>196.73099999999999</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>171.82</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>158.53899999999999</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>171.08600000000001</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>157.154</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>152.97499999999999</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>175.85400000000001</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>1004.75</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>656.95500000000004</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>179.15100000000001</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>177.18</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>166.36600000000001</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>171.41499999999999</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>179.114</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>190.48400000000001</v>
+      </c>
+      <c r="AZ5" s="1">
+        <v>156.07900000000001</v>
+      </c>
+      <c r="BA5" s="1">
+        <v>157.85300000000001</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>183.01400000000001</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>154.82599999999999</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>166.24</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>187.673</v>
+      </c>
+      <c r="BF5" s="1">
+        <v>167.20699999999999</v>
+      </c>
+      <c r="BG5" s="1">
+        <v>179.68700000000001</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>16482.5</v>
+      </c>
+      <c r="BI5" s="1">
+        <v>156.62299999999999</v>
+      </c>
+      <c r="BJ5" s="1">
+        <v>177.773</v>
+      </c>
+      <c r="BK5" s="1">
+        <v>159.809</v>
+      </c>
+      <c r="BL5" s="1">
+        <v>166.07300000000001</v>
+      </c>
+      <c r="BM5" s="1">
+        <v>229.92400000000001</v>
+      </c>
+      <c r="BN5" s="1">
+        <v>166.02500000000001</v>
+      </c>
+      <c r="BO5" s="1">
+        <v>155.06299999999999</v>
+      </c>
+      <c r="BP5" s="1">
+        <v>441.61399999999998</v>
+      </c>
+      <c r="BQ5" s="1">
+        <v>171.41</v>
+      </c>
+      <c r="BR5" s="1">
+        <v>190.82300000000001</v>
+      </c>
+      <c r="BS5" s="1">
+        <v>178.49199999999999</v>
+      </c>
+      <c r="BT5" s="1">
+        <v>166.28800000000001</v>
+      </c>
+      <c r="BU5" s="1">
+        <v>175.07</v>
+      </c>
+      <c r="BV5" s="1">
+        <v>166.035</v>
+      </c>
+      <c r="BW5" s="1">
+        <v>793.58500000000004</v>
+      </c>
+      <c r="BX5" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="BY5" s="1">
+        <v>157.24</v>
+      </c>
+      <c r="BZ5" s="1">
+        <v>256.685</v>
+      </c>
+      <c r="CA5" s="1">
+        <v>163.27099999999999</v>
+      </c>
+      <c r="CB5" s="1">
+        <v>152.14599999999999</v>
+      </c>
+      <c r="CC5" s="1">
+        <v>162.97</v>
+      </c>
+      <c r="CD5" s="1">
+        <v>158.922</v>
+      </c>
+      <c r="CE5" s="1">
+        <v>173.03800000000001</v>
+      </c>
+      <c r="CF5" s="1">
+        <v>94.978700000000003</v>
+      </c>
+      <c r="CG5" s="1">
+        <v>169.33699999999999</v>
+      </c>
+      <c r="CH5" s="1">
+        <v>162.74799999999999</v>
+      </c>
+      <c r="CI5" s="1">
+        <v>163.916</v>
+      </c>
+      <c r="CJ5" s="1">
+        <v>163.16900000000001</v>
+      </c>
+      <c r="CK5" s="1">
+        <v>153.477</v>
+      </c>
+      <c r="CL5" s="1">
+        <v>154.71700000000001</v>
+      </c>
+      <c r="CM5" s="1">
+        <v>166.029</v>
+      </c>
+      <c r="CN5" s="1">
+        <v>169.09100000000001</v>
+      </c>
+      <c r="CO5" s="1">
+        <v>154.53100000000001</v>
+      </c>
+      <c r="CP5" s="1">
+        <v>153.37</v>
+      </c>
+      <c r="CQ5" s="1">
+        <v>166.024</v>
+      </c>
+      <c r="CR5" s="1">
+        <v>151.51599999999999</v>
+      </c>
+      <c r="CS5" s="1">
+        <v>154.31100000000001</v>
+      </c>
+      <c r="CT5" s="1">
+        <v>155.739</v>
+      </c>
+      <c r="CU5" s="1">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="CV5" s="1">
+        <v>5.7056800000000001</v>
+      </c>
+      <c r="CW5" s="1">
+        <v>153.99199999999999</v>
+      </c>
+      <c r="CX5" s="1">
+        <v>180.70599999999999</v>
+      </c>
+      <c r="CY5" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ5" s="1">
+        <v>161.35900000000001</v>
+      </c>
+      <c r="DA5" s="1">
+        <v>155.79300000000001</v>
+      </c>
+      <c r="DB5" s="1">
+        <v>191.965</v>
+      </c>
+      <c r="DC5" s="1">
+        <v>213.25200000000001</v>
+      </c>
+      <c r="DD5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF5" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG5" s="1">
+        <v>0.63960300000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="1">
+        <v>183.245</v>
+      </c>
+      <c r="F6" s="1">
+        <v>170.44399999999999</v>
+      </c>
+      <c r="G6" s="1">
+        <v>154.64699999999999</v>
+      </c>
+      <c r="H6" s="1">
+        <v>157.386</v>
+      </c>
+      <c r="I6" s="1">
+        <v>158.31200000000001</v>
+      </c>
+      <c r="J6" s="1">
+        <v>190.035</v>
+      </c>
+      <c r="K6" s="1">
+        <v>156.78200000000001</v>
+      </c>
+      <c r="L6" s="1">
+        <v>157.32400000000001</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N6" s="1">
+        <v>526.07399999999996</v>
+      </c>
+      <c r="O6" s="1">
+        <v>180.363</v>
+      </c>
+      <c r="P6" s="1">
+        <v>167.75700000000001</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="R6" s="1">
+        <v>168.15199999999999</v>
+      </c>
+      <c r="S6" s="1">
+        <v>178.459</v>
+      </c>
+      <c r="T6" s="1">
+        <v>303.346</v>
+      </c>
+      <c r="U6" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="V6" s="1">
+        <v>212.358</v>
+      </c>
+      <c r="W6" s="1">
+        <v>2971.99</v>
+      </c>
+      <c r="X6" s="1">
+        <v>176.67099999999999</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>178.70400000000001</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>186.911</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>883.75400000000002</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>115.47499999999999</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>178.56100000000001</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>158.81399999999999</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>289.03100000000001</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>157.37899999999999</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>1796.76</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>158.828</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>157.727</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>219.161</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>185.917</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>159.46899999999999</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>202.71700000000001</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>162.74600000000001</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>158.07400000000001</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>194.24600000000001</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>1971.41</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>972.26900000000001</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>199.31399999999999</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>192.34399999999999</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>181.184</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>184.517</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>195.78100000000001</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>212.648</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>158.08099999999999</v>
+      </c>
+      <c r="BA6" s="1">
+        <v>163.81299999999999</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>185.994</v>
+      </c>
+      <c r="BC6" s="1">
+        <v>157.46600000000001</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>169.12</v>
+      </c>
+      <c r="BE6" s="1">
+        <v>205.86600000000001</v>
+      </c>
+      <c r="BF6" s="1">
+        <v>183.643</v>
+      </c>
+      <c r="BG6" s="1">
+        <v>199.17099999999999</v>
+      </c>
+      <c r="BH6" s="1">
+        <v>65868.5</v>
+      </c>
+      <c r="BI6" s="1">
+        <v>158.05799999999999</v>
+      </c>
+      <c r="BJ6" s="1">
+        <v>189.679</v>
+      </c>
+      <c r="BK6" s="1">
+        <v>166.91900000000001</v>
+      </c>
+      <c r="BL6" s="1">
+        <v>179.26900000000001</v>
+      </c>
+      <c r="BM6" s="1">
+        <v>282.14100000000002</v>
+      </c>
+      <c r="BN6" s="1">
+        <v>176.18799999999999</v>
+      </c>
+      <c r="BO6" s="1">
+        <v>157.53</v>
+      </c>
+      <c r="BP6" s="1">
+        <v>528.09699999999998</v>
+      </c>
+      <c r="BQ6" s="1">
+        <v>184.035</v>
+      </c>
+      <c r="BR6" s="1">
+        <v>213.62700000000001</v>
+      </c>
+      <c r="BS6" s="1">
+        <v>199.428</v>
+      </c>
+      <c r="BT6" s="1">
+        <v>176.51499999999999</v>
+      </c>
+      <c r="BU6" s="1">
+        <v>189.458</v>
+      </c>
+      <c r="BV6" s="1">
+        <v>176.20099999999999</v>
+      </c>
+      <c r="BW6" s="1">
+        <v>951.298</v>
+      </c>
+      <c r="BX6" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="BY6" s="1">
+        <v>162.792</v>
+      </c>
+      <c r="BZ6" s="1">
+        <v>303.346</v>
+      </c>
+      <c r="CA6" s="1">
+        <v>171.96</v>
+      </c>
+      <c r="CB6" s="1">
+        <v>156.047</v>
+      </c>
+      <c r="CC6" s="1">
+        <v>171.48099999999999</v>
+      </c>
+      <c r="CD6" s="1">
+        <v>165.52099999999999</v>
+      </c>
+      <c r="CE6" s="1">
+        <v>186.34</v>
+      </c>
+      <c r="CF6" s="1">
+        <v>94.997600000000006</v>
+      </c>
+      <c r="CG6" s="1">
+        <v>181.179</v>
+      </c>
+      <c r="CH6" s="1">
+        <v>179.28100000000001</v>
+      </c>
+      <c r="CI6" s="1">
+        <v>173.37700000000001</v>
+      </c>
+      <c r="CJ6" s="1">
+        <v>167.36500000000001</v>
+      </c>
+      <c r="CK6" s="1">
+        <v>158.51900000000001</v>
+      </c>
+      <c r="CL6" s="1">
+        <v>157.19800000000001</v>
+      </c>
+      <c r="CM6" s="1">
+        <v>176.19200000000001</v>
+      </c>
+      <c r="CN6" s="1">
+        <v>170.553</v>
+      </c>
+      <c r="CO6" s="1">
+        <v>157.07599999999999</v>
+      </c>
+      <c r="CP6" s="1">
+        <v>156.655</v>
+      </c>
+      <c r="CQ6" s="1">
+        <v>176.18700000000001</v>
+      </c>
+      <c r="CR6" s="1">
+        <v>155.67400000000001</v>
+      </c>
+      <c r="CS6" s="1">
+        <v>157.13900000000001</v>
+      </c>
+      <c r="CT6" s="1">
+        <v>157.93799999999999</v>
+      </c>
+      <c r="CU6" s="1">
+        <v>157.6</v>
+      </c>
+      <c r="CV6" s="1">
+        <v>5.9053800000000001</v>
+      </c>
+      <c r="CW6" s="1">
+        <v>156.99</v>
+      </c>
+      <c r="CX6" s="1">
+        <v>209.87899999999999</v>
+      </c>
+      <c r="CY6" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ6" s="1">
+        <v>169.161</v>
+      </c>
+      <c r="DA6" s="1">
+        <v>158.20500000000001</v>
+      </c>
+      <c r="DB6" s="1">
+        <v>210.584</v>
+      </c>
+      <c r="DC6" s="1">
+        <v>259.79399999999998</v>
+      </c>
+      <c r="DD6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF6" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG6" s="1">
+        <v>0.63583000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>100</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="E7" s="1">
+        <v>195.06</v>
+      </c>
+      <c r="F7" s="1">
+        <v>174.53800000000001</v>
+      </c>
+      <c r="G7" s="1">
+        <v>154.71700000000001</v>
+      </c>
+      <c r="H7" s="1">
+        <v>159.114</v>
+      </c>
+      <c r="I7" s="1">
+        <v>159.18700000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>203.67599999999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>158.386</v>
+      </c>
+      <c r="L7" s="1">
+        <v>159.386</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N7" s="1">
+        <v>943.88900000000001</v>
+      </c>
+      <c r="O7" s="1">
+        <v>190.821</v>
+      </c>
+      <c r="P7" s="1">
+        <v>173.20599999999999</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="R7" s="1">
+        <v>177.143</v>
+      </c>
+      <c r="S7" s="1">
+        <v>188.404</v>
+      </c>
+      <c r="T7" s="1">
+        <v>350.00700000000001</v>
+      </c>
+      <c r="U7" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="V7" s="1">
+        <v>395.87400000000002</v>
+      </c>
+      <c r="W7" s="1">
+        <v>6345.72</v>
+      </c>
+      <c r="X7" s="1">
+        <v>185.934</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>188.56100000000001</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>201.148</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>1722.19</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>115.622</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>188.47800000000001</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>159.464</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>333.15600000000001</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>159.43199999999999</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>3510.79</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>159.42699999999999</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>160.041</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>240.839</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>199.798</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>159.80699999999999</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>240.62899999999999</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>167.423</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>162.339</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>212.501</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>3903.78</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>1369.78</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>219.33199999999999</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>206.22200000000001</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>195.98699999999999</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>196.73400000000001</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>211.71</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>234.648</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>159.268</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>168.773</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>187.5</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>158.79</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>170.56</v>
+      </c>
+      <c r="BE7" s="1">
+        <v>222.733</v>
+      </c>
+      <c r="BF7" s="1">
+        <v>200.07900000000001</v>
+      </c>
+      <c r="BG7" s="1">
+        <v>218.655</v>
+      </c>
+      <c r="BH7" s="1">
+        <v>263412</v>
+      </c>
+      <c r="BI7" s="1">
+        <v>158.99199999999999</v>
+      </c>
+      <c r="BJ7" s="1">
+        <v>200.38800000000001</v>
+      </c>
+      <c r="BK7" s="1">
+        <v>173.02799999999999</v>
+      </c>
+      <c r="BL7" s="1">
+        <v>192.27199999999999</v>
+      </c>
+      <c r="BM7" s="1">
+        <v>346.2</v>
+      </c>
+      <c r="BN7" s="1">
+        <v>185.32900000000001</v>
+      </c>
+      <c r="BO7" s="1">
+        <v>158.76499999999999</v>
+      </c>
+      <c r="BP7" s="1">
+        <v>614.58000000000004</v>
+      </c>
+      <c r="BQ7" s="1">
+        <v>195.57499999999999</v>
+      </c>
+      <c r="BR7" s="1">
+        <v>236.429</v>
+      </c>
+      <c r="BS7" s="1">
+        <v>220.357</v>
+      </c>
+      <c r="BT7" s="1">
+        <v>185.71899999999999</v>
+      </c>
+      <c r="BU7" s="1">
+        <v>202.95099999999999</v>
+      </c>
+      <c r="BV7" s="1">
+        <v>185.346</v>
+      </c>
+      <c r="BW7" s="1">
+        <v>1097.8</v>
+      </c>
+      <c r="BX7" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="BY7" s="1">
+        <v>167.363</v>
+      </c>
+      <c r="BZ7" s="1">
+        <v>350.00700000000001</v>
+      </c>
+      <c r="CA7" s="1">
+        <v>179.58600000000001</v>
+      </c>
+      <c r="CB7" s="1">
+        <v>158.017</v>
+      </c>
+      <c r="CC7" s="1">
+        <v>178.99100000000001</v>
+      </c>
+      <c r="CD7" s="1">
+        <v>171.16399999999999</v>
+      </c>
+      <c r="CE7" s="1">
+        <v>198.50700000000001</v>
+      </c>
+      <c r="CF7" s="1">
+        <v>95.000100000000003</v>
+      </c>
+      <c r="CG7" s="1">
+        <v>192.05500000000001</v>
+      </c>
+      <c r="CH7" s="1">
+        <v>202.33500000000001</v>
+      </c>
+      <c r="CI7" s="1">
+        <v>181.923</v>
+      </c>
+      <c r="CJ7" s="1">
+        <v>169.98</v>
+      </c>
+      <c r="CK7" s="1">
+        <v>167.89699999999999</v>
+      </c>
+      <c r="CL7" s="1">
+        <v>159.12700000000001</v>
+      </c>
+      <c r="CM7" s="1">
+        <v>185.334</v>
+      </c>
+      <c r="CN7" s="1">
+        <v>171.27799999999999</v>
+      </c>
+      <c r="CO7" s="1">
+        <v>158.875</v>
+      </c>
+      <c r="CP7" s="1">
+        <v>158.32</v>
+      </c>
+      <c r="CQ7" s="1">
+        <v>185.328</v>
+      </c>
+      <c r="CR7" s="1">
+        <v>157.815</v>
+      </c>
+      <c r="CS7" s="1">
+        <v>158.565</v>
+      </c>
+      <c r="CT7" s="1">
+        <v>159</v>
+      </c>
+      <c r="CU7" s="1">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="CV7" s="1">
+        <v>6.00678</v>
+      </c>
+      <c r="CW7" s="1">
+        <v>158.494</v>
+      </c>
+      <c r="CX7" s="1">
+        <v>240.91900000000001</v>
+      </c>
+      <c r="CY7" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ7" s="1">
+        <v>175.923</v>
+      </c>
+      <c r="DA7" s="1">
+        <v>159.411</v>
+      </c>
+      <c r="DB7" s="1">
+        <v>229.06700000000001</v>
+      </c>
+      <c r="DC7" s="1">
+        <v>316.03300000000002</v>
+      </c>
+      <c r="DD7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF7" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG7" s="1">
+        <v>0.63396799999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14F8E49-787B-42A5-8853-3A8AB20BD89C}">
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.3984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="6.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1">
+        <v>9.7888199999999995E-2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>41</v>
+      </c>
+      <c r="J2" s="1">
+        <v>39.726500000000001</v>
+      </c>
+      <c r="K2" s="1">
+        <v>120.274</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1595899999999999</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.95024799999999998</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1">
+        <v>8.9522900000000002E-2</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>41</v>
+      </c>
+      <c r="J3" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K3" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A4" s="1">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>9.1103900000000002E-2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>41</v>
+      </c>
+      <c r="J4" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K4" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A5" s="1">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>9.0033699999999994E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>41</v>
+      </c>
+      <c r="J5" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K5" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A6" s="1">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>9.0068700000000002E-2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>41</v>
+      </c>
+      <c r="J6" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K6" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>8.9805200000000002E-2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>41</v>
+      </c>
+      <c r="J7" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A8" s="1">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>8.9951900000000001E-2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>41</v>
+      </c>
+      <c r="J8" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A9" s="1">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8.9575299999999997E-2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>41</v>
+      </c>
+      <c r="J9" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K9" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A10" s="1">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>9.0033699999999994E-2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>41</v>
+      </c>
+      <c r="J10" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A11" s="1">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8.9717000000000005E-2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>41</v>
+      </c>
+      <c r="J11" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.6">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>9.0243299999999999E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.212396</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>41</v>
+      </c>
+      <c r="J12" s="1">
+        <v>107.31699999999999</v>
+      </c>
+      <c r="K12" s="1">
+        <v>67.067400000000006</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tool/PMP/old/PMP_Sample.xlsx
+++ b/tool/PMP/old/PMP_Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C883A926-EBD6-4A8E-A5DA-77A586E5BE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8101E2A9-0EEA-4915-BE5D-58EA8E8E78CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
   </bookViews>
   <sheets>
     <sheet name="Rain" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="146">
   <si>
     <t>Year / Station</t>
   </si>
@@ -475,6 +475,9 @@
   </si>
   <si>
     <t>inf</t>
+  </si>
+  <si>
+    <t>R.HydroTools-Semicircular</t>
   </si>
 </sst>
 </file>
@@ -516,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -525,6 +528,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,7 +971,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-R.HydroTools-Anglit</c:v>
+                  <c:v>25020230-R.HydroTools-Anglit</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1054,6 +1058,105 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-B4A2-4502-9742-A60DED037D90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!$S$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020230-R.HydroTools-Semicircular</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>PMP!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!$S$4:$S$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>114.79300000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140.30500000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>153.39599999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>163.16900000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>167.36500000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>169.98</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DB6E-42B9-A160-D3A373CE2B42}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4150,7 +4253,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EEC4ED-A2A6-48CB-9363-E12F4E5CCB23}">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
@@ -4158,7 +4261,7 @@
     <col min="16" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" s="2" customFormat="1" ht="66" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
@@ -4210,8 +4313,11 @@
       <c r="R1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="S1" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B2" s="2">
         <v>2502023</v>
       </c>
@@ -4260,8 +4366,14 @@
       <c r="Q2" s="2">
         <v>25020230</v>
       </c>
+      <c r="R2" s="2">
+        <v>25020230</v>
+      </c>
+      <c r="S2" s="2">
+        <v>25020230</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19" s="2" customFormat="1" ht="82.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -4270,7 +4382,7 @@
         <v>2502023-Excel-Gumbel</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f t="shared" ref="C3:R3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
+        <f t="shared" ref="C3:S3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
         <v>2502026-Excel-Gumbel</v>
       </c>
       <c r="D3" s="2" t="str">
@@ -4331,10 +4443,14 @@
       </c>
       <c r="R3" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>-R.HydroTools-Anglit</v>
+        <v>25020230-R.HydroTools-Anglit</v>
+      </c>
+      <c r="S3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>25020230-R.HydroTools-Semicircular</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.6">
       <c r="A4" s="3">
         <v>2.33</v>
       </c>
@@ -4389,8 +4505,11 @@
       <c r="R4" s="1">
         <v>114.28700000000001</v>
       </c>
+      <c r="S4" s="3">
+        <v>114.79300000000001</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>5</v>
       </c>
@@ -4445,8 +4564,11 @@
       <c r="R5" s="1">
         <v>138.881</v>
       </c>
+      <c r="S5" s="3">
+        <v>140.30500000000001</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.6">
       <c r="A6" s="3">
         <v>10</v>
       </c>
@@ -4501,8 +4623,11 @@
       <c r="R6" s="1">
         <v>152.80099999999999</v>
       </c>
+      <c r="S6" s="3">
+        <v>153.39599999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>25</v>
       </c>
@@ -4557,8 +4682,11 @@
       <c r="R7" s="1">
         <v>164.61099999999999</v>
       </c>
+      <c r="S7" s="3">
+        <v>163.16900000000001</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.6">
       <c r="A8" s="3">
         <v>50</v>
       </c>
@@ -4613,8 +4741,11 @@
       <c r="R8" s="1">
         <v>170.44399999999999</v>
       </c>
+      <c r="S8" s="3">
+        <v>167.36500000000001</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>100</v>
       </c>
@@ -4668,6 +4799,9 @@
       </c>
       <c r="R9" s="1">
         <v>174.53800000000001</v>
+      </c>
+      <c r="S9" s="3">
+        <v>169.98</v>
       </c>
     </row>
   </sheetData>
@@ -4678,85 +4812,99 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC3BD22-A60D-404D-A6C3-12A1448027F8}">
-  <dimension ref="A1:DG7"/>
+  <dimension ref="A1:DG11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.06640625" style="1"/>
-    <col min="11" max="15" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="49" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="57" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="61" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="66" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="8.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="8.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="72" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="9.06640625" style="1"/>
-    <col min="76" max="76" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="8.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="14.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="11.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="8.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="11.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="7.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="10.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="14.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="18.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="2.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="96" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="8.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="9.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="56" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="16.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="9.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="9.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="71" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="76" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="8.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="83" max="84" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="11.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="88" max="89" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="9.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="10.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="11.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="12.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="8.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="10.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="11.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="14.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="2.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="112" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:111" x14ac:dyDescent="0.6">
@@ -7102,6 +7250,1346 @@
       </c>
       <c r="DG7" s="1">
         <v>0.63396799999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>250</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.996</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>209.70500000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>178.15600000000001</v>
+      </c>
+      <c r="G8" s="1">
+        <v>154.73699999999999</v>
+      </c>
+      <c r="H8" s="1">
+        <v>160.43700000000001</v>
+      </c>
+      <c r="I8" s="1">
+        <v>159.69</v>
+      </c>
+      <c r="J8" s="1">
+        <v>220.71199999999999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>159.35300000000001</v>
+      </c>
+      <c r="L8" s="1">
+        <v>161.85400000000001</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N8" s="1">
+        <v>2196.67</v>
+      </c>
+      <c r="O8" s="1">
+        <v>203.50899999999999</v>
+      </c>
+      <c r="P8" s="1">
+        <v>178.64500000000001</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>196.251</v>
+      </c>
+      <c r="R8" s="1">
+        <v>188.607</v>
+      </c>
+      <c r="S8" s="1">
+        <v>200.41</v>
+      </c>
+      <c r="T8" s="1">
+        <v>411.68900000000002</v>
+      </c>
+      <c r="U8" s="1">
+        <v>196.25</v>
+      </c>
+      <c r="V8" s="1">
+        <v>805.64599999999996</v>
+      </c>
+      <c r="W8" s="1">
+        <v>15149.9</v>
+      </c>
+      <c r="X8" s="1">
+        <v>197.01400000000001</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>200.44800000000001</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>219.81899999999999</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>4241.74</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>115.8</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>200.44499999999999</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>159.81200000000001</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>391.48500000000001</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>161.102</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>7494.5</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>159.77699999999999</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>162.13800000000001</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>268.63900000000001</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>217.99600000000001</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>159.94900000000001</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>301.80799999999999</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>172.62700000000001</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>167.083</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>236.53800000000001</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>9700.11</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>2035.21</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>245.68799999999999</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>223.041</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>215.55</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>211.893</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>231.95</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>263.61500000000001</v>
+      </c>
+      <c r="AZ8" s="1">
+        <v>160.18299999999999</v>
+      </c>
+      <c r="BA8" s="1">
+        <v>174.244</v>
+      </c>
+      <c r="BB8" s="1">
+        <v>188.52099999999999</v>
+      </c>
+      <c r="BC8" s="1">
+        <v>159.58600000000001</v>
+      </c>
+      <c r="BD8" s="1">
+        <v>171.42400000000001</v>
+      </c>
+      <c r="BE8" s="1">
+        <v>243.41800000000001</v>
+      </c>
+      <c r="BF8" s="1">
+        <v>221.80600000000001</v>
+      </c>
+      <c r="BG8" s="1">
+        <v>244.41200000000001</v>
+      </c>
+      <c r="BH8" s="4">
+        <v>1646220</v>
+      </c>
+      <c r="BI8" s="1">
+        <v>159.81399999999999</v>
+      </c>
+      <c r="BJ8" s="1">
+        <v>213.18299999999999</v>
+      </c>
+      <c r="BK8" s="1">
+        <v>179.99799999999999</v>
+      </c>
+      <c r="BL8" s="1">
+        <v>209.32400000000001</v>
+      </c>
+      <c r="BM8" s="1">
+        <v>453.69799999999998</v>
+      </c>
+      <c r="BN8" s="1">
+        <v>196.25299999999999</v>
+      </c>
+      <c r="BO8" s="1">
+        <v>159.506</v>
+      </c>
+      <c r="BP8" s="1">
+        <v>728.904</v>
+      </c>
+      <c r="BQ8" s="1">
+        <v>209.565</v>
+      </c>
+      <c r="BR8" s="1">
+        <v>266.70699999999999</v>
+      </c>
+      <c r="BS8" s="1">
+        <v>248.02099999999999</v>
+      </c>
+      <c r="BT8" s="1">
+        <v>196.72300000000001</v>
+      </c>
+      <c r="BU8" s="1">
+        <v>219.767</v>
+      </c>
+      <c r="BV8" s="1">
+        <v>196.27199999999999</v>
+      </c>
+      <c r="BW8" s="1">
+        <v>1278.6199999999999</v>
+      </c>
+      <c r="BX8" s="1">
+        <v>196.251</v>
+      </c>
+      <c r="BY8" s="1">
+        <v>172.35499999999999</v>
+      </c>
+      <c r="BZ8" s="1">
+        <v>411.68900000000002</v>
+      </c>
+      <c r="CA8" s="1">
+        <v>188.464</v>
+      </c>
+      <c r="CB8" s="1">
+        <v>159.20500000000001</v>
+      </c>
+      <c r="CC8" s="1">
+        <v>187.80199999999999</v>
+      </c>
+      <c r="CD8" s="1">
+        <v>177.58099999999999</v>
+      </c>
+      <c r="CE8" s="1">
+        <v>213.26</v>
+      </c>
+      <c r="CF8" s="1">
+        <v>95.000399999999999</v>
+      </c>
+      <c r="CG8" s="1">
+        <v>205.334</v>
+      </c>
+      <c r="CH8" s="1">
+        <v>245.62899999999999</v>
+      </c>
+      <c r="CI8" s="1">
+        <v>192.17099999999999</v>
+      </c>
+      <c r="CJ8" s="1">
+        <v>172.001</v>
+      </c>
+      <c r="CK8" s="1">
+        <v>195.50200000000001</v>
+      </c>
+      <c r="CL8" s="1">
+        <v>161.19399999999999</v>
+      </c>
+      <c r="CM8" s="1">
+        <v>196.25800000000001</v>
+      </c>
+      <c r="CN8" s="1">
+        <v>171.71199999999999</v>
+      </c>
+      <c r="CO8" s="1">
+        <v>160.47200000000001</v>
+      </c>
+      <c r="CP8" s="1">
+        <v>159.32599999999999</v>
+      </c>
+      <c r="CQ8" s="1">
+        <v>196.251</v>
+      </c>
+      <c r="CR8" s="1">
+        <v>159.12100000000001</v>
+      </c>
+      <c r="CS8" s="1">
+        <v>159.42500000000001</v>
+      </c>
+      <c r="CT8" s="1">
+        <v>159.61500000000001</v>
+      </c>
+      <c r="CU8" s="1">
+        <v>159.52000000000001</v>
+      </c>
+      <c r="CV8" s="1">
+        <v>6.0678700000000001</v>
+      </c>
+      <c r="CW8" s="1">
+        <v>159.398</v>
+      </c>
+      <c r="CX8" s="1">
+        <v>284.30599999999998</v>
+      </c>
+      <c r="CY8" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ8" s="1">
+        <v>183.709</v>
+      </c>
+      <c r="DA8" s="1">
+        <v>160.13499999999999</v>
+      </c>
+      <c r="DB8" s="1">
+        <v>253.40199999999999</v>
+      </c>
+      <c r="DC8" s="1">
+        <v>409.05700000000002</v>
+      </c>
+      <c r="DD8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF8" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG8" s="1">
+        <v>0.63285800000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>500</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.998</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>220.22499999999999</v>
+      </c>
+      <c r="F9" s="1">
+        <v>179.976</v>
+      </c>
+      <c r="G9" s="1">
+        <v>154.74</v>
+      </c>
+      <c r="H9" s="1">
+        <v>161.01300000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>159.851</v>
+      </c>
+      <c r="J9" s="1">
+        <v>233.02</v>
+      </c>
+      <c r="K9" s="1">
+        <v>159.67699999999999</v>
+      </c>
+      <c r="L9" s="1">
+        <v>163.648</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N9" s="1">
+        <v>4284.43</v>
+      </c>
+      <c r="O9" s="1">
+        <v>212.43899999999999</v>
+      </c>
+      <c r="P9" s="1">
+        <v>181.75899999999999</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="R9" s="1">
+        <v>197.042</v>
+      </c>
+      <c r="S9" s="1">
+        <v>208.82300000000001</v>
+      </c>
+      <c r="T9" s="1">
+        <v>458.34899999999999</v>
+      </c>
+      <c r="U9" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1274.18</v>
+      </c>
+      <c r="W9" s="1">
+        <v>27060.400000000001</v>
+      </c>
+      <c r="X9" s="1">
+        <v>204.714</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>208.77</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>233.892</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>8442.41</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>115.925</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>208.82599999999999</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>159.91499999999999</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>435.60899999999998</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>161.875</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>12355.5</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>159.89099999999999</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>163.23599999999999</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>289.17</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>231.709</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>159.982</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>357.63799999999998</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>176.017</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>170.17500000000001</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>254.68700000000001</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>19360.400000000001</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>2654.94</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>265.589</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>234.83799999999999</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>230.34700000000001</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>222.78899999999999</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>246.79599999999999</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>285.48700000000002</v>
+      </c>
+      <c r="AZ9" s="1">
+        <v>160.601</v>
+      </c>
+      <c r="BA9" s="1">
+        <v>177.77199999999999</v>
+      </c>
+      <c r="BB9" s="1">
+        <v>189.01</v>
+      </c>
+      <c r="BC9" s="1">
+        <v>159.852</v>
+      </c>
+      <c r="BD9" s="1">
+        <v>171.71199999999999</v>
+      </c>
+      <c r="BE9" s="1">
+        <v>258.06799999999998</v>
+      </c>
+      <c r="BF9" s="1">
+        <v>238.24100000000001</v>
+      </c>
+      <c r="BG9" s="1">
+        <v>263.89600000000002</v>
+      </c>
+      <c r="BH9" s="4">
+        <v>6584820</v>
+      </c>
+      <c r="BI9" s="1">
+        <v>160.25299999999999</v>
+      </c>
+      <c r="BJ9" s="1">
+        <v>222.065</v>
+      </c>
+      <c r="BK9" s="1">
+        <v>184.64</v>
+      </c>
+      <c r="BL9" s="1">
+        <v>222.17599999999999</v>
+      </c>
+      <c r="BM9" s="1">
+        <v>556.66</v>
+      </c>
+      <c r="BN9" s="1">
+        <v>203.83500000000001</v>
+      </c>
+      <c r="BO9" s="1">
+        <v>159.75299999999999</v>
+      </c>
+      <c r="BP9" s="1">
+        <v>815.38699999999994</v>
+      </c>
+      <c r="BQ9" s="1">
+        <v>219.39099999999999</v>
+      </c>
+      <c r="BR9" s="1">
+        <v>289.76400000000001</v>
+      </c>
+      <c r="BS9" s="1">
+        <v>268.94799999999998</v>
+      </c>
+      <c r="BT9" s="1">
+        <v>204.36600000000001</v>
+      </c>
+      <c r="BU9" s="1">
+        <v>231.886</v>
+      </c>
+      <c r="BV9" s="1">
+        <v>203.857</v>
+      </c>
+      <c r="BW9" s="1">
+        <v>1407.83</v>
+      </c>
+      <c r="BX9" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="BY9" s="1">
+        <v>175.548</v>
+      </c>
+      <c r="BZ9" s="1">
+        <v>458.34899999999999</v>
+      </c>
+      <c r="CA9" s="1">
+        <v>194.47900000000001</v>
+      </c>
+      <c r="CB9" s="1">
+        <v>159.602</v>
+      </c>
+      <c r="CC9" s="1">
+        <v>193.82599999999999</v>
+      </c>
+      <c r="CD9" s="1">
+        <v>181.846</v>
+      </c>
+      <c r="CE9" s="1">
+        <v>223.62100000000001</v>
+      </c>
+      <c r="CF9" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="CG9" s="1">
+        <v>214.733</v>
+      </c>
+      <c r="CH9" s="1">
+        <v>290.62700000000001</v>
+      </c>
+      <c r="CI9" s="1">
+        <v>199.30500000000001</v>
+      </c>
+      <c r="CJ9" s="1">
+        <v>172.88499999999999</v>
+      </c>
+      <c r="CK9" s="1">
+        <v>241.33600000000001</v>
+      </c>
+      <c r="CL9" s="1">
+        <v>162.523</v>
+      </c>
+      <c r="CM9" s="1">
+        <v>203.84</v>
+      </c>
+      <c r="CN9" s="1">
+        <v>171.85599999999999</v>
+      </c>
+      <c r="CO9" s="1">
+        <v>161.27699999999999</v>
+      </c>
+      <c r="CP9" s="1">
+        <v>159.66300000000001</v>
+      </c>
+      <c r="CQ9" s="1">
+        <v>203.83199999999999</v>
+      </c>
+      <c r="CR9" s="1">
+        <v>159.56</v>
+      </c>
+      <c r="CS9" s="1">
+        <v>159.71199999999999</v>
+      </c>
+      <c r="CT9" s="1">
+        <v>159.81299999999999</v>
+      </c>
+      <c r="CU9" s="1">
+        <v>159.76</v>
+      </c>
+      <c r="CV9" s="1">
+        <v>6.0882500000000004</v>
+      </c>
+      <c r="CW9" s="1">
+        <v>159.69900000000001</v>
+      </c>
+      <c r="CX9" s="1">
+        <v>318.60000000000002</v>
+      </c>
+      <c r="CY9" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ9" s="1">
+        <v>188.93600000000001</v>
+      </c>
+      <c r="DA9" s="1">
+        <v>160.376</v>
+      </c>
+      <c r="DB9" s="1">
+        <v>271.77600000000001</v>
+      </c>
+      <c r="DC9" s="1">
+        <v>497.04</v>
+      </c>
+      <c r="DD9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF9" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG9" s="1">
+        <v>0.63248899999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>750</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.99866699999999997</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.33333E-3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>226.19900000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>180.78100000000001</v>
+      </c>
+      <c r="G10" s="1">
+        <v>154.74</v>
+      </c>
+      <c r="H10" s="1">
+        <v>161.244</v>
+      </c>
+      <c r="I10" s="1">
+        <v>159.90199999999999</v>
+      </c>
+      <c r="J10" s="1">
+        <v>240.03</v>
+      </c>
+      <c r="K10" s="1">
+        <v>159.78399999999999</v>
+      </c>
+      <c r="L10" s="1">
+        <v>164.68700000000001</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N10" s="1">
+        <v>6372.14</v>
+      </c>
+      <c r="O10" s="1">
+        <v>217.44399999999999</v>
+      </c>
+      <c r="P10" s="1">
+        <v>183.268</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="R10" s="1">
+        <v>201.90100000000001</v>
+      </c>
+      <c r="S10" s="1">
+        <v>213.524</v>
+      </c>
+      <c r="T10" s="1">
+        <v>485.64400000000001</v>
+      </c>
+      <c r="U10" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1622.13</v>
+      </c>
+      <c r="W10" s="1">
+        <v>37035.4</v>
+      </c>
+      <c r="X10" s="1">
+        <v>208.995</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>213.417</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>242.113</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>12643.3</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>115.994</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>213.50800000000001</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>159.947</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>461.42</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>162.19800000000001</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>16165.4</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>159.928</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>163.738</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>301.017</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>239.721</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>159.99</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>394.56099999999998</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>177.83</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>171.828</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>265.29700000000003</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>29020.7</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>3067.61</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>277.22399999999999</v>
+      </c>
+      <c r="AU10" s="1">
+        <v>241.429</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>239.00299999999999</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>228.98</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>255.33099999999999</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>298.274</v>
+      </c>
+      <c r="AZ10" s="1">
+        <v>160.77799999999999</v>
+      </c>
+      <c r="BA10" s="1">
+        <v>179.642</v>
+      </c>
+      <c r="BB10" s="1">
+        <v>189.25</v>
+      </c>
+      <c r="BC10" s="1">
+        <v>159.94</v>
+      </c>
+      <c r="BD10" s="1">
+        <v>171.80799999999999</v>
+      </c>
+      <c r="BE10" s="1">
+        <v>266.298</v>
+      </c>
+      <c r="BF10" s="1">
+        <v>247.85599999999999</v>
+      </c>
+      <c r="BG10" s="1">
+        <v>275.29300000000001</v>
+      </c>
+      <c r="BH10" s="4">
+        <v>14815800</v>
+      </c>
+      <c r="BI10" s="1">
+        <v>160.46100000000001</v>
+      </c>
+      <c r="BJ10" s="1">
+        <v>226.999</v>
+      </c>
+      <c r="BK10" s="1">
+        <v>187.15199999999999</v>
+      </c>
+      <c r="BL10" s="1">
+        <v>229.685</v>
+      </c>
+      <c r="BM10" s="1">
+        <v>627.39800000000002</v>
+      </c>
+      <c r="BN10" s="1">
+        <v>208.047</v>
+      </c>
+      <c r="BO10" s="1">
+        <v>159.83500000000001</v>
+      </c>
+      <c r="BP10" s="1">
+        <v>865.976</v>
+      </c>
+      <c r="BQ10" s="1">
+        <v>224.887</v>
+      </c>
+      <c r="BR10" s="1">
+        <v>303.32</v>
+      </c>
+      <c r="BS10" s="1">
+        <v>281.19</v>
+      </c>
+      <c r="BT10" s="1">
+        <v>208.614</v>
+      </c>
+      <c r="BU10" s="1">
+        <v>238.779</v>
+      </c>
+      <c r="BV10" s="1">
+        <v>208.071</v>
+      </c>
+      <c r="BW10" s="1">
+        <v>1480.91</v>
+      </c>
+      <c r="BX10" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="BY10" s="1">
+        <v>177.233</v>
+      </c>
+      <c r="BZ10" s="1">
+        <v>485.64400000000001</v>
+      </c>
+      <c r="CA10" s="1">
+        <v>197.76900000000001</v>
+      </c>
+      <c r="CB10" s="1">
+        <v>159.73500000000001</v>
+      </c>
+      <c r="CC10" s="1">
+        <v>197.143</v>
+      </c>
+      <c r="CD10" s="1">
+        <v>184.154</v>
+      </c>
+      <c r="CE10" s="1">
+        <v>229.41499999999999</v>
+      </c>
+      <c r="CF10" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="CG10" s="1">
+        <v>220.02099999999999</v>
+      </c>
+      <c r="CH10" s="1">
+        <v>322.92899999999997</v>
+      </c>
+      <c r="CI10" s="1">
+        <v>203.274</v>
+      </c>
+      <c r="CJ10" s="1">
+        <v>173.24100000000001</v>
+      </c>
+      <c r="CK10" s="1">
+        <v>287.142</v>
+      </c>
+      <c r="CL10" s="1">
+        <v>163.23400000000001</v>
+      </c>
+      <c r="CM10" s="1">
+        <v>208.05199999999999</v>
+      </c>
+      <c r="CN10" s="1">
+        <v>171.904</v>
+      </c>
+      <c r="CO10" s="1">
+        <v>161.63300000000001</v>
+      </c>
+      <c r="CP10" s="1">
+        <v>159.77500000000001</v>
+      </c>
+      <c r="CQ10" s="1">
+        <v>208.04400000000001</v>
+      </c>
+      <c r="CR10" s="1">
+        <v>159.70599999999999</v>
+      </c>
+      <c r="CS10" s="1">
+        <v>159.80799999999999</v>
+      </c>
+      <c r="CT10" s="1">
+        <v>159.87700000000001</v>
+      </c>
+      <c r="CU10" s="1">
+        <v>159.84</v>
+      </c>
+      <c r="CV10" s="1">
+        <v>6.0950499999999996</v>
+      </c>
+      <c r="CW10" s="1">
+        <v>159.79900000000001</v>
+      </c>
+      <c r="CX10" s="1">
+        <v>339.16199999999998</v>
+      </c>
+      <c r="CY10" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ10" s="1">
+        <v>191.78100000000001</v>
+      </c>
+      <c r="DA10" s="1">
+        <v>160.45699999999999</v>
+      </c>
+      <c r="DB10" s="1">
+        <v>282.51799999999997</v>
+      </c>
+      <c r="DC10" s="1">
+        <v>556.99699999999996</v>
+      </c>
+      <c r="DD10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF10" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG10" s="1">
+        <v>0.63236599999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:111" x14ac:dyDescent="0.6">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.999</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>230.36799999999999</v>
+      </c>
+      <c r="F11" s="1">
+        <v>181.262</v>
+      </c>
+      <c r="G11" s="1">
+        <v>154.74100000000001</v>
+      </c>
+      <c r="H11" s="1">
+        <v>161.37299999999999</v>
+      </c>
+      <c r="I11" s="1">
+        <v>159.928</v>
+      </c>
+      <c r="J11" s="1">
+        <v>244.93</v>
+      </c>
+      <c r="K11" s="1">
+        <v>159.83799999999999</v>
+      </c>
+      <c r="L11" s="1">
+        <v>165.422</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N11" s="1">
+        <v>8459.85</v>
+      </c>
+      <c r="O11" s="1">
+        <v>220.90700000000001</v>
+      </c>
+      <c r="P11" s="1">
+        <v>184.22</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>210.94399999999999</v>
+      </c>
+      <c r="R11" s="1">
+        <v>205.32</v>
+      </c>
+      <c r="S11" s="1">
+        <v>216.773</v>
+      </c>
+      <c r="T11" s="1">
+        <v>505.01</v>
+      </c>
+      <c r="U11" s="1">
+        <v>210.94300000000001</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1905.13</v>
+      </c>
+      <c r="W11" s="1">
+        <v>45808.6</v>
+      </c>
+      <c r="X11" s="1">
+        <v>211.94300000000001</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>216.62799999999999</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>247.94399999999999</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>16844.3</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>116.042</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>216.74299999999999</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>159.96199999999999</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>479.73399999999998</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>162.38300000000001</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>19381.900000000001</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>159.946</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>164.04499999999999</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>309.358</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>245.40199999999999</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>100</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>159.99299999999999</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>422.81599999999997</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>179.04900000000001</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>172.94</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>272.82299999999998</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>38680.9</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>3383.99</v>
+      </c>
+      <c r="AT11" s="1">
+        <v>285.476</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>245.98</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>245.14500000000001</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>233.3</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>261.33</v>
+      </c>
+      <c r="AY11" s="1">
+        <v>307.34399999999999</v>
+      </c>
+      <c r="AZ11" s="1">
+        <v>160.88200000000001</v>
+      </c>
+      <c r="BA11" s="1">
+        <v>180.89500000000001</v>
+      </c>
+      <c r="BB11" s="1">
+        <v>189.40799999999999</v>
+      </c>
+      <c r="BC11" s="1">
+        <v>159.98500000000001</v>
+      </c>
+      <c r="BD11" s="1">
+        <v>171.85599999999999</v>
+      </c>
+      <c r="BE11" s="1">
+        <v>271.99900000000002</v>
+      </c>
+      <c r="BF11" s="1">
+        <v>254.67699999999999</v>
+      </c>
+      <c r="BG11" s="1">
+        <v>283.38</v>
+      </c>
+      <c r="BH11" s="4">
+        <v>26339200</v>
+      </c>
+      <c r="BI11" s="1">
+        <v>160.59200000000001</v>
+      </c>
+      <c r="BJ11" s="1">
+        <v>230.39599999999999</v>
+      </c>
+      <c r="BK11" s="1">
+        <v>188.85599999999999</v>
+      </c>
+      <c r="BL11" s="1">
+        <v>235.01</v>
+      </c>
+      <c r="BM11" s="1">
+        <v>682.97199999999998</v>
+      </c>
+      <c r="BN11" s="1">
+        <v>210.946</v>
+      </c>
+      <c r="BO11" s="1">
+        <v>159.876</v>
+      </c>
+      <c r="BP11" s="1">
+        <v>901.87</v>
+      </c>
+      <c r="BQ11" s="1">
+        <v>228.685</v>
+      </c>
+      <c r="BR11" s="1">
+        <v>312.971</v>
+      </c>
+      <c r="BS11" s="1">
+        <v>289.875</v>
+      </c>
+      <c r="BT11" s="1">
+        <v>211.53899999999999</v>
+      </c>
+      <c r="BU11" s="1">
+        <v>243.59100000000001</v>
+      </c>
+      <c r="BV11" s="1">
+        <v>210.97200000000001</v>
+      </c>
+      <c r="BW11" s="1">
+        <v>1531.77</v>
+      </c>
+      <c r="BX11" s="1">
+        <v>210.94399999999999</v>
+      </c>
+      <c r="BY11" s="1">
+        <v>178.35900000000001</v>
+      </c>
+      <c r="BZ11" s="1">
+        <v>505.01</v>
+      </c>
+      <c r="CA11" s="1">
+        <v>200.012</v>
+      </c>
+      <c r="CB11" s="1">
+        <v>159.80099999999999</v>
+      </c>
+      <c r="CC11" s="1">
+        <v>199.41499999999999</v>
+      </c>
+      <c r="CD11" s="1">
+        <v>185.71799999999999</v>
+      </c>
+      <c r="CE11" s="1">
+        <v>233.41900000000001</v>
+      </c>
+      <c r="CF11" s="1">
+        <v>95.000500000000002</v>
+      </c>
+      <c r="CG11" s="1">
+        <v>223.68799999999999</v>
+      </c>
+      <c r="CH11" s="1">
+        <v>348.93</v>
+      </c>
+      <c r="CI11" s="1">
+        <v>206.00899999999999</v>
+      </c>
+      <c r="CJ11" s="1">
+        <v>173.441</v>
+      </c>
+      <c r="CK11" s="1">
+        <v>332.94</v>
+      </c>
+      <c r="CL11" s="1">
+        <v>163.71299999999999</v>
+      </c>
+      <c r="CM11" s="1">
+        <v>210.952</v>
+      </c>
+      <c r="CN11" s="1">
+        <v>171.928</v>
+      </c>
+      <c r="CO11" s="1">
+        <v>161.846</v>
+      </c>
+      <c r="CP11" s="1">
+        <v>159.83099999999999</v>
+      </c>
+      <c r="CQ11" s="1">
+        <v>210.94399999999999</v>
+      </c>
+      <c r="CR11" s="1">
+        <v>159.78</v>
+      </c>
+      <c r="CS11" s="1">
+        <v>159.85599999999999</v>
+      </c>
+      <c r="CT11" s="1">
+        <v>159.90899999999999</v>
+      </c>
+      <c r="CU11" s="1">
+        <v>159.88</v>
+      </c>
+      <c r="CV11" s="1">
+        <v>6.0984400000000001</v>
+      </c>
+      <c r="CW11" s="1">
+        <v>159.84899999999999</v>
+      </c>
+      <c r="CX11" s="1">
+        <v>353.95299999999997</v>
+      </c>
+      <c r="CY11" s="1">
+        <v>160</v>
+      </c>
+      <c r="CZ11" s="1">
+        <v>193.71600000000001</v>
+      </c>
+      <c r="DA11" s="1">
+        <v>160.49700000000001</v>
+      </c>
+      <c r="DB11" s="1">
+        <v>290.13799999999998</v>
+      </c>
+      <c r="DC11" s="1">
+        <v>603.86300000000006</v>
+      </c>
+      <c r="DD11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="DE11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DF11" s="1">
+        <v>41</v>
+      </c>
+      <c r="DG11" s="1">
+        <v>0.63230500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/tool/PMP/old/PMP_Sample.xlsx
+++ b/tool/PMP/old/PMP_Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21658CCC-64E8-48E7-B82B-CCF6E58DCDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F3408A-BC73-495E-A5A0-8AC7685CE3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="5" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
   </bookViews>
   <sheets>
     <sheet name="Rain" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="25020230PMP" sheetId="5" r:id="rId3"/>
     <sheet name="25020230" sheetId="3" r:id="rId4"/>
     <sheet name="25020230BestFit" sheetId="4" r:id="rId5"/>
+    <sheet name="25020260PMP" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="97">
   <si>
     <t>Year / Station</t>
   </si>
@@ -318,6 +320,21 @@
   <si>
     <t>R.HydroTools-Levy_stable</t>
   </si>
+  <si>
+    <t>prob_l</t>
+  </si>
+  <si>
+    <t>prob_g</t>
+  </si>
+  <si>
+    <t>25020260_1969_2009</t>
+  </si>
+  <si>
+    <t>R.HydroTools-Invgauss</t>
+  </si>
+  <si>
+    <t>R.HydroTools-powernorm</t>
+  </si>
 </sst>
 </file>
 
@@ -358,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,6 +391,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,7 +436,7 @@
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>2502023</c:v>
+              <c:v>25020230</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -461,7 +485,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2502023-Excel-Gumbel</c:v>
+                  <c:v>25020230-Excel-Gumbel</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8584,6 +8608,928 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
+          <c:f>'25020260PMP'!$B$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>25020260</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-Excel-Gumbel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>220</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-R.HydroTools-Gumbel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>126.64700000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>148.64699999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>166.56700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>189.208</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>206.00399999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>222.67599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-R.HydroTools-powernorm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$E$4:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>116.089</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138.012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>153.345</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>170.226</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>181.36799999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>191.523</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-R.HydroTools-Invgauss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$D$4:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>114.58799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>137.27699999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>154.149</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>173.86199999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>187.59200000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200.636</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="489679200"/>
+        <c:axId val="489674880"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="489679200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="489674880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="489674880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="489679200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -8625,6 +9571,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9696,6 +10682,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -9764,6 +11266,49 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>117311</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>207065</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2041663</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>157369</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFA797B2-436E-49BB-B69B-CA4FA5085B83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -10166,7 +11711,7 @@
         <v>135</v>
       </c>
       <c r="Q2" s="1" t="str">
-        <f>_xlfn.CONCAT(A2,",",C2)</f>
+        <f t="shared" ref="Q2:Q11" si="0">_xlfn.CONCAT(A2,",",D2)</f>
         <v>1959,</v>
       </c>
     </row>
@@ -10181,7 +11726,7 @@
         <v>100</v>
       </c>
       <c r="Q3" s="1" t="str">
-        <f t="shared" ref="Q3:Q52" si="0">_xlfn.CONCAT(A3,",",C3)</f>
+        <f t="shared" si="0"/>
         <v>1960,</v>
       </c>
     </row>
@@ -10316,8 +11861,8 @@
         <v>97</v>
       </c>
       <c r="Q12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1969,112</v>
+        <f>_xlfn.CONCAT(A12,",",D12)</f>
+        <v>1969,132</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.6">
@@ -10346,8 +11891,8 @@
         <v>133</v>
       </c>
       <c r="Q13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1970,100</v>
+        <f t="shared" ref="Q13:Q52" si="1">_xlfn.CONCAT(A13,",",D13)</f>
+        <v>1970,115</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.6">
@@ -10376,8 +11921,8 @@
         <v>103</v>
       </c>
       <c r="Q14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1971,85</v>
+        <f t="shared" si="1"/>
+        <v>1971,100</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.6">
@@ -10409,8 +11954,8 @@
         <v>47</v>
       </c>
       <c r="Q15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1972,72</v>
+        <f t="shared" si="1"/>
+        <v>1972,97</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.6">
@@ -10445,8 +11990,8 @@
         <v>70</v>
       </c>
       <c r="Q16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1973,128</v>
+        <f t="shared" si="1"/>
+        <v>1973,116</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.6">
@@ -10481,8 +12026,8 @@
         <v>90</v>
       </c>
       <c r="Q17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1974,155</v>
+        <f t="shared" si="1"/>
+        <v>1974,92</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.6">
@@ -10517,8 +12062,8 @@
         <v>140</v>
       </c>
       <c r="Q18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1975,172</v>
+        <f t="shared" si="1"/>
+        <v>1975,104</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.6">
@@ -10553,8 +12098,8 @@
         <v>151</v>
       </c>
       <c r="Q19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1976,123</v>
+        <f t="shared" si="1"/>
+        <v>1976,82</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.6">
@@ -10592,8 +12137,8 @@
         <v>102</v>
       </c>
       <c r="Q20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1977,115</v>
+        <f t="shared" si="1"/>
+        <v>1977,90</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.6">
@@ -10631,8 +12176,8 @@
         <v>97</v>
       </c>
       <c r="Q21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1978,170</v>
+        <f t="shared" si="1"/>
+        <v>1978,130</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.6">
@@ -10673,8 +12218,8 @@
         <v>140</v>
       </c>
       <c r="Q22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1979,136</v>
+        <f t="shared" si="1"/>
+        <v>1979,116</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.6">
@@ -10715,8 +12260,8 @@
         <v>80</v>
       </c>
       <c r="Q23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1980,105</v>
+        <f t="shared" si="1"/>
+        <v>1980,130</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.6">
@@ -10763,8 +12308,8 @@
         <v>99</v>
       </c>
       <c r="Q24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1981,100</v>
+        <f t="shared" si="1"/>
+        <v>1981,78</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.6">
@@ -10811,8 +12356,8 @@
         <v>112</v>
       </c>
       <c r="Q25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1982,80</v>
+        <f t="shared" si="1"/>
+        <v>1982,150</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.6">
@@ -10859,8 +12404,8 @@
         <v>120</v>
       </c>
       <c r="Q26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1983,149</v>
+        <f t="shared" si="1"/>
+        <v>1983,103</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.6">
@@ -10907,8 +12452,8 @@
         <v>84</v>
       </c>
       <c r="Q27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1984,145</v>
+        <f t="shared" si="1"/>
+        <v>1984,150</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.6">
@@ -10955,8 +12500,8 @@
         <v>100</v>
       </c>
       <c r="Q28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1985,110</v>
+        <f t="shared" si="1"/>
+        <v>1985,98</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.6">
@@ -11003,8 +12548,8 @@
         <v>75</v>
       </c>
       <c r="Q29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1986,52</v>
+        <f t="shared" si="1"/>
+        <v>1986,55</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.6">
@@ -11048,8 +12593,8 @@
         <v>123</v>
       </c>
       <c r="Q30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1987,170</v>
+        <f t="shared" si="1"/>
+        <v>1987,90</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.6">
@@ -11099,8 +12644,8 @@
         <v>85</v>
       </c>
       <c r="Q31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1988,105</v>
+        <f t="shared" si="1"/>
+        <v>1988,88</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.6">
@@ -11150,8 +12695,8 @@
         <v>67</v>
       </c>
       <c r="Q32" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1989,115</v>
+        <f t="shared" si="1"/>
+        <v>1989,77</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.6">
@@ -11201,8 +12746,8 @@
         <v>68</v>
       </c>
       <c r="Q33" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1990,63</v>
+        <f t="shared" si="1"/>
+        <v>1990,93</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.6">
@@ -11249,8 +12794,8 @@
         <v>108</v>
       </c>
       <c r="Q34" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1991,130</v>
+        <f t="shared" si="1"/>
+        <v>1991,90</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.6">
@@ -11300,8 +12845,8 @@
         <v>106</v>
       </c>
       <c r="Q35" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1992,147</v>
+        <f t="shared" si="1"/>
+        <v>1992,105</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.6">
@@ -11351,8 +12896,8 @@
         <v>66</v>
       </c>
       <c r="Q36" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1993,78</v>
+        <f t="shared" si="1"/>
+        <v>1993,120</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.6">
@@ -11396,8 +12941,8 @@
         <v>95</v>
       </c>
       <c r="Q37" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1994,84</v>
+        <f t="shared" si="1"/>
+        <v>1994,100</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.6">
@@ -11444,8 +12989,8 @@
         <v>81</v>
       </c>
       <c r="Q38" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1995,98</v>
+        <f t="shared" si="1"/>
+        <v>1995,70</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.6">
@@ -11492,8 +13037,8 @@
         <v>147</v>
       </c>
       <c r="Q39" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1996,106</v>
+        <f t="shared" si="1"/>
+        <v>1996,150</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.6">
@@ -11540,8 +13085,8 @@
         <v>57</v>
       </c>
       <c r="Q40" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1997,74</v>
+        <f t="shared" si="1"/>
+        <v>1997,70</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.6">
@@ -11588,8 +13133,8 @@
         <v>103</v>
       </c>
       <c r="Q41" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1998,98</v>
+        <f t="shared" si="1"/>
+        <v>1998,124</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.6">
@@ -11636,8 +13181,8 @@
         <v>114</v>
       </c>
       <c r="Q42" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>1999,152</v>
+        <f t="shared" si="1"/>
+        <v>1999,130</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.6">
@@ -11684,8 +13229,8 @@
         <v>89</v>
       </c>
       <c r="Q43" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2000,97</v>
+        <f t="shared" si="1"/>
+        <v>2000,120</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.6">
@@ -11732,8 +13277,8 @@
         <v>56</v>
       </c>
       <c r="Q44" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2001,97</v>
+        <f t="shared" si="1"/>
+        <v>2001,70</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.6">
@@ -11777,8 +13322,8 @@
         <v>105</v>
       </c>
       <c r="Q45" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2002,93</v>
+        <f t="shared" si="1"/>
+        <v>2002,96</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.6">
@@ -11819,8 +13364,8 @@
         <v>27</v>
       </c>
       <c r="Q46" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2003,93</v>
+        <f t="shared" si="1"/>
+        <v>2003,271</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.6">
@@ -11864,8 +13409,8 @@
         <v>88</v>
       </c>
       <c r="Q47" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2004,112</v>
+        <f t="shared" si="1"/>
+        <v>2004,90</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.6">
@@ -11906,8 +13451,8 @@
         <v>119</v>
       </c>
       <c r="Q48" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2005,75</v>
+        <f t="shared" si="1"/>
+        <v>2005,106</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.6">
@@ -11948,8 +13493,8 @@
         <v>134</v>
       </c>
       <c r="Q49" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2006,137</v>
+        <f t="shared" si="1"/>
+        <v>2006,125</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.6">
@@ -11990,8 +13535,8 @@
         <v>68</v>
       </c>
       <c r="Q50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2007,149</v>
+        <f t="shared" si="1"/>
+        <v>2007,90</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.6">
@@ -12032,8 +13577,8 @@
         <v>111</v>
       </c>
       <c r="Q51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2008,138</v>
+        <f t="shared" si="1"/>
+        <v>2008,121</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.6">
@@ -12074,8 +13619,8 @@
         <v>96</v>
       </c>
       <c r="Q52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>2009,107</v>
+        <f t="shared" si="1"/>
+        <v>2009,90</v>
       </c>
     </row>
   </sheetData>
@@ -12089,315 +13634,317 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="14" width="8.73046875" style="3" customWidth="1"/>
+    <col min="2" max="12" width="9.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.06640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="9.1328125" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.06640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2">
-        <v>2502023</v>
-      </c>
-      <c r="C1" s="2">
-        <v>2502026</v>
-      </c>
-      <c r="D1" s="2">
-        <v>2502028</v>
-      </c>
-      <c r="E1" s="2">
-        <v>2502069</v>
-      </c>
-      <c r="F1" s="2">
-        <v>2802008</v>
-      </c>
-      <c r="G1" s="2">
-        <v>2802023</v>
-      </c>
-      <c r="H1" s="2">
-        <v>2802044</v>
-      </c>
-      <c r="I1" s="2">
-        <v>2802060</v>
-      </c>
-      <c r="J1" s="2">
-        <v>2802508</v>
-      </c>
-      <c r="K1" s="2">
-        <v>2802509</v>
-      </c>
-      <c r="L1" s="2">
-        <v>2803504</v>
-      </c>
-      <c r="M1" s="2">
-        <v>2804031</v>
-      </c>
-      <c r="N1" s="2">
-        <v>2804035</v>
+      <c r="B1" s="8">
+        <v>25020230</v>
+      </c>
+      <c r="C1" s="8">
+        <v>25020260</v>
+      </c>
+      <c r="D1" s="8">
+        <v>25020280</v>
+      </c>
+      <c r="E1" s="8">
+        <v>25020690</v>
+      </c>
+      <c r="F1" s="8">
+        <v>28020080</v>
+      </c>
+      <c r="G1" s="8">
+        <v>28020230</v>
+      </c>
+      <c r="H1" s="8">
+        <v>28020440</v>
+      </c>
+      <c r="I1" s="8">
+        <v>28020600</v>
+      </c>
+      <c r="J1" s="8">
+        <v>28025080</v>
+      </c>
+      <c r="K1" s="8">
+        <v>28025090</v>
+      </c>
+      <c r="L1" s="8">
+        <v>28035040</v>
+      </c>
+      <c r="M1" s="8">
+        <v>28040310</v>
+      </c>
+      <c r="N1" s="8">
+        <v>28040350</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" s="3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A2" s="7">
         <v>2.33</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="7">
         <v>103</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="7">
         <v>107</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="7">
         <v>111</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="7">
         <v>92</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="7">
         <v>102</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="7">
         <v>102</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="7">
         <v>92</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="7">
         <v>91</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="7">
         <v>100</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="7">
         <v>100</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="7">
         <v>89</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="7">
         <v>98</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="7">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A3" s="7">
         <v>5</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="7">
         <v>132</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="7">
         <v>133</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="7">
         <v>149</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="7">
         <v>117</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="7">
         <v>136</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="7">
         <v>136</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="7">
         <v>114</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="7">
         <v>111</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="7">
         <v>121</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="7">
         <v>117</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="7">
         <v>112</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="7">
         <v>120</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="7">
         <v>119</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A4" s="7">
         <v>10</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="7">
         <v>155</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="7">
         <v>154</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="7">
         <v>179</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="7">
         <v>137</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="7">
         <v>164</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="7">
         <v>165</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="7">
         <v>132</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="7">
         <v>127</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="7">
         <v>138</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="7">
         <v>130</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="7">
         <v>131</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="7">
         <v>138</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="7">
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A5" s="7">
         <v>25</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="7">
         <v>184</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="7">
         <v>181</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="7">
         <v>218</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="7">
         <v>162</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="7">
         <v>199</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="7">
         <v>201</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="7">
         <v>155</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="7">
         <v>148</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="7">
         <v>159</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="7">
         <v>148</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="7">
         <v>155</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="7">
         <v>161</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="7">
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A6" s="7">
         <v>50</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="7">
         <v>205</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="7">
         <v>201</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="7">
         <v>247</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="7">
         <v>180</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="7">
         <v>225</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="7">
         <v>227</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="7">
         <v>172</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="7">
         <v>163</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="7">
         <v>175</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="7">
         <v>161</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="7">
         <v>173</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="7">
         <v>178</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="7">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.6">
+      <c r="A7" s="7">
         <v>100</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="7">
         <v>226</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="7">
         <v>220</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="7">
         <v>276</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="7">
         <v>199</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="7">
         <v>251</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="7">
         <v>254</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="7">
         <v>189</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="7">
         <v>178</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="7">
         <v>190</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="7">
         <v>174</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="7">
         <v>190</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="7">
         <v>195</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="7">
         <v>196</v>
       </c>
     </row>
@@ -12432,7 +13979,7 @@
     </row>
     <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B2" s="5">
-        <v>2502023</v>
+        <v>25020230</v>
       </c>
       <c r="C2" s="5">
         <v>25020230</v>
@@ -12450,7 +13997,7 @@
       </c>
       <c r="B3" s="5" t="str">
         <f>_xlfn.CONCAT(B2,"-",B1)</f>
-        <v>2502023-Excel-Gumbel</v>
+        <v>25020230-Excel-Gumbel</v>
       </c>
       <c r="C3" s="5" t="str">
         <f t="shared" ref="C3:E3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
@@ -15286,4 +16833,2261 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2165B25E-5849-4D0E-BE2E-04E16316E776}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="34.86328125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="5">
+        <v>25020260</v>
+      </c>
+      <c r="C2" s="5">
+        <v>25020260</v>
+      </c>
+      <c r="D2" s="5">
+        <v>25020260</v>
+      </c>
+      <c r="E2" s="5">
+        <v>25020260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,"-",B1)</f>
+        <v>25020260-Excel-Gumbel</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <f t="shared" ref="C3:E3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
+        <v>25020260-R.HydroTools-Gumbel</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>25020260-R.HydroTools-Invgauss</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>25020260-R.HydroTools-powernorm</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="B4" s="6">
+        <v>107</v>
+      </c>
+      <c r="C4" s="6">
+        <v>126.64700000000001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>114.58799999999999</v>
+      </c>
+      <c r="E4" s="6">
+        <v>116.089</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6">
+        <v>133</v>
+      </c>
+      <c r="C5" s="6">
+        <v>148.64699999999999</v>
+      </c>
+      <c r="D5" s="6">
+        <v>137.27699999999999</v>
+      </c>
+      <c r="E5" s="6">
+        <v>138.012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6">
+        <v>154</v>
+      </c>
+      <c r="C6" s="6">
+        <v>166.56700000000001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>154.149</v>
+      </c>
+      <c r="E6" s="6">
+        <v>153.345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
+        <v>25</v>
+      </c>
+      <c r="B7" s="6">
+        <v>181</v>
+      </c>
+      <c r="C7" s="6">
+        <v>189.208</v>
+      </c>
+      <c r="D7" s="6">
+        <v>173.86199999999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>170.226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6">
+        <v>201</v>
+      </c>
+      <c r="C8" s="6">
+        <v>206.00399999999999</v>
+      </c>
+      <c r="D8" s="6">
+        <v>187.59200000000001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>181.36799999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
+        <v>100</v>
+      </c>
+      <c r="B9" s="6">
+        <v>220</v>
+      </c>
+      <c r="C9" s="6">
+        <v>222.67599999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>200.636</v>
+      </c>
+      <c r="E9" s="6">
+        <v>191.523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D13" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C93394-4CAA-4D45-B4FF-F549FD11CBF9}">
+  <dimension ref="A1:BJ11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" t="s">
+        <v>52</v>
+      </c>
+      <c r="W1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>84</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>85</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>86</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>4</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2.33</v>
+      </c>
+      <c r="C2">
+        <v>0.57081499999999996</v>
+      </c>
+      <c r="D2">
+        <v>0.42918499999999998</v>
+      </c>
+      <c r="E2">
+        <v>116.04900000000001</v>
+      </c>
+      <c r="F2">
+        <v>113.998</v>
+      </c>
+      <c r="G2">
+        <v>116.154</v>
+      </c>
+      <c r="H2">
+        <v>118.252</v>
+      </c>
+      <c r="I2">
+        <v>114.59699999999999</v>
+      </c>
+      <c r="J2">
+        <v>116.154</v>
+      </c>
+      <c r="K2">
+        <v>103.474</v>
+      </c>
+      <c r="L2">
+        <v>118.03700000000001</v>
+      </c>
+      <c r="M2">
+        <v>116.15900000000001</v>
+      </c>
+      <c r="N2">
+        <v>116.262</v>
+      </c>
+      <c r="O2">
+        <v>115.35899999999999</v>
+      </c>
+      <c r="P2">
+        <v>116.154</v>
+      </c>
+      <c r="Q2">
+        <v>104.44799999999999</v>
+      </c>
+      <c r="R2">
+        <v>111.922</v>
+      </c>
+      <c r="S2">
+        <v>114.839</v>
+      </c>
+      <c r="T2">
+        <v>106.508</v>
+      </c>
+      <c r="U2">
+        <v>123.30500000000001</v>
+      </c>
+      <c r="V2">
+        <v>122.52</v>
+      </c>
+      <c r="W2">
+        <v>112.886</v>
+      </c>
+      <c r="X2">
+        <v>110.556</v>
+      </c>
+      <c r="Y2">
+        <v>112.488</v>
+      </c>
+      <c r="Z2">
+        <v>117.17400000000001</v>
+      </c>
+      <c r="AA2">
+        <v>116.056</v>
+      </c>
+      <c r="AB2">
+        <v>114.58799999999999</v>
+      </c>
+      <c r="AC2">
+        <v>59.181800000000003</v>
+      </c>
+      <c r="AD2">
+        <v>116.297</v>
+      </c>
+      <c r="AE2">
+        <v>51.998699999999999</v>
+      </c>
+      <c r="AF2">
+        <v>113.241</v>
+      </c>
+      <c r="AG2">
+        <v>116.12</v>
+      </c>
+      <c r="AH2">
+        <v>111.274</v>
+      </c>
+      <c r="AI2">
+        <v>118.17</v>
+      </c>
+      <c r="AJ2">
+        <v>118.32899999999999</v>
+      </c>
+      <c r="AK2">
+        <v>117.61</v>
+      </c>
+      <c r="AL2">
+        <v>116.354</v>
+      </c>
+      <c r="AM2">
+        <v>115.875</v>
+      </c>
+      <c r="AN2">
+        <v>115.572</v>
+      </c>
+      <c r="AO2">
+        <v>111.015</v>
+      </c>
+      <c r="AP2">
+        <v>115.605</v>
+      </c>
+      <c r="AQ2">
+        <v>114.21599999999999</v>
+      </c>
+      <c r="AR2">
+        <v>116.643</v>
+      </c>
+      <c r="AS2">
+        <v>118.252</v>
+      </c>
+      <c r="AT2">
+        <v>103.474</v>
+      </c>
+      <c r="AU2">
+        <v>117.188</v>
+      </c>
+      <c r="AV2">
+        <v>88.744100000000003</v>
+      </c>
+      <c r="AW2">
+        <v>116.089</v>
+      </c>
+      <c r="AX2">
+        <v>115.04</v>
+      </c>
+      <c r="AY2">
+        <v>116.26</v>
+      </c>
+      <c r="AZ2">
+        <v>89.5672</v>
+      </c>
+      <c r="BA2">
+        <v>118.245</v>
+      </c>
+      <c r="BB2">
+        <v>118.252</v>
+      </c>
+      <c r="BC2">
+        <v>106.587</v>
+      </c>
+      <c r="BD2">
+        <v>116.96</v>
+      </c>
+      <c r="BE2">
+        <v>126.64700000000001</v>
+      </c>
+      <c r="BF2">
+        <v>109.497</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI2">
+        <v>41</v>
+      </c>
+      <c r="BJ2">
+        <v>0.729209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0.8</v>
+      </c>
+      <c r="D3">
+        <v>0.2</v>
+      </c>
+      <c r="E3">
+        <v>137.554</v>
+      </c>
+      <c r="F3">
+        <v>136.5</v>
+      </c>
+      <c r="G3">
+        <v>137.661</v>
+      </c>
+      <c r="H3">
+        <v>138.31299999999999</v>
+      </c>
+      <c r="I3">
+        <v>132.804</v>
+      </c>
+      <c r="J3">
+        <v>137.661</v>
+      </c>
+      <c r="K3">
+        <v>149.94</v>
+      </c>
+      <c r="L3">
+        <v>138.17599999999999</v>
+      </c>
+      <c r="M3">
+        <v>137.661</v>
+      </c>
+      <c r="N3">
+        <v>137.62700000000001</v>
+      </c>
+      <c r="O3">
+        <v>136.64699999999999</v>
+      </c>
+      <c r="P3">
+        <v>137.661</v>
+      </c>
+      <c r="Q3">
+        <v>146.90799999999999</v>
+      </c>
+      <c r="R3">
+        <v>141.779</v>
+      </c>
+      <c r="S3">
+        <v>137.16499999999999</v>
+      </c>
+      <c r="T3">
+        <v>122.251</v>
+      </c>
+      <c r="U3">
+        <v>142.34299999999999</v>
+      </c>
+      <c r="V3">
+        <v>137.69200000000001</v>
+      </c>
+      <c r="W3">
+        <v>134.61699999999999</v>
+      </c>
+      <c r="X3">
+        <v>133.82599999999999</v>
+      </c>
+      <c r="Y3">
+        <v>137.125</v>
+      </c>
+      <c r="Z3">
+        <v>134.50299999999999</v>
+      </c>
+      <c r="AA3">
+        <v>137.44300000000001</v>
+      </c>
+      <c r="AB3">
+        <v>137.27699999999999</v>
+      </c>
+      <c r="AC3">
+        <v>162.833</v>
+      </c>
+      <c r="AD3">
+        <v>137.55699999999999</v>
+      </c>
+      <c r="AE3">
+        <v>51.998699999999999</v>
+      </c>
+      <c r="AF3">
+        <v>138.928</v>
+      </c>
+      <c r="AG3">
+        <v>132.453</v>
+      </c>
+      <c r="AH3">
+        <v>135.17500000000001</v>
+      </c>
+      <c r="AI3">
+        <v>139.798</v>
+      </c>
+      <c r="AJ3">
+        <v>138.553</v>
+      </c>
+      <c r="AK3">
+        <v>135.97399999999999</v>
+      </c>
+      <c r="AL3">
+        <v>137.62</v>
+      </c>
+      <c r="AM3">
+        <v>137.94800000000001</v>
+      </c>
+      <c r="AN3">
+        <v>136.88</v>
+      </c>
+      <c r="AO3">
+        <v>132.94800000000001</v>
+      </c>
+      <c r="AP3">
+        <v>137.965</v>
+      </c>
+      <c r="AQ3">
+        <v>137.15299999999999</v>
+      </c>
+      <c r="AR3">
+        <v>137.477</v>
+      </c>
+      <c r="AS3">
+        <v>138.31299999999999</v>
+      </c>
+      <c r="AT3">
+        <v>149.94</v>
+      </c>
+      <c r="AU3">
+        <v>137.94399999999999</v>
+      </c>
+      <c r="AV3">
+        <v>153.33000000000001</v>
+      </c>
+      <c r="AW3">
+        <v>138.012</v>
+      </c>
+      <c r="AX3">
+        <v>137.82499999999999</v>
+      </c>
+      <c r="AY3">
+        <v>137.62700000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>91.693600000000004</v>
+      </c>
+      <c r="BA3">
+        <v>138.303</v>
+      </c>
+      <c r="BB3">
+        <v>138.31299999999999</v>
+      </c>
+      <c r="BC3">
+        <v>126.402</v>
+      </c>
+      <c r="BD3">
+        <v>138.52199999999999</v>
+      </c>
+      <c r="BE3">
+        <v>148.64699999999999</v>
+      </c>
+      <c r="BF3">
+        <v>133.857</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI3">
+        <v>41</v>
+      </c>
+      <c r="BJ3">
+        <v>0.67232000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>0.9</v>
+      </c>
+      <c r="D4">
+        <v>0.1</v>
+      </c>
+      <c r="E4">
+        <v>153.08699999999999</v>
+      </c>
+      <c r="F4">
+        <v>153.73099999999999</v>
+      </c>
+      <c r="G4">
+        <v>153.017</v>
+      </c>
+      <c r="H4">
+        <v>151.62</v>
+      </c>
+      <c r="I4">
+        <v>147.31399999999999</v>
+      </c>
+      <c r="J4">
+        <v>153.017</v>
+      </c>
+      <c r="K4">
+        <v>192.12100000000001</v>
+      </c>
+      <c r="L4">
+        <v>151.673</v>
+      </c>
+      <c r="M4">
+        <v>153.012</v>
+      </c>
+      <c r="N4">
+        <v>152.85900000000001</v>
+      </c>
+      <c r="O4">
+        <v>154.03200000000001</v>
+      </c>
+      <c r="P4">
+        <v>153.017</v>
+      </c>
+      <c r="Q4">
+        <v>185.45</v>
+      </c>
+      <c r="R4">
+        <v>165.80699999999999</v>
+      </c>
+      <c r="S4">
+        <v>154.80799999999999</v>
+      </c>
+      <c r="T4">
+        <v>140.196</v>
+      </c>
+      <c r="U4">
+        <v>152.94300000000001</v>
+      </c>
+      <c r="V4">
+        <v>146.13900000000001</v>
+      </c>
+      <c r="W4">
+        <v>152.316</v>
+      </c>
+      <c r="X4">
+        <v>153.15100000000001</v>
+      </c>
+      <c r="Y4">
+        <v>155.35599999999999</v>
+      </c>
+      <c r="Z4">
+        <v>148.34</v>
+      </c>
+      <c r="AA4">
+        <v>152.791</v>
+      </c>
+      <c r="AB4">
+        <v>154.149</v>
+      </c>
+      <c r="AC4">
+        <v>1079.42</v>
+      </c>
+      <c r="AD4">
+        <v>152.69499999999999</v>
+      </c>
+      <c r="AE4">
+        <v>51.998699999999999</v>
+      </c>
+      <c r="AF4">
+        <v>158.48400000000001</v>
+      </c>
+      <c r="AG4">
+        <v>147.279</v>
+      </c>
+      <c r="AH4">
+        <v>156.87100000000001</v>
+      </c>
+      <c r="AI4">
+        <v>154.14500000000001</v>
+      </c>
+      <c r="AJ4">
+        <v>151.89500000000001</v>
+      </c>
+      <c r="AK4">
+        <v>149.49799999999999</v>
+      </c>
+      <c r="AL4">
+        <v>152.75399999999999</v>
+      </c>
+      <c r="AM4">
+        <v>153.483</v>
+      </c>
+      <c r="AN4">
+        <v>154.44900000000001</v>
+      </c>
+      <c r="AO4">
+        <v>152.04400000000001</v>
+      </c>
+      <c r="AP4">
+        <v>153.95599999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>154.995</v>
+      </c>
+      <c r="AR4">
+        <v>152.29</v>
+      </c>
+      <c r="AS4">
+        <v>151.62</v>
+      </c>
+      <c r="AT4">
+        <v>192.12100000000001</v>
+      </c>
+      <c r="AU4">
+        <v>152.25200000000001</v>
+      </c>
+      <c r="AV4">
+        <v>238.36</v>
+      </c>
+      <c r="AW4">
+        <v>153.345</v>
+      </c>
+      <c r="AX4">
+        <v>154.07</v>
+      </c>
+      <c r="AY4">
+        <v>152.86199999999999</v>
+      </c>
+      <c r="AZ4">
+        <v>93.209699999999998</v>
+      </c>
+      <c r="BA4">
+        <v>151.61000000000001</v>
+      </c>
+      <c r="BB4">
+        <v>151.62</v>
+      </c>
+      <c r="BC4">
+        <v>147.43</v>
+      </c>
+      <c r="BD4">
+        <v>153.04900000000001</v>
+      </c>
+      <c r="BE4">
+        <v>166.56700000000001</v>
+      </c>
+      <c r="BF4">
+        <v>157.65</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI4">
+        <v>41</v>
+      </c>
+      <c r="BJ4">
+        <v>0.65132199999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>0.96</v>
+      </c>
+      <c r="D5">
+        <v>0.04</v>
+      </c>
+      <c r="E5">
+        <v>170.911</v>
+      </c>
+      <c r="F5">
+        <v>174.46299999999999</v>
+      </c>
+      <c r="G5">
+        <v>170.37299999999999</v>
+      </c>
+      <c r="H5">
+        <v>165.81200000000001</v>
+      </c>
+      <c r="I5">
+        <v>165.61</v>
+      </c>
+      <c r="J5">
+        <v>170.37299999999999</v>
+      </c>
+      <c r="K5">
+        <v>247.88</v>
+      </c>
+      <c r="L5">
+        <v>166.23400000000001</v>
+      </c>
+      <c r="M5">
+        <v>170.36199999999999</v>
+      </c>
+      <c r="N5">
+        <v>170.078</v>
+      </c>
+      <c r="O5">
+        <v>177.20500000000001</v>
+      </c>
+      <c r="P5">
+        <v>170.37299999999999</v>
+      </c>
+      <c r="Q5">
+        <v>236.399</v>
+      </c>
+      <c r="R5">
+        <v>195.345</v>
+      </c>
+      <c r="S5">
+        <v>176.815</v>
+      </c>
+      <c r="T5">
+        <v>170.37799999999999</v>
+      </c>
+      <c r="U5">
+        <v>162.858</v>
+      </c>
+      <c r="V5">
+        <v>154.04</v>
+      </c>
+      <c r="W5">
+        <v>174.679</v>
+      </c>
+      <c r="X5">
+        <v>177.65299999999999</v>
+      </c>
+      <c r="Y5">
+        <v>175.875</v>
+      </c>
+      <c r="Z5">
+        <v>166.12</v>
+      </c>
+      <c r="AA5">
+        <v>170.274</v>
+      </c>
+      <c r="AB5">
+        <v>173.86199999999999</v>
+      </c>
+      <c r="AC5">
+        <v>17174.5</v>
+      </c>
+      <c r="AD5">
+        <v>169.81399999999999</v>
+      </c>
+      <c r="AE5">
+        <v>51.998699999999999</v>
+      </c>
+      <c r="AF5">
+        <v>181.09899999999999</v>
+      </c>
+      <c r="AG5">
+        <v>166.87899999999999</v>
+      </c>
+      <c r="AH5">
+        <v>185.55199999999999</v>
+      </c>
+      <c r="AI5">
+        <v>169.44499999999999</v>
+      </c>
+      <c r="AJ5">
+        <v>166.05799999999999</v>
+      </c>
+      <c r="AK5">
+        <v>165.85599999999999</v>
+      </c>
+      <c r="AL5">
+        <v>169.857</v>
+      </c>
+      <c r="AM5">
+        <v>170.67</v>
+      </c>
+      <c r="AN5">
+        <v>178.36699999999999</v>
+      </c>
+      <c r="AO5">
+        <v>177.05799999999999</v>
+      </c>
+      <c r="AP5">
+        <v>171.75899999999999</v>
+      </c>
+      <c r="AQ5">
+        <v>176.79599999999999</v>
+      </c>
+      <c r="AR5">
+        <v>169.13800000000001</v>
+      </c>
+      <c r="AS5">
+        <v>165.81200000000001</v>
+      </c>
+      <c r="AT5">
+        <v>247.88</v>
+      </c>
+      <c r="AU5">
+        <v>167.988</v>
+      </c>
+      <c r="AV5">
+        <v>402.37599999999998</v>
+      </c>
+      <c r="AW5">
+        <v>170.226</v>
+      </c>
+      <c r="AX5">
+        <v>172.13800000000001</v>
+      </c>
+      <c r="AY5">
+        <v>170.084</v>
+      </c>
+      <c r="AZ5">
+        <v>94.895899999999997</v>
+      </c>
+      <c r="BA5">
+        <v>165.79900000000001</v>
+      </c>
+      <c r="BB5">
+        <v>165.81200000000001</v>
+      </c>
+      <c r="BC5">
+        <v>179.05600000000001</v>
+      </c>
+      <c r="BD5">
+        <v>168.571</v>
+      </c>
+      <c r="BE5">
+        <v>189.208</v>
+      </c>
+      <c r="BF5">
+        <v>193.85300000000001</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI5">
+        <v>41</v>
+      </c>
+      <c r="BJ5">
+        <v>0.63960300000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>0.98</v>
+      </c>
+      <c r="D6">
+        <v>0.02</v>
+      </c>
+      <c r="E6">
+        <v>183.18899999999999</v>
+      </c>
+      <c r="F6">
+        <v>189.315</v>
+      </c>
+      <c r="G6">
+        <v>182.13200000000001</v>
+      </c>
+      <c r="H6">
+        <v>174.97900000000001</v>
+      </c>
+      <c r="I6">
+        <v>179.101</v>
+      </c>
+      <c r="J6">
+        <v>182.13200000000001</v>
+      </c>
+      <c r="K6">
+        <v>290.06099999999998</v>
+      </c>
+      <c r="L6">
+        <v>175.75899999999999</v>
+      </c>
+      <c r="M6">
+        <v>182.11600000000001</v>
+      </c>
+      <c r="N6">
+        <v>181.756</v>
+      </c>
+      <c r="O6">
+        <v>195.68600000000001</v>
+      </c>
+      <c r="P6">
+        <v>182.13200000000001</v>
+      </c>
+      <c r="Q6">
+        <v>274.94099999999997</v>
+      </c>
+      <c r="R6">
+        <v>216.648</v>
+      </c>
+      <c r="S6">
+        <v>193.048</v>
+      </c>
+      <c r="T6">
+        <v>198.911</v>
+      </c>
+      <c r="U6">
+        <v>168.63</v>
+      </c>
+      <c r="V6">
+        <v>158.63999999999999</v>
+      </c>
+      <c r="W6">
+        <v>191.27</v>
+      </c>
+      <c r="X6">
+        <v>195.84200000000001</v>
+      </c>
+      <c r="Y6">
+        <v>189.554</v>
+      </c>
+      <c r="Z6">
+        <v>179.48699999999999</v>
+      </c>
+      <c r="AA6">
+        <v>182.226</v>
+      </c>
+      <c r="AB6">
+        <v>187.59200000000001</v>
+      </c>
+      <c r="AC6">
+        <v>138083</v>
+      </c>
+      <c r="AD6">
+        <v>181.43899999999999</v>
+      </c>
+      <c r="AE6">
+        <v>169.63499999999999</v>
+      </c>
+      <c r="AF6">
+        <v>196.482</v>
+      </c>
+      <c r="AG6">
+        <v>181.70500000000001</v>
+      </c>
+      <c r="AH6">
+        <v>207.24799999999999</v>
+      </c>
+      <c r="AI6">
+        <v>179.32900000000001</v>
+      </c>
+      <c r="AJ6">
+        <v>175.17099999999999</v>
+      </c>
+      <c r="AK6">
+        <v>177.76</v>
+      </c>
+      <c r="AL6">
+        <v>181.46299999999999</v>
+      </c>
+      <c r="AM6">
+        <v>182.059</v>
+      </c>
+      <c r="AN6">
+        <v>197.93299999999999</v>
+      </c>
+      <c r="AO6">
+        <v>195.94399999999999</v>
+      </c>
+      <c r="AP6">
+        <v>183.58699999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>192.642</v>
+      </c>
+      <c r="AR6">
+        <v>180.68700000000001</v>
+      </c>
+      <c r="AS6">
+        <v>174.97900000000001</v>
+      </c>
+      <c r="AT6">
+        <v>290.06099999999998</v>
+      </c>
+      <c r="AU6">
+        <v>178.41900000000001</v>
+      </c>
+      <c r="AV6">
+        <v>576.98500000000001</v>
+      </c>
+      <c r="AW6">
+        <v>181.36799999999999</v>
+      </c>
+      <c r="AX6">
+        <v>184.13800000000001</v>
+      </c>
+      <c r="AY6">
+        <v>181.76400000000001</v>
+      </c>
+      <c r="AZ6">
+        <v>96.015799999999999</v>
+      </c>
+      <c r="BA6">
+        <v>174.96600000000001</v>
+      </c>
+      <c r="BB6">
+        <v>174.97900000000001</v>
+      </c>
+      <c r="BC6">
+        <v>205.37200000000001</v>
+      </c>
+      <c r="BD6">
+        <v>178.572</v>
+      </c>
+      <c r="BE6">
+        <v>206.00399999999999</v>
+      </c>
+      <c r="BF6">
+        <v>225.982</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI6">
+        <v>41</v>
+      </c>
+      <c r="BJ6">
+        <v>0.63583000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>0.99</v>
+      </c>
+      <c r="D7">
+        <v>0.01</v>
+      </c>
+      <c r="E7">
+        <v>194.791</v>
+      </c>
+      <c r="F7">
+        <v>203.761</v>
+      </c>
+      <c r="G7">
+        <v>193.08099999999999</v>
+      </c>
+      <c r="H7">
+        <v>183.22499999999999</v>
+      </c>
+      <c r="I7">
+        <v>192.405</v>
+      </c>
+      <c r="J7">
+        <v>193.08099999999999</v>
+      </c>
+      <c r="K7">
+        <v>332.24099999999999</v>
+      </c>
+      <c r="L7">
+        <v>184.429</v>
+      </c>
+      <c r="M7">
+        <v>193.06100000000001</v>
+      </c>
+      <c r="N7">
+        <v>192.642</v>
+      </c>
+      <c r="O7">
+        <v>215.34899999999999</v>
+      </c>
+      <c r="P7">
+        <v>193.08099999999999</v>
+      </c>
+      <c r="Q7">
+        <v>313.483</v>
+      </c>
+      <c r="R7">
+        <v>237.33699999999999</v>
+      </c>
+      <c r="S7">
+        <v>209.12799999999999</v>
+      </c>
+      <c r="T7">
+        <v>233.11099999999999</v>
+      </c>
+      <c r="U7">
+        <v>173.458</v>
+      </c>
+      <c r="V7">
+        <v>162.48699999999999</v>
+      </c>
+      <c r="W7">
+        <v>207.73699999999999</v>
+      </c>
+      <c r="X7">
+        <v>213.899</v>
+      </c>
+      <c r="Y7">
+        <v>202.07300000000001</v>
+      </c>
+      <c r="Z7">
+        <v>192.84</v>
+      </c>
+      <c r="AA7">
+        <v>193.446</v>
+      </c>
+      <c r="AB7">
+        <v>200.636</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>1095750</v>
+      </c>
+      <c r="AD7">
+        <v>192.29300000000001</v>
+      </c>
+      <c r="AE7">
+        <v>170.83500000000001</v>
+      </c>
+      <c r="AF7">
+        <v>210.745</v>
+      </c>
+      <c r="AG7">
+        <v>196.53100000000001</v>
+      </c>
+      <c r="AH7">
+        <v>228.94499999999999</v>
+      </c>
+      <c r="AI7">
+        <v>188.21899999999999</v>
+      </c>
+      <c r="AJ7">
+        <v>183.346</v>
+      </c>
+      <c r="AK7">
+        <v>189.489</v>
+      </c>
+      <c r="AL7">
+        <v>192.29400000000001</v>
+      </c>
+      <c r="AM7">
+        <v>192.46899999999999</v>
+      </c>
+      <c r="AN7">
+        <v>219.24799999999999</v>
+      </c>
+      <c r="AO7">
+        <v>214.82400000000001</v>
+      </c>
+      <c r="AP7">
+        <v>194.40700000000001</v>
+      </c>
+      <c r="AQ7">
+        <v>208.239</v>
+      </c>
+      <c r="AR7">
+        <v>191.57599999999999</v>
+      </c>
+      <c r="AS7">
+        <v>183.22499999999999</v>
+      </c>
+      <c r="AT7">
+        <v>332.24099999999999</v>
+      </c>
+      <c r="AU7">
+        <v>187.98099999999999</v>
+      </c>
+      <c r="AV7">
+        <v>807.07399999999996</v>
+      </c>
+      <c r="AW7">
+        <v>191.523</v>
+      </c>
+      <c r="AX7">
+        <v>195.113</v>
+      </c>
+      <c r="AY7">
+        <v>192.65299999999999</v>
+      </c>
+      <c r="AZ7">
+        <v>97.040099999999995</v>
+      </c>
+      <c r="BA7">
+        <v>183.21100000000001</v>
+      </c>
+      <c r="BB7">
+        <v>183.22499999999999</v>
+      </c>
+      <c r="BC7">
+        <v>233.37200000000001</v>
+      </c>
+      <c r="BD7">
+        <v>187.53299999999999</v>
+      </c>
+      <c r="BE7">
+        <v>222.67599999999999</v>
+      </c>
+      <c r="BF7">
+        <v>263.13799999999998</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI7">
+        <v>41</v>
+      </c>
+      <c r="BJ7">
+        <v>0.63396799999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>250</v>
+      </c>
+      <c r="C8">
+        <v>0.996</v>
+      </c>
+      <c r="D8">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E8">
+        <v>209.40600000000001</v>
+      </c>
+      <c r="F8">
+        <v>222.505</v>
+      </c>
+      <c r="G8">
+        <v>206.631</v>
+      </c>
+      <c r="H8">
+        <v>193.078</v>
+      </c>
+      <c r="I8">
+        <v>209.792</v>
+      </c>
+      <c r="J8">
+        <v>206.631</v>
+      </c>
+      <c r="K8">
+        <v>388.00099999999998</v>
+      </c>
+      <c r="L8">
+        <v>194.946</v>
+      </c>
+      <c r="M8">
+        <v>206.60599999999999</v>
+      </c>
+      <c r="N8">
+        <v>206.136</v>
+      </c>
+      <c r="O8">
+        <v>243.51499999999999</v>
+      </c>
+      <c r="P8">
+        <v>206.631</v>
+      </c>
+      <c r="Q8">
+        <v>364.43200000000002</v>
+      </c>
+      <c r="R8">
+        <v>263.988</v>
+      </c>
+      <c r="S8">
+        <v>230.274</v>
+      </c>
+      <c r="T8">
+        <v>288.298</v>
+      </c>
+      <c r="U8">
+        <v>178.828</v>
+      </c>
+      <c r="V8">
+        <v>166.767</v>
+      </c>
+      <c r="W8">
+        <v>229.42</v>
+      </c>
+      <c r="X8">
+        <v>237.67400000000001</v>
+      </c>
+      <c r="Y8">
+        <v>217.245</v>
+      </c>
+      <c r="Z8">
+        <v>210.48699999999999</v>
+      </c>
+      <c r="AA8">
+        <v>207.46799999999999</v>
+      </c>
+      <c r="AB8">
+        <v>217.114</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>16761600</v>
+      </c>
+      <c r="AD8">
+        <v>205.77600000000001</v>
+      </c>
+      <c r="AE8">
+        <v>171.55500000000001</v>
+      </c>
+      <c r="AF8">
+        <v>228.23500000000001</v>
+      </c>
+      <c r="AG8">
+        <v>216.131</v>
+      </c>
+      <c r="AH8">
+        <v>257.62599999999998</v>
+      </c>
+      <c r="AI8">
+        <v>198.84200000000001</v>
+      </c>
+      <c r="AJ8">
+        <v>193.083</v>
+      </c>
+      <c r="AK8">
+        <v>204.87200000000001</v>
+      </c>
+      <c r="AL8">
+        <v>205.738</v>
+      </c>
+      <c r="AM8">
+        <v>205.089</v>
+      </c>
+      <c r="AN8">
+        <v>250.66300000000001</v>
+      </c>
+      <c r="AO8">
+        <v>239.779</v>
+      </c>
+      <c r="AP8">
+        <v>207.52699999999999</v>
+      </c>
+      <c r="AQ8">
+        <v>228.744</v>
+      </c>
+      <c r="AR8">
+        <v>205.27500000000001</v>
+      </c>
+      <c r="AS8">
+        <v>193.078</v>
+      </c>
+      <c r="AT8">
+        <v>388.00099999999998</v>
+      </c>
+      <c r="AU8">
+        <v>199.631</v>
+      </c>
+      <c r="AV8">
+        <v>1218.74</v>
+      </c>
+      <c r="AW8">
+        <v>203.80099999999999</v>
+      </c>
+      <c r="AX8">
+        <v>208.422</v>
+      </c>
+      <c r="AY8">
+        <v>206.15100000000001</v>
+      </c>
+      <c r="AZ8">
+        <v>98.282200000000003</v>
+      </c>
+      <c r="BA8">
+        <v>193.06299999999999</v>
+      </c>
+      <c r="BB8">
+        <v>193.078</v>
+      </c>
+      <c r="BC8">
+        <v>272.51</v>
+      </c>
+      <c r="BD8">
+        <v>198.18299999999999</v>
+      </c>
+      <c r="BE8">
+        <v>244.62799999999999</v>
+      </c>
+      <c r="BF8">
+        <v>321.53500000000003</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI8">
+        <v>41</v>
+      </c>
+      <c r="BJ8">
+        <v>0.63285800000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>500</v>
+      </c>
+      <c r="C9">
+        <v>0.998</v>
+      </c>
+      <c r="D9">
+        <v>2E-3</v>
+      </c>
+      <c r="E9">
+        <v>220.06700000000001</v>
+      </c>
+      <c r="F9">
+        <v>236.55</v>
+      </c>
+      <c r="G9">
+        <v>216.339</v>
+      </c>
+      <c r="H9">
+        <v>199.91800000000001</v>
+      </c>
+      <c r="I9">
+        <v>222.834</v>
+      </c>
+      <c r="J9">
+        <v>216.339</v>
+      </c>
+      <c r="K9">
+        <v>430.18200000000002</v>
+      </c>
+      <c r="L9">
+        <v>202.37100000000001</v>
+      </c>
+      <c r="M9">
+        <v>216.31</v>
+      </c>
+      <c r="N9">
+        <v>215.821</v>
+      </c>
+      <c r="O9">
+        <v>266.68299999999999</v>
+      </c>
+      <c r="P9">
+        <v>216.339</v>
+      </c>
+      <c r="Q9">
+        <v>402.97399999999999</v>
+      </c>
+      <c r="R9">
+        <v>283.74099999999999</v>
+      </c>
+      <c r="S9">
+        <v>246.232</v>
+      </c>
+      <c r="T9">
+        <v>338.661</v>
+      </c>
+      <c r="U9">
+        <v>182.328</v>
+      </c>
+      <c r="V9">
+        <v>169.55600000000001</v>
+      </c>
+      <c r="W9">
+        <v>245.792</v>
+      </c>
+      <c r="X9">
+        <v>255.62700000000001</v>
+      </c>
+      <c r="Y9">
+        <v>227.887</v>
+      </c>
+      <c r="Z9">
+        <v>223.83600000000001</v>
+      </c>
+      <c r="AA9">
+        <v>217.61600000000001</v>
+      </c>
+      <c r="AB9">
+        <v>229.14</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>131462000</v>
+      </c>
+      <c r="AD9">
+        <v>215.47499999999999</v>
+      </c>
+      <c r="AE9">
+        <v>171.79499999999999</v>
+      </c>
+      <c r="AF9">
+        <v>240.62299999999999</v>
+      </c>
+      <c r="AG9">
+        <v>230.95699999999999</v>
+      </c>
+      <c r="AH9">
+        <v>279.322</v>
+      </c>
+      <c r="AI9">
+        <v>206.215</v>
+      </c>
+      <c r="AJ9">
+        <v>199.82400000000001</v>
+      </c>
+      <c r="AK9">
+        <v>216.465</v>
+      </c>
+      <c r="AL9">
+        <v>215.405</v>
+      </c>
+      <c r="AM9">
+        <v>213.953</v>
+      </c>
+      <c r="AN9">
+        <v>277.25599999999997</v>
+      </c>
+      <c r="AO9">
+        <v>258.65699999999998</v>
+      </c>
+      <c r="AP9">
+        <v>216.74100000000001</v>
+      </c>
+      <c r="AQ9">
+        <v>244.30600000000001</v>
+      </c>
+      <c r="AR9">
+        <v>215.26900000000001</v>
+      </c>
+      <c r="AS9">
+        <v>199.91800000000001</v>
+      </c>
+      <c r="AT9">
+        <v>430.18200000000002</v>
+      </c>
+      <c r="AU9">
+        <v>207.86199999999999</v>
+      </c>
+      <c r="AV9">
+        <v>1631.75</v>
+      </c>
+      <c r="AW9">
+        <v>212.40299999999999</v>
+      </c>
+      <c r="AX9">
+        <v>217.768</v>
+      </c>
+      <c r="AY9">
+        <v>215.83799999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>99.154399999999995</v>
+      </c>
+      <c r="BA9">
+        <v>199.90199999999999</v>
+      </c>
+      <c r="BB9">
+        <v>199.91800000000001</v>
+      </c>
+      <c r="BC9">
+        <v>303.44600000000003</v>
+      </c>
+      <c r="BD9">
+        <v>205.535</v>
+      </c>
+      <c r="BE9">
+        <v>261.20400000000001</v>
+      </c>
+      <c r="BF9">
+        <v>374.07100000000003</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI9">
+        <v>41</v>
+      </c>
+      <c r="BJ9">
+        <v>0.63248899999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>750</v>
+      </c>
+      <c r="C10">
+        <v>0.99866699999999997</v>
+      </c>
+      <c r="D10">
+        <v>1.33333E-3</v>
+      </c>
+      <c r="E10">
+        <v>226.184</v>
+      </c>
+      <c r="F10">
+        <v>244.74600000000001</v>
+      </c>
+      <c r="G10">
+        <v>221.84</v>
+      </c>
+      <c r="H10">
+        <v>203.71700000000001</v>
+      </c>
+      <c r="I10">
+        <v>230.42699999999999</v>
+      </c>
+      <c r="J10">
+        <v>221.84</v>
+      </c>
+      <c r="K10">
+        <v>454.85599999999999</v>
+      </c>
+      <c r="L10">
+        <v>206.548</v>
+      </c>
+      <c r="M10">
+        <v>221.809</v>
+      </c>
+      <c r="N10">
+        <v>221.315</v>
+      </c>
+      <c r="O10">
+        <v>281.048</v>
+      </c>
+      <c r="P10">
+        <v>221.84</v>
+      </c>
+      <c r="Q10">
+        <v>425.52</v>
+      </c>
+      <c r="R10">
+        <v>295.16300000000001</v>
+      </c>
+      <c r="S10">
+        <v>255.56</v>
+      </c>
+      <c r="T10">
+        <v>371.96800000000002</v>
+      </c>
+      <c r="U10">
+        <v>184.19900000000001</v>
+      </c>
+      <c r="V10">
+        <v>171.047</v>
+      </c>
+      <c r="W10">
+        <v>255.363</v>
+      </c>
+      <c r="X10">
+        <v>266.12200000000001</v>
+      </c>
+      <c r="Y10">
+        <v>233.83199999999999</v>
+      </c>
+      <c r="Z10">
+        <v>231.64400000000001</v>
+      </c>
+      <c r="AA10">
+        <v>223.40600000000001</v>
+      </c>
+      <c r="AB10">
+        <v>236.03299999999999</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>438240000</v>
+      </c>
+      <c r="AD10">
+        <v>220.988</v>
+      </c>
+      <c r="AE10">
+        <v>171.875</v>
+      </c>
+      <c r="AF10">
+        <v>247.58099999999999</v>
+      </c>
+      <c r="AG10">
+        <v>239.63</v>
+      </c>
+      <c r="AH10">
+        <v>292.01299999999998</v>
+      </c>
+      <c r="AI10">
+        <v>210.31100000000001</v>
+      </c>
+      <c r="AJ10">
+        <v>203.56200000000001</v>
+      </c>
+      <c r="AK10">
+        <v>223.238</v>
+      </c>
+      <c r="AL10">
+        <v>220.89699999999999</v>
+      </c>
+      <c r="AM10">
+        <v>218.91</v>
+      </c>
+      <c r="AN10">
+        <v>294.072</v>
+      </c>
+      <c r="AO10">
+        <v>269.69900000000001</v>
+      </c>
+      <c r="AP10">
+        <v>221.892</v>
+      </c>
+      <c r="AQ10">
+        <v>253.465</v>
+      </c>
+      <c r="AR10">
+        <v>221.00399999999999</v>
+      </c>
+      <c r="AS10">
+        <v>203.71700000000001</v>
+      </c>
+      <c r="AT10">
+        <v>454.85599999999999</v>
+      </c>
+      <c r="AU10">
+        <v>212.48599999999999</v>
+      </c>
+      <c r="AV10">
+        <v>1922.19</v>
+      </c>
+      <c r="AW10">
+        <v>217.20699999999999</v>
+      </c>
+      <c r="AX10">
+        <v>222.995</v>
+      </c>
+      <c r="AY10">
+        <v>221.333</v>
+      </c>
+      <c r="AZ10">
+        <v>99.642200000000003</v>
+      </c>
+      <c r="BA10">
+        <v>203.70099999999999</v>
+      </c>
+      <c r="BB10">
+        <v>203.71700000000001</v>
+      </c>
+      <c r="BC10">
+        <v>321.995</v>
+      </c>
+      <c r="BD10">
+        <v>209.60300000000001</v>
+      </c>
+      <c r="BE10">
+        <v>270.89400000000001</v>
+      </c>
+      <c r="BF10">
+        <v>408.67399999999998</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI10">
+        <v>41</v>
+      </c>
+      <c r="BJ10">
+        <v>0.63236599999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1000</v>
+      </c>
+      <c r="C11">
+        <v>0.999</v>
+      </c>
+      <c r="D11">
+        <v>1E-3</v>
+      </c>
+      <c r="E11">
+        <v>230.48</v>
+      </c>
+      <c r="F11">
+        <v>250.56</v>
+      </c>
+      <c r="G11">
+        <v>225.672</v>
+      </c>
+      <c r="H11">
+        <v>206.333</v>
+      </c>
+      <c r="I11">
+        <v>235.80199999999999</v>
+      </c>
+      <c r="J11">
+        <v>225.672</v>
+      </c>
+      <c r="K11">
+        <v>472.36200000000002</v>
+      </c>
+      <c r="L11">
+        <v>209.44800000000001</v>
+      </c>
+      <c r="M11">
+        <v>225.63900000000001</v>
+      </c>
+      <c r="N11">
+        <v>225.14599999999999</v>
+      </c>
+      <c r="O11">
+        <v>291.62599999999998</v>
+      </c>
+      <c r="P11">
+        <v>225.672</v>
+      </c>
+      <c r="Q11">
+        <v>441.51600000000002</v>
+      </c>
+      <c r="R11">
+        <v>303.21499999999997</v>
+      </c>
+      <c r="S11">
+        <v>262.17599999999999</v>
+      </c>
+      <c r="T11">
+        <v>397.45699999999999</v>
+      </c>
+      <c r="U11">
+        <v>185.458</v>
+      </c>
+      <c r="V11">
+        <v>172.05</v>
+      </c>
+      <c r="W11">
+        <v>262.15199999999999</v>
+      </c>
+      <c r="X11">
+        <v>273.56599999999997</v>
+      </c>
+      <c r="Y11">
+        <v>237.93799999999999</v>
+      </c>
+      <c r="Z11">
+        <v>237.184</v>
+      </c>
+      <c r="AA11">
+        <v>227.458</v>
+      </c>
+      <c r="AB11">
+        <v>240.86799999999999</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>1029520000</v>
+      </c>
+      <c r="AD11">
+        <v>224.83600000000001</v>
+      </c>
+      <c r="AE11">
+        <v>171.91499999999999</v>
+      </c>
+      <c r="AF11">
+        <v>252.40199999999999</v>
+      </c>
+      <c r="AG11">
+        <v>245.78299999999999</v>
+      </c>
+      <c r="AH11">
+        <v>301.01799999999997</v>
+      </c>
+      <c r="AI11">
+        <v>213.131</v>
+      </c>
+      <c r="AJ11">
+        <v>206.13300000000001</v>
+      </c>
+      <c r="AK11">
+        <v>228.042</v>
+      </c>
+      <c r="AL11">
+        <v>224.73</v>
+      </c>
+      <c r="AM11">
+        <v>222.33699999999999</v>
+      </c>
+      <c r="AN11">
+        <v>306.61</v>
+      </c>
+      <c r="AO11">
+        <v>277.53399999999999</v>
+      </c>
+      <c r="AP11">
+        <v>225.452</v>
+      </c>
+      <c r="AQ11">
+        <v>259.99700000000001</v>
+      </c>
+      <c r="AR11">
+        <v>225.03399999999999</v>
+      </c>
+      <c r="AS11">
+        <v>206.333</v>
+      </c>
+      <c r="AT11">
+        <v>472.36200000000002</v>
+      </c>
+      <c r="AU11">
+        <v>215.691</v>
+      </c>
+      <c r="AV11">
+        <v>2153.0300000000002</v>
+      </c>
+      <c r="AW11">
+        <v>220.524</v>
+      </c>
+      <c r="AX11">
+        <v>226.607</v>
+      </c>
+      <c r="AY11">
+        <v>225.16499999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>99.979299999999995</v>
+      </c>
+      <c r="BA11">
+        <v>206.316</v>
+      </c>
+      <c r="BB11">
+        <v>206.333</v>
+      </c>
+      <c r="BC11">
+        <v>335.33699999999999</v>
+      </c>
+      <c r="BD11">
+        <v>212.39699999999999</v>
+      </c>
+      <c r="BE11">
+        <v>277.767</v>
+      </c>
+      <c r="BF11">
+        <v>435.14299999999997</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>33</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>94</v>
+      </c>
+      <c r="BI11">
+        <v>41</v>
+      </c>
+      <c r="BJ11">
+        <v>0.63230500000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tool/PMP/old/PMP_Sample.xlsx
+++ b/tool/PMP/old/PMP_Sample.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC3B29B-E61D-4D8D-92CB-59E3012F36AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFBF7C3-41BF-4C52-832E-8C28C5D78FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{47787139-5384-4680-882A-D7262C6BD61D}"/>
   </bookViews>
   <sheets>
     <sheet name="Rain" sheetId="1" r:id="rId1"/>
-    <sheet name="PMP" sheetId="2" r:id="rId2"/>
-    <sheet name="25020260PMP" sheetId="6" r:id="rId3"/>
-    <sheet name="25020230PMP" sheetId="5" r:id="rId4"/>
-    <sheet name="25020230" sheetId="3" r:id="rId5"/>
-    <sheet name="25020230BestFit" sheetId="4" r:id="rId6"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId2"/>
+    <sheet name="PMP" sheetId="2" r:id="rId3"/>
+    <sheet name="25020280PMP" sheetId="8" r:id="rId4"/>
+    <sheet name="25020260PMP" sheetId="6" r:id="rId5"/>
+    <sheet name="25020230PMP" sheetId="5" r:id="rId6"/>
+    <sheet name="25020230" sheetId="3" r:id="rId7"/>
+    <sheet name="25020230BestFit" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="100">
   <si>
     <t>Year / Station</t>
   </si>
@@ -321,10 +322,28 @@
     <t>R.HydroTools-Levy_stable</t>
   </si>
   <si>
+    <t>prob_l</t>
+  </si>
+  <si>
+    <t>prob_g</t>
+  </si>
+  <si>
     <t>R.HydroTools-Invgauss</t>
   </si>
   <si>
     <t>R.HydroTools-powernorm</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>25020280_1969_2009</t>
+  </si>
+  <si>
+    <t>R.HydroTools-levy_stable</t>
+  </si>
+  <si>
+    <t>R.HydroTools-fisk</t>
   </si>
 </sst>
 </file>
@@ -423,11 +442,11 @@
     <c:title>
       <c:tx>
         <c:strRef>
-          <c:f>'25020260PMP'!$B$2</c:f>
+          <c:f>'25020280PMP'!$B$2</c:f>
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>25020260</c:v>
+              <c:v>25020280</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -472,11 +491,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'25020260PMP'!$B$3</c:f>
+              <c:f>'25020280PMP'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>25020260-Excel-Gumbel</c:v>
+                  <c:v>25020280-Excel-Gumbel</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -507,7 +526,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -534,27 +553,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$B$4:$B$9</c:f>
+              <c:f>'25020280PMP'!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>107</c:v>
+                  <c:v>111</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>133</c:v>
+                  <c:v>149</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154</c:v>
+                  <c:v>179</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>181</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>201</c:v>
+                  <c:v>247</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>220</c:v>
+                  <c:v>276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -562,7 +581,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000000-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -571,11 +590,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'25020260PMP'!$C$3</c:f>
+              <c:f>'25020280PMP'!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>25020260-R.HydroTools-Gumbel</c:v>
+                  <c:v>25020280-R.HydroTools-Gumbel</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -606,7 +625,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -633,27 +652,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$C$4:$C$9</c:f>
+              <c:f>'25020280PMP'!$C$4:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>126.64700000000001</c:v>
+                  <c:v>123.529</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>148.64699999999999</c:v>
+                  <c:v>148.44499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>166.56700000000001</c:v>
+                  <c:v>168.738</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>189.208</c:v>
+                  <c:v>194.37899999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>206.00399999999999</c:v>
+                  <c:v>213.40100000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>222.67599999999999</c:v>
+                  <c:v>232.28200000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -661,7 +680,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000001-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -705,7 +724,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -745,7 +764,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000002-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -789,7 +808,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -829,7 +848,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000003-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -873,7 +892,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -913,7 +932,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000004-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -922,11 +941,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>'25020260PMP'!$E$3</c:f>
+              <c:f>'25020280PMP'!$E$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>25020260-R.HydroTools-powernorm</c:v>
+                  <c:v>25020280-R.HydroTools-fisk</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -957,7 +976,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -984,27 +1003,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$E$4:$E$9</c:f>
+              <c:f>'25020280PMP'!$E$4:$E$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>116.089</c:v>
+                  <c:v>107.17100000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>138.012</c:v>
+                  <c:v>125.602</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>153.345</c:v>
+                  <c:v>141.155</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>170.226</c:v>
+                  <c:v>162.54300000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>181.36799999999999</c:v>
+                  <c:v>180.10400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>191.523</c:v>
+                  <c:v>199.251</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1012,7 +1031,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000005-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1021,11 +1040,11 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'25020260PMP'!$D$3</c:f>
+              <c:f>'25020280PMP'!$D$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>25020260-R.HydroTools-Invgauss</c:v>
+                  <c:v>25020280-R.HydroTools-levy_stable</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1062,7 +1081,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:f>'25020280PMP'!$A$4:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1089,27 +1108,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'25020260PMP'!$D$4:$D$9</c:f>
+              <c:f>'25020280PMP'!$D$4:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>114.58799999999999</c:v>
+                  <c:v>107.05200000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>137.27699999999999</c:v>
+                  <c:v>124.768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>154.149</c:v>
+                  <c:v>139.649</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>173.86199999999999</c:v>
+                  <c:v>162.364</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>187.59200000000001</c:v>
+                  <c:v>186.10499999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>200.636</c:v>
+                  <c:v>221.024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1117,7 +1136,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-7A8B-434C-A040-831C426DE3A4}"/>
+              <c16:uniqueId val="{00000006-C5C6-47BD-99AD-7EC982D3FD79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1345,6 +1364,928 @@
     <c:title>
       <c:tx>
         <c:strRef>
+          <c:f>'25020260PMP'!$B$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>25020260</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-Excel-Gumbel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>220</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-R.HydroTools-Gumbel</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>126.64700000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>148.64699999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>166.56700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>189.208</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>206.00399999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>222.67599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>PMP!#REF!</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-R.HydroTools-powernorm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$E$4:$E$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>116.089</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138.012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>153.345</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>170.226</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>181.36799999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>191.523</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'25020260PMP'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25020260-R.HydroTools-Invgauss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$A$4:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'25020260PMP'!$D$4:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>114.58799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>137.27699999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>154.149</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>173.86199999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>187.59200000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200.636</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7A8B-434C-A040-831C426DE3A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="489679200"/>
+        <c:axId val="489674880"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="489679200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="489674880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="489674880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="489679200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
           <c:f>PMP!$B$1</c:f>
           <c:strCache>
             <c:ptCount val="1"/>
@@ -2250,7 +3191,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9602,6 +10543,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -11189,6 +12170,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -11196,13 +12693,56 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>117311</xdr:colOff>
       <xdr:row>9</xdr:row>
+      <xdr:rowOff>207063</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2316376</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>5345</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DB909AA-46BB-4EEE-A264-2A98B424B0B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>117310</xdr:colOff>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>207065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2041663</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>157369</xdr:rowOff>
+      <xdr:colOff>2316375</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>5347</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11232,20 +12772,20 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>117311</xdr:colOff>
+      <xdr:colOff>117310</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>207065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2041663</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>157369</xdr:rowOff>
+      <xdr:colOff>2316375</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>5347</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11275,7 +12815,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -11285,10 +12825,10 @@
       <xdr:rowOff>162484</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>180135</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>64714</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>419106</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>106676</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13620,6 +15160,2089 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C93394-4CAA-4D45-B4FF-F549FD11CBF9}">
+  <dimension ref="AC1:CS11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AJ1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>4</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>2.33</v>
+      </c>
+      <c r="AL2">
+        <v>0.57081499999999996</v>
+      </c>
+      <c r="AM2">
+        <v>0.42918499999999998</v>
+      </c>
+      <c r="AN2">
+        <v>106.776</v>
+      </c>
+      <c r="AO2">
+        <v>107.88800000000001</v>
+      </c>
+      <c r="AP2">
+        <v>113.79</v>
+      </c>
+      <c r="AQ2">
+        <v>114.01600000000001</v>
+      </c>
+      <c r="AR2">
+        <v>106.206</v>
+      </c>
+      <c r="AS2">
+        <v>108.381</v>
+      </c>
+      <c r="AT2">
+        <v>99.748500000000007</v>
+      </c>
+      <c r="AU2">
+        <v>107.09699999999999</v>
+      </c>
+      <c r="AV2">
+        <v>107.08199999999999</v>
+      </c>
+      <c r="AW2">
+        <v>107.901</v>
+      </c>
+      <c r="AX2">
+        <v>107.17100000000001</v>
+      </c>
+      <c r="AY2">
+        <v>108.381</v>
+      </c>
+      <c r="AZ2">
+        <v>107.102</v>
+      </c>
+      <c r="BA2">
+        <v>101.788</v>
+      </c>
+      <c r="BB2">
+        <v>107.794</v>
+      </c>
+      <c r="BC2">
+        <v>100.71599999999999</v>
+      </c>
+      <c r="BD2">
+        <v>255.61500000000001</v>
+      </c>
+      <c r="BE2">
+        <v>118.849</v>
+      </c>
+      <c r="BF2">
+        <v>107.93899999999999</v>
+      </c>
+      <c r="BG2">
+        <v>105.301</v>
+      </c>
+      <c r="BH2">
+        <v>107.488</v>
+      </c>
+      <c r="BI2">
+        <v>112.795</v>
+      </c>
+      <c r="BJ2">
+        <v>107.10299999999999</v>
+      </c>
+      <c r="BK2">
+        <v>107.785</v>
+      </c>
+      <c r="BL2">
+        <v>106.97199999999999</v>
+      </c>
+      <c r="BM2">
+        <v>106.124</v>
+      </c>
+      <c r="BN2">
+        <v>103.729</v>
+      </c>
+      <c r="BO2">
+        <v>109.96599999999999</v>
+      </c>
+      <c r="BP2">
+        <v>111.602</v>
+      </c>
+      <c r="BQ2">
+        <v>105.15300000000001</v>
+      </c>
+      <c r="BR2">
+        <v>107.05200000000001</v>
+      </c>
+      <c r="BS2">
+        <v>114.352</v>
+      </c>
+      <c r="BT2">
+        <v>113.289</v>
+      </c>
+      <c r="BU2">
+        <v>107.398</v>
+      </c>
+      <c r="BV2">
+        <v>111.324</v>
+      </c>
+      <c r="BW2">
+        <v>106.73099999999999</v>
+      </c>
+      <c r="BX2">
+        <v>105.82</v>
+      </c>
+      <c r="BY2">
+        <v>93.693299999999994</v>
+      </c>
+      <c r="BZ2">
+        <v>109.07299999999999</v>
+      </c>
+      <c r="CA2">
+        <v>107.163</v>
+      </c>
+      <c r="CB2">
+        <v>114.01600000000001</v>
+      </c>
+      <c r="CC2">
+        <v>99.748500000000007</v>
+      </c>
+      <c r="CD2">
+        <v>100.005</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG2">
+        <v>110.379</v>
+      </c>
+      <c r="CH2">
+        <v>107.93899999999999</v>
+      </c>
+      <c r="CI2">
+        <v>111.85599999999999</v>
+      </c>
+      <c r="CJ2">
+        <v>108.185</v>
+      </c>
+      <c r="CK2">
+        <v>114.01600000000001</v>
+      </c>
+      <c r="CL2">
+        <v>100.806</v>
+      </c>
+      <c r="CM2">
+        <v>99.963399999999993</v>
+      </c>
+      <c r="CN2">
+        <v>123.529</v>
+      </c>
+      <c r="CO2">
+        <v>104.482</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR2">
+        <v>41</v>
+      </c>
+      <c r="CS2">
+        <v>0.729209</v>
+      </c>
+    </row>
+    <row r="3" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>5</v>
+      </c>
+      <c r="AL3">
+        <v>0.8</v>
+      </c>
+      <c r="AM3">
+        <v>0.2</v>
+      </c>
+      <c r="AN3">
+        <v>128.107</v>
+      </c>
+      <c r="AO3">
+        <v>129.40600000000001</v>
+      </c>
+      <c r="AP3">
+        <v>200.523</v>
+      </c>
+      <c r="AQ3">
+        <v>136.73500000000001</v>
+      </c>
+      <c r="AR3">
+        <v>122.988</v>
+      </c>
+      <c r="AS3">
+        <v>131.23400000000001</v>
+      </c>
+      <c r="AT3">
+        <v>140.143</v>
+      </c>
+      <c r="AU3">
+        <v>128.13900000000001</v>
+      </c>
+      <c r="AV3">
+        <v>128.83799999999999</v>
+      </c>
+      <c r="AW3">
+        <v>130.56899999999999</v>
+      </c>
+      <c r="AX3">
+        <v>125.602</v>
+      </c>
+      <c r="AY3">
+        <v>131.23400000000001</v>
+      </c>
+      <c r="AZ3">
+        <v>132.245</v>
+      </c>
+      <c r="BA3">
+        <v>138.946</v>
+      </c>
+      <c r="BB3">
+        <v>128.75899999999999</v>
+      </c>
+      <c r="BC3">
+        <v>118.545</v>
+      </c>
+      <c r="BD3">
+        <v>258.16399999999999</v>
+      </c>
+      <c r="BE3">
+        <v>136.03200000000001</v>
+      </c>
+      <c r="BF3">
+        <v>132.54900000000001</v>
+      </c>
+      <c r="BG3">
+        <v>131.654</v>
+      </c>
+      <c r="BH3">
+        <v>135.38900000000001</v>
+      </c>
+      <c r="BI3">
+        <v>132.41999999999999</v>
+      </c>
+      <c r="BJ3">
+        <v>129.012</v>
+      </c>
+      <c r="BK3">
+        <v>130.46299999999999</v>
+      </c>
+      <c r="BL3">
+        <v>129.31100000000001</v>
+      </c>
+      <c r="BM3">
+        <v>125.94799999999999</v>
+      </c>
+      <c r="BN3">
+        <v>127.271</v>
+      </c>
+      <c r="BO3">
+        <v>133.76300000000001</v>
+      </c>
+      <c r="BP3">
+        <v>130.09899999999999</v>
+      </c>
+      <c r="BQ3">
+        <v>127.486</v>
+      </c>
+      <c r="BR3">
+        <v>124.768</v>
+      </c>
+      <c r="BS3">
+        <v>138.05099999999999</v>
+      </c>
+      <c r="BT3">
+        <v>134.08600000000001</v>
+      </c>
+      <c r="BU3">
+        <v>129.619</v>
+      </c>
+      <c r="BV3">
+        <v>136.322</v>
+      </c>
+      <c r="BW3">
+        <v>126.285</v>
+      </c>
+      <c r="BX3">
+        <v>130.65899999999999</v>
+      </c>
+      <c r="BY3">
+        <v>129.19300000000001</v>
+      </c>
+      <c r="BZ3">
+        <v>130.20500000000001</v>
+      </c>
+      <c r="CA3">
+        <v>128.61199999999999</v>
+      </c>
+      <c r="CB3">
+        <v>136.73500000000001</v>
+      </c>
+      <c r="CC3">
+        <v>140.143</v>
+      </c>
+      <c r="CD3">
+        <v>125.389</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG3">
+        <v>136.18199999999999</v>
+      </c>
+      <c r="CH3">
+        <v>130.58799999999999</v>
+      </c>
+      <c r="CI3">
+        <v>135.36000000000001</v>
+      </c>
+      <c r="CJ3">
+        <v>123.786</v>
+      </c>
+      <c r="CK3">
+        <v>136.73500000000001</v>
+      </c>
+      <c r="CL3">
+        <v>123.246</v>
+      </c>
+      <c r="CM3">
+        <v>123.529</v>
+      </c>
+      <c r="CN3">
+        <v>148.44499999999999</v>
+      </c>
+      <c r="CO3">
+        <v>126.863</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR3">
+        <v>41</v>
+      </c>
+      <c r="CS3">
+        <v>0.67232000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AJ4">
+        <v>2</v>
+      </c>
+      <c r="AK4">
+        <v>10</v>
+      </c>
+      <c r="AL4">
+        <v>0.9</v>
+      </c>
+      <c r="AM4">
+        <v>0.1</v>
+      </c>
+      <c r="AN4">
+        <v>146.15700000000001</v>
+      </c>
+      <c r="AO4">
+        <v>146.67699999999999</v>
+      </c>
+      <c r="AP4">
+        <v>288.85199999999998</v>
+      </c>
+      <c r="AQ4">
+        <v>151.80600000000001</v>
+      </c>
+      <c r="AR4">
+        <v>137.09800000000001</v>
+      </c>
+      <c r="AS4">
+        <v>149.005</v>
+      </c>
+      <c r="AT4">
+        <v>176.81200000000001</v>
+      </c>
+      <c r="AU4">
+        <v>146.71899999999999</v>
+      </c>
+      <c r="AV4">
+        <v>146.81299999999999</v>
+      </c>
+      <c r="AW4">
+        <v>148.68299999999999</v>
+      </c>
+      <c r="AX4">
+        <v>141.155</v>
+      </c>
+      <c r="AY4">
+        <v>149.005</v>
+      </c>
+      <c r="AZ4">
+        <v>151.99</v>
+      </c>
+      <c r="BA4">
+        <v>171.751</v>
+      </c>
+      <c r="BB4">
+        <v>145.75</v>
+      </c>
+      <c r="BC4">
+        <v>138.86799999999999</v>
+      </c>
+      <c r="BD4">
+        <v>259.584</v>
+      </c>
+      <c r="BE4">
+        <v>145.59800000000001</v>
+      </c>
+      <c r="BF4">
+        <v>152.59399999999999</v>
+      </c>
+      <c r="BG4">
+        <v>153.53899999999999</v>
+      </c>
+      <c r="BH4">
+        <v>156.036</v>
+      </c>
+      <c r="BI4">
+        <v>148.09100000000001</v>
+      </c>
+      <c r="BJ4">
+        <v>147.18299999999999</v>
+      </c>
+      <c r="BK4">
+        <v>148.66900000000001</v>
+      </c>
+      <c r="BL4">
+        <v>148.36199999999999</v>
+      </c>
+      <c r="BM4">
+        <v>144.298</v>
+      </c>
+      <c r="BN4">
+        <v>143.827</v>
+      </c>
+      <c r="BO4">
+        <v>151.881</v>
+      </c>
+      <c r="BP4">
+        <v>146.88900000000001</v>
+      </c>
+      <c r="BQ4">
+        <v>147.75899999999999</v>
+      </c>
+      <c r="BR4">
+        <v>139.649</v>
+      </c>
+      <c r="BS4">
+        <v>153.71100000000001</v>
+      </c>
+      <c r="BT4">
+        <v>149.40199999999999</v>
+      </c>
+      <c r="BU4">
+        <v>147.714</v>
+      </c>
+      <c r="BV4">
+        <v>153.91499999999999</v>
+      </c>
+      <c r="BW4">
+        <v>143.48699999999999</v>
+      </c>
+      <c r="BX4">
+        <v>152.285</v>
+      </c>
+      <c r="BY4">
+        <v>159.19</v>
+      </c>
+      <c r="BZ4">
+        <v>146.25399999999999</v>
+      </c>
+      <c r="CA4">
+        <v>146.44800000000001</v>
+      </c>
+      <c r="CB4">
+        <v>151.80600000000001</v>
+      </c>
+      <c r="CC4">
+        <v>176.81200000000001</v>
+      </c>
+      <c r="CD4">
+        <v>150.571</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG4">
+        <v>154.58000000000001</v>
+      </c>
+      <c r="CH4">
+        <v>148.64599999999999</v>
+      </c>
+      <c r="CI4">
+        <v>152.11799999999999</v>
+      </c>
+      <c r="CJ4">
+        <v>136.55799999999999</v>
+      </c>
+      <c r="CK4">
+        <v>151.80600000000001</v>
+      </c>
+      <c r="CL4">
+        <v>147.06</v>
+      </c>
+      <c r="CM4">
+        <v>145.94</v>
+      </c>
+      <c r="CN4">
+        <v>168.738</v>
+      </c>
+      <c r="CO4">
+        <v>148.59100000000001</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR4">
+        <v>41</v>
+      </c>
+      <c r="CS4">
+        <v>0.65132199999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AJ5">
+        <v>3</v>
+      </c>
+      <c r="AK5">
+        <v>25</v>
+      </c>
+      <c r="AL5">
+        <v>0.96</v>
+      </c>
+      <c r="AM5">
+        <v>0.04</v>
+      </c>
+      <c r="AN5">
+        <v>170.36</v>
+      </c>
+      <c r="AO5">
+        <v>168.38499999999999</v>
+      </c>
+      <c r="AP5">
+        <v>412.91</v>
+      </c>
+      <c r="AQ5">
+        <v>167.87700000000001</v>
+      </c>
+      <c r="AR5">
+        <v>155.244</v>
+      </c>
+      <c r="AS5">
+        <v>170.357</v>
+      </c>
+      <c r="AT5">
+        <v>225.286</v>
+      </c>
+      <c r="AU5">
+        <v>171.26300000000001</v>
+      </c>
+      <c r="AV5">
+        <v>170.001</v>
+      </c>
+      <c r="AW5">
+        <v>171</v>
+      </c>
+      <c r="AX5">
+        <v>162.54300000000001</v>
+      </c>
+      <c r="AY5">
+        <v>170.358</v>
+      </c>
+      <c r="AZ5">
+        <v>175.93600000000001</v>
+      </c>
+      <c r="BA5">
+        <v>214.43700000000001</v>
+      </c>
+      <c r="BB5">
+        <v>167.172</v>
+      </c>
+      <c r="BC5">
+        <v>173.04900000000001</v>
+      </c>
+      <c r="BD5">
+        <v>260.911</v>
+      </c>
+      <c r="BE5">
+        <v>154.54599999999999</v>
+      </c>
+      <c r="BF5">
+        <v>177.92</v>
+      </c>
+      <c r="BG5">
+        <v>181.28700000000001</v>
+      </c>
+      <c r="BH5">
+        <v>179.273</v>
+      </c>
+      <c r="BI5">
+        <v>168.226</v>
+      </c>
+      <c r="BJ5">
+        <v>170.71</v>
+      </c>
+      <c r="BK5">
+        <v>171.20500000000001</v>
+      </c>
+      <c r="BL5">
+        <v>173.58799999999999</v>
+      </c>
+      <c r="BM5">
+        <v>170.84800000000001</v>
+      </c>
+      <c r="BN5">
+        <v>164.55600000000001</v>
+      </c>
+      <c r="BO5">
+        <v>172.83199999999999</v>
+      </c>
+      <c r="BP5">
+        <v>169.08600000000001</v>
+      </c>
+      <c r="BQ5">
+        <v>174.559</v>
+      </c>
+      <c r="BR5">
+        <v>162.364</v>
+      </c>
+      <c r="BS5">
+        <v>170.35599999999999</v>
+      </c>
+      <c r="BT5">
+        <v>167.92699999999999</v>
+      </c>
+      <c r="BU5">
+        <v>170.595</v>
+      </c>
+      <c r="BV5">
+        <v>173.37899999999999</v>
+      </c>
+      <c r="BW5">
+        <v>167.79400000000001</v>
+      </c>
+      <c r="BX5">
+        <v>180.614</v>
+      </c>
+      <c r="BY5">
+        <v>194.15799999999999</v>
+      </c>
+      <c r="BZ5">
+        <v>165.447</v>
+      </c>
+      <c r="CA5">
+        <v>169.73699999999999</v>
+      </c>
+      <c r="CB5">
+        <v>167.87700000000001</v>
+      </c>
+      <c r="CC5">
+        <v>225.286</v>
+      </c>
+      <c r="CD5">
+        <v>185.47399999999999</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG5">
+        <v>175.042</v>
+      </c>
+      <c r="CH5">
+        <v>170.852</v>
+      </c>
+      <c r="CI5">
+        <v>170.756</v>
+      </c>
+      <c r="CJ5">
+        <v>154.66300000000001</v>
+      </c>
+      <c r="CK5">
+        <v>167.87700000000001</v>
+      </c>
+      <c r="CL5">
+        <v>182.876</v>
+      </c>
+      <c r="CM5">
+        <v>176.583</v>
+      </c>
+      <c r="CN5">
+        <v>194.37899999999999</v>
+      </c>
+      <c r="CO5">
+        <v>181.44399999999999</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR5">
+        <v>41</v>
+      </c>
+      <c r="CS5">
+        <v>0.63960300000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AJ6">
+        <v>4</v>
+      </c>
+      <c r="AK6">
+        <v>50</v>
+      </c>
+      <c r="AL6">
+        <v>0.98</v>
+      </c>
+      <c r="AM6">
+        <v>0.02</v>
+      </c>
+      <c r="AN6">
+        <v>189.73500000000001</v>
+      </c>
+      <c r="AO6">
+        <v>184.56299999999999</v>
+      </c>
+      <c r="AP6">
+        <v>510.16500000000002</v>
+      </c>
+      <c r="AQ6">
+        <v>178.25899999999999</v>
+      </c>
+      <c r="AR6">
+        <v>168.77099999999999</v>
+      </c>
+      <c r="AS6">
+        <v>185.51</v>
+      </c>
+      <c r="AT6">
+        <v>261.95600000000002</v>
+      </c>
+      <c r="AU6">
+        <v>189.83</v>
+      </c>
+      <c r="AV6">
+        <v>187.68799999999999</v>
+      </c>
+      <c r="AW6">
+        <v>187.178</v>
+      </c>
+      <c r="AX6">
+        <v>180.10400000000001</v>
+      </c>
+      <c r="AY6">
+        <v>185.511</v>
+      </c>
+      <c r="AZ6">
+        <v>193.095</v>
+      </c>
+      <c r="BA6">
+        <v>246.40799999999999</v>
+      </c>
+      <c r="BB6">
+        <v>183.05</v>
+      </c>
+      <c r="BC6">
+        <v>205.36199999999999</v>
+      </c>
+      <c r="BD6">
+        <v>261.68400000000003</v>
+      </c>
+      <c r="BE6">
+        <v>159.755</v>
+      </c>
+      <c r="BF6">
+        <v>196.708</v>
+      </c>
+      <c r="BG6">
+        <v>201.886</v>
+      </c>
+      <c r="BH6">
+        <v>194.76499999999999</v>
+      </c>
+      <c r="BI6">
+        <v>183.36500000000001</v>
+      </c>
+      <c r="BJ6">
+        <v>188.71799999999999</v>
+      </c>
+      <c r="BK6">
+        <v>187.61099999999999</v>
+      </c>
+      <c r="BL6">
+        <v>193.172</v>
+      </c>
+      <c r="BM6">
+        <v>193.215</v>
+      </c>
+      <c r="BN6">
+        <v>181.10499999999999</v>
+      </c>
+      <c r="BO6">
+        <v>187.084</v>
+      </c>
+      <c r="BP6">
+        <v>185.876</v>
+      </c>
+      <c r="BQ6">
+        <v>194.83199999999999</v>
+      </c>
+      <c r="BR6">
+        <v>186.10499999999999</v>
+      </c>
+      <c r="BS6">
+        <v>181.08</v>
+      </c>
+      <c r="BT6">
+        <v>181.40899999999999</v>
+      </c>
+      <c r="BU6">
+        <v>187.66200000000001</v>
+      </c>
+      <c r="BV6">
+        <v>186.27799999999999</v>
+      </c>
+      <c r="BW6">
+        <v>188.154</v>
+      </c>
+      <c r="BX6">
+        <v>202.00200000000001</v>
+      </c>
+      <c r="BY6">
+        <v>217.67099999999999</v>
+      </c>
+      <c r="BZ6">
+        <v>179.13200000000001</v>
+      </c>
+      <c r="CA6">
+        <v>187.76499999999999</v>
+      </c>
+      <c r="CB6">
+        <v>178.25899999999999</v>
+      </c>
+      <c r="CC6">
+        <v>261.95600000000002</v>
+      </c>
+      <c r="CD6">
+        <v>212.63200000000001</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG6">
+        <v>188.631</v>
+      </c>
+      <c r="CH6">
+        <v>186.923</v>
+      </c>
+      <c r="CI6">
+        <v>183.13499999999999</v>
+      </c>
+      <c r="CJ6">
+        <v>170.5</v>
+      </c>
+      <c r="CK6">
+        <v>178.25899999999999</v>
+      </c>
+      <c r="CL6">
+        <v>212.679</v>
+      </c>
+      <c r="CM6">
+        <v>200.357</v>
+      </c>
+      <c r="CN6">
+        <v>213.40100000000001</v>
+      </c>
+      <c r="CO6">
+        <v>210.42500000000001</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR6">
+        <v>41</v>
+      </c>
+      <c r="CS6">
+        <v>0.63583000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AC7" s="9"/>
+      <c r="AJ7">
+        <v>5</v>
+      </c>
+      <c r="AK7">
+        <v>100</v>
+      </c>
+      <c r="AL7">
+        <v>0.99</v>
+      </c>
+      <c r="AM7">
+        <v>0.01</v>
+      </c>
+      <c r="AN7">
+        <v>210.554</v>
+      </c>
+      <c r="AO7">
+        <v>200.804</v>
+      </c>
+      <c r="AP7">
+        <v>609.40200000000004</v>
+      </c>
+      <c r="AQ7">
+        <v>187.59800000000001</v>
+      </c>
+      <c r="AR7">
+        <v>182.191</v>
+      </c>
+      <c r="AS7">
+        <v>200.071</v>
+      </c>
+      <c r="AT7">
+        <v>298.625</v>
+      </c>
+      <c r="AU7">
+        <v>208.39599999999999</v>
+      </c>
+      <c r="AV7">
+        <v>205.77199999999999</v>
+      </c>
+      <c r="AW7">
+        <v>202.971</v>
+      </c>
+      <c r="AX7">
+        <v>199.251</v>
+      </c>
+      <c r="AY7">
+        <v>200.07300000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>209.72900000000001</v>
+      </c>
+      <c r="BA7">
+        <v>278.19200000000001</v>
+      </c>
+      <c r="BB7">
+        <v>198.80500000000001</v>
+      </c>
+      <c r="BC7">
+        <v>244.09299999999999</v>
+      </c>
+      <c r="BD7">
+        <v>262.33100000000002</v>
+      </c>
+      <c r="BE7">
+        <v>164.11199999999999</v>
+      </c>
+      <c r="BF7">
+        <v>215.358</v>
+      </c>
+      <c r="BG7">
+        <v>222.33600000000001</v>
+      </c>
+      <c r="BH7">
+        <v>208.94300000000001</v>
+      </c>
+      <c r="BI7">
+        <v>198.48699999999999</v>
+      </c>
+      <c r="BJ7">
+        <v>207.18</v>
+      </c>
+      <c r="BK7">
+        <v>203.68199999999999</v>
+      </c>
+      <c r="BL7">
+        <v>213.37700000000001</v>
+      </c>
+      <c r="BM7">
+        <v>217.863</v>
+      </c>
+      <c r="BN7">
+        <v>199.227</v>
+      </c>
+      <c r="BO7">
+        <v>200.297</v>
+      </c>
+      <c r="BP7">
+        <v>202.667</v>
+      </c>
+      <c r="BQ7">
+        <v>215.10499999999999</v>
+      </c>
+      <c r="BR7">
+        <v>221.024</v>
+      </c>
+      <c r="BS7">
+        <v>190.70599999999999</v>
+      </c>
+      <c r="BT7">
+        <v>194.69200000000001</v>
+      </c>
+      <c r="BU7">
+        <v>204.75899999999999</v>
+      </c>
+      <c r="BV7">
+        <v>198.06700000000001</v>
+      </c>
+      <c r="BW7">
+        <v>210.679</v>
+      </c>
+      <c r="BX7">
+        <v>223.38399999999999</v>
+      </c>
+      <c r="BY7">
+        <v>239.191</v>
+      </c>
+      <c r="BZ7">
+        <v>192.40100000000001</v>
+      </c>
+      <c r="CA7">
+        <v>206.458</v>
+      </c>
+      <c r="CB7">
+        <v>187.59800000000001</v>
+      </c>
+      <c r="CC7">
+        <v>298.625</v>
+      </c>
+      <c r="CD7">
+        <v>240.22900000000001</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG7">
+        <v>201.06100000000001</v>
+      </c>
+      <c r="CH7">
+        <v>202.59399999999999</v>
+      </c>
+      <c r="CI7">
+        <v>194.45699999999999</v>
+      </c>
+      <c r="CJ7">
+        <v>189.07599999999999</v>
+      </c>
+      <c r="CK7">
+        <v>187.59800000000001</v>
+      </c>
+      <c r="CL7">
+        <v>244.38900000000001</v>
+      </c>
+      <c r="CM7">
+        <v>224.54900000000001</v>
+      </c>
+      <c r="CN7">
+        <v>232.28200000000001</v>
+      </c>
+      <c r="CO7">
+        <v>243.768</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR7">
+        <v>41</v>
+      </c>
+      <c r="CS7">
+        <v>0.63396799999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AC8" s="9"/>
+      <c r="AJ8">
+        <v>6</v>
+      </c>
+      <c r="AK8">
+        <v>250</v>
+      </c>
+      <c r="AL8">
+        <v>0.996</v>
+      </c>
+      <c r="AM8">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AN8">
+        <v>241.089</v>
+      </c>
+      <c r="AO8">
+        <v>222.62</v>
+      </c>
+      <c r="AP8">
+        <v>742.78899999999999</v>
+      </c>
+      <c r="AQ8">
+        <v>198.75700000000001</v>
+      </c>
+      <c r="AR8">
+        <v>199.81700000000001</v>
+      </c>
+      <c r="AS8">
+        <v>218.64599999999999</v>
+      </c>
+      <c r="AT8">
+        <v>347.09899999999999</v>
+      </c>
+      <c r="AU8">
+        <v>232.94</v>
+      </c>
+      <c r="AV8">
+        <v>230.55500000000001</v>
+      </c>
+      <c r="AW8">
+        <v>223.441</v>
+      </c>
+      <c r="AX8">
+        <v>227.46299999999999</v>
+      </c>
+      <c r="AY8">
+        <v>218.649</v>
+      </c>
+      <c r="AZ8">
+        <v>231.172</v>
+      </c>
+      <c r="BA8">
+        <v>319.99700000000001</v>
+      </c>
+      <c r="BB8">
+        <v>219.54499999999999</v>
+      </c>
+      <c r="BC8">
+        <v>306.59300000000002</v>
+      </c>
+      <c r="BD8">
+        <v>263.05</v>
+      </c>
+      <c r="BE8">
+        <v>168.959</v>
+      </c>
+      <c r="BF8">
+        <v>239.91300000000001</v>
+      </c>
+      <c r="BG8">
+        <v>249.261</v>
+      </c>
+      <c r="BH8">
+        <v>226.125</v>
+      </c>
+      <c r="BI8">
+        <v>218.47200000000001</v>
+      </c>
+      <c r="BJ8">
+        <v>232.56200000000001</v>
+      </c>
+      <c r="BK8">
+        <v>224.58600000000001</v>
+      </c>
+      <c r="BL8">
+        <v>241.19399999999999</v>
+      </c>
+      <c r="BM8">
+        <v>254.345</v>
+      </c>
+      <c r="BN8">
+        <v>226.476</v>
+      </c>
+      <c r="BO8">
+        <v>216.501</v>
+      </c>
+      <c r="BP8">
+        <v>224.863</v>
+      </c>
+      <c r="BQ8">
+        <v>241.905</v>
+      </c>
+      <c r="BR8">
+        <v>296.20100000000002</v>
+      </c>
+      <c r="BS8">
+        <v>202.184</v>
+      </c>
+      <c r="BT8">
+        <v>212.11199999999999</v>
+      </c>
+      <c r="BU8">
+        <v>227.614</v>
+      </c>
+      <c r="BV8">
+        <v>212.35900000000001</v>
+      </c>
+      <c r="BW8">
+        <v>244.392</v>
+      </c>
+      <c r="BX8">
+        <v>251.64500000000001</v>
+      </c>
+      <c r="BY8">
+        <v>265.20299999999997</v>
+      </c>
+      <c r="BZ8">
+        <v>209.56200000000001</v>
+      </c>
+      <c r="CA8">
+        <v>232.529</v>
+      </c>
+      <c r="CB8">
+        <v>198.75700000000001</v>
+      </c>
+      <c r="CC8">
+        <v>347.09899999999999</v>
+      </c>
+      <c r="CD8">
+        <v>277.20100000000002</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG8">
+        <v>216.13300000000001</v>
+      </c>
+      <c r="CH8">
+        <v>222.88399999999999</v>
+      </c>
+      <c r="CI8">
+        <v>208.185</v>
+      </c>
+      <c r="CJ8">
+        <v>219.30600000000001</v>
+      </c>
+      <c r="CK8">
+        <v>198.75700000000001</v>
+      </c>
+      <c r="CL8">
+        <v>288.71300000000002</v>
+      </c>
+      <c r="CM8">
+        <v>257.07299999999998</v>
+      </c>
+      <c r="CN8">
+        <v>257.14299999999997</v>
+      </c>
+      <c r="CO8">
+        <v>295.86</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ8" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR8">
+        <v>41</v>
+      </c>
+      <c r="CS8">
+        <v>0.63285800000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AC9" s="9"/>
+      <c r="AJ9">
+        <v>7</v>
+      </c>
+      <c r="AK9">
+        <v>500</v>
+      </c>
+      <c r="AL9">
+        <v>0.998</v>
+      </c>
+      <c r="AM9">
+        <v>2E-3</v>
+      </c>
+      <c r="AN9">
+        <v>267.14699999999999</v>
+      </c>
+      <c r="AO9">
+        <v>239.51900000000001</v>
+      </c>
+      <c r="AP9">
+        <v>844.95299999999997</v>
+      </c>
+      <c r="AQ9">
+        <v>206.50200000000001</v>
+      </c>
+      <c r="AR9">
+        <v>213.08699999999999</v>
+      </c>
+      <c r="AS9">
+        <v>232.30500000000001</v>
+      </c>
+      <c r="AT9">
+        <v>383.76799999999997</v>
+      </c>
+      <c r="AU9">
+        <v>251.50700000000001</v>
+      </c>
+      <c r="AV9">
+        <v>250.12200000000001</v>
+      </c>
+      <c r="AW9">
+        <v>238.70500000000001</v>
+      </c>
+      <c r="AX9">
+        <v>251.32400000000001</v>
+      </c>
+      <c r="AY9">
+        <v>232.30799999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>247.10300000000001</v>
+      </c>
+      <c r="BA9">
+        <v>351.5</v>
+      </c>
+      <c r="BB9">
+        <v>235.20400000000001</v>
+      </c>
+      <c r="BC9">
+        <v>363.62900000000002</v>
+      </c>
+      <c r="BD9">
+        <v>263.51900000000001</v>
+      </c>
+      <c r="BE9">
+        <v>172.11799999999999</v>
+      </c>
+      <c r="BF9">
+        <v>258.45499999999998</v>
+      </c>
+      <c r="BG9">
+        <v>269.59199999999998</v>
+      </c>
+      <c r="BH9">
+        <v>238.17699999999999</v>
+      </c>
+      <c r="BI9">
+        <v>233.589</v>
+      </c>
+      <c r="BJ9">
+        <v>252.65899999999999</v>
+      </c>
+      <c r="BK9">
+        <v>240.22499999999999</v>
+      </c>
+      <c r="BL9">
+        <v>263.15100000000001</v>
+      </c>
+      <c r="BM9">
+        <v>285.17500000000001</v>
+      </c>
+      <c r="BN9">
+        <v>250.161</v>
+      </c>
+      <c r="BO9">
+        <v>227.977</v>
+      </c>
+      <c r="BP9">
+        <v>241.654</v>
+      </c>
+      <c r="BQ9">
+        <v>262.178</v>
+      </c>
+      <c r="BR9">
+        <v>387.74599999999998</v>
+      </c>
+      <c r="BS9">
+        <v>210.136</v>
+      </c>
+      <c r="BT9">
+        <v>225.24199999999999</v>
+      </c>
+      <c r="BU9">
+        <v>245.19900000000001</v>
+      </c>
+      <c r="BV9">
+        <v>222.39699999999999</v>
+      </c>
+      <c r="BW9">
+        <v>273.33100000000002</v>
+      </c>
+      <c r="BX9">
+        <v>273.024</v>
+      </c>
+      <c r="BY9">
+        <v>283.38600000000002</v>
+      </c>
+      <c r="BZ9">
+        <v>222.38800000000001</v>
+      </c>
+      <c r="CA9">
+        <v>253.49100000000001</v>
+      </c>
+      <c r="CB9">
+        <v>206.50200000000001</v>
+      </c>
+      <c r="CC9">
+        <v>383.76799999999997</v>
+      </c>
+      <c r="CD9">
+        <v>305.44900000000001</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF9" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG9">
+        <v>226.71799999999999</v>
+      </c>
+      <c r="CH9">
+        <v>237.999</v>
+      </c>
+      <c r="CI9">
+        <v>217.827</v>
+      </c>
+      <c r="CJ9">
+        <v>247.762</v>
+      </c>
+      <c r="CK9">
+        <v>206.50200000000001</v>
+      </c>
+      <c r="CL9">
+        <v>323.74799999999999</v>
+      </c>
+      <c r="CM9">
+        <v>282.036</v>
+      </c>
+      <c r="CN9">
+        <v>275.91399999999999</v>
+      </c>
+      <c r="CO9">
+        <v>342.44799999999998</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR9">
+        <v>41</v>
+      </c>
+      <c r="CS9">
+        <v>0.63248899999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AC10" s="9"/>
+      <c r="AJ10">
+        <v>8</v>
+      </c>
+      <c r="AK10">
+        <v>750</v>
+      </c>
+      <c r="AL10">
+        <v>0.99866699999999997</v>
+      </c>
+      <c r="AM10">
+        <v>1.33333E-3</v>
+      </c>
+      <c r="AN10">
+        <v>283.85599999999999</v>
+      </c>
+      <c r="AO10">
+        <v>249.59800000000001</v>
+      </c>
+      <c r="AP10">
+        <v>905.11800000000005</v>
+      </c>
+      <c r="AQ10">
+        <v>210.80500000000001</v>
+      </c>
+      <c r="AR10">
+        <v>220.82900000000001</v>
+      </c>
+      <c r="AS10">
+        <v>240.16499999999999</v>
+      </c>
+      <c r="AT10">
+        <v>405.21800000000002</v>
+      </c>
+      <c r="AU10">
+        <v>262.36799999999999</v>
+      </c>
+      <c r="AV10">
+        <v>261.93900000000002</v>
+      </c>
+      <c r="AW10">
+        <v>247.566</v>
+      </c>
+      <c r="AX10">
+        <v>266.40199999999999</v>
+      </c>
+      <c r="AY10">
+        <v>240.16900000000001</v>
+      </c>
+      <c r="AZ10">
+        <v>256.33600000000001</v>
+      </c>
+      <c r="BA10">
+        <v>369.88799999999998</v>
+      </c>
+      <c r="BB10">
+        <v>244.357</v>
+      </c>
+      <c r="BC10">
+        <v>401.34899999999999</v>
+      </c>
+      <c r="BD10">
+        <v>263.76900000000001</v>
+      </c>
+      <c r="BE10">
+        <v>173.80600000000001</v>
+      </c>
+      <c r="BF10">
+        <v>269.29399999999998</v>
+      </c>
+      <c r="BG10">
+        <v>281.47800000000001</v>
+      </c>
+      <c r="BH10">
+        <v>244.91</v>
+      </c>
+      <c r="BI10">
+        <v>242.43199999999999</v>
+      </c>
+      <c r="BJ10">
+        <v>264.822</v>
+      </c>
+      <c r="BK10">
+        <v>249.322</v>
+      </c>
+      <c r="BL10">
+        <v>276.38200000000001</v>
+      </c>
+      <c r="BM10">
+        <v>304.59699999999998</v>
+      </c>
+      <c r="BN10">
+        <v>265.44200000000001</v>
+      </c>
+      <c r="BO10">
+        <v>234.42400000000001</v>
+      </c>
+      <c r="BP10">
+        <v>251.476</v>
+      </c>
+      <c r="BQ10">
+        <v>274.03699999999998</v>
+      </c>
+      <c r="BR10">
+        <v>461.58100000000002</v>
+      </c>
+      <c r="BS10">
+        <v>214.548</v>
+      </c>
+      <c r="BT10">
+        <v>232.91300000000001</v>
+      </c>
+      <c r="BU10">
+        <v>255.63</v>
+      </c>
+      <c r="BV10">
+        <v>228.011</v>
+      </c>
+      <c r="BW10">
+        <v>291.8</v>
+      </c>
+      <c r="BX10">
+        <v>285.52999999999997</v>
+      </c>
+      <c r="BY10">
+        <v>293.52</v>
+      </c>
+      <c r="BZ10">
+        <v>229.85900000000001</v>
+      </c>
+      <c r="CA10">
+        <v>266.315</v>
+      </c>
+      <c r="CB10">
+        <v>210.80500000000001</v>
+      </c>
+      <c r="CC10">
+        <v>405.21800000000002</v>
+      </c>
+      <c r="CD10">
+        <v>322.06299999999999</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF10" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG10">
+        <v>232.637</v>
+      </c>
+      <c r="CH10">
+        <v>246.76900000000001</v>
+      </c>
+      <c r="CI10">
+        <v>223.21799999999999</v>
+      </c>
+      <c r="CJ10">
+        <v>267.17599999999999</v>
+      </c>
+      <c r="CK10">
+        <v>210.80500000000001</v>
+      </c>
+      <c r="CL10">
+        <v>344.75400000000002</v>
+      </c>
+      <c r="CM10">
+        <v>296.767</v>
+      </c>
+      <c r="CN10">
+        <v>286.88799999999998</v>
+      </c>
+      <c r="CO10">
+        <v>373.01100000000002</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ10" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR10">
+        <v>41</v>
+      </c>
+      <c r="CS10">
+        <v>0.63236599999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="29:97" x14ac:dyDescent="0.45">
+      <c r="AC11" s="9"/>
+      <c r="AJ11">
+        <v>9</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>0.999</v>
+      </c>
+      <c r="AM11">
+        <v>1E-3</v>
+      </c>
+      <c r="AN11">
+        <v>296.47300000000001</v>
+      </c>
+      <c r="AO11">
+        <v>256.84500000000003</v>
+      </c>
+      <c r="AP11">
+        <v>947.96299999999997</v>
+      </c>
+      <c r="AQ11">
+        <v>213.767</v>
+      </c>
+      <c r="AR11">
+        <v>226.315</v>
+      </c>
+      <c r="AS11">
+        <v>245.69200000000001</v>
+      </c>
+      <c r="AT11">
+        <v>420.43700000000001</v>
+      </c>
+      <c r="AU11">
+        <v>270.07400000000001</v>
+      </c>
+      <c r="AV11">
+        <v>270.50299999999999</v>
+      </c>
+      <c r="AW11">
+        <v>253.827</v>
+      </c>
+      <c r="AX11">
+        <v>277.63799999999998</v>
+      </c>
+      <c r="AY11">
+        <v>245.696</v>
+      </c>
+      <c r="AZ11">
+        <v>262.85599999999999</v>
+      </c>
+      <c r="BA11">
+        <v>382.91899999999998</v>
+      </c>
+      <c r="BB11">
+        <v>250.851</v>
+      </c>
+      <c r="BC11">
+        <v>430.214</v>
+      </c>
+      <c r="BD11">
+        <v>263.93799999999999</v>
+      </c>
+      <c r="BE11">
+        <v>174.94300000000001</v>
+      </c>
+      <c r="BF11">
+        <v>276.98200000000003</v>
+      </c>
+      <c r="BG11">
+        <v>289.90899999999999</v>
+      </c>
+      <c r="BH11">
+        <v>249.56</v>
+      </c>
+      <c r="BI11">
+        <v>248.70699999999999</v>
+      </c>
+      <c r="BJ11">
+        <v>273.64699999999999</v>
+      </c>
+      <c r="BK11">
+        <v>255.75899999999999</v>
+      </c>
+      <c r="BL11">
+        <v>285.94799999999998</v>
+      </c>
+      <c r="BM11">
+        <v>319.029</v>
+      </c>
+      <c r="BN11">
+        <v>276.98500000000001</v>
+      </c>
+      <c r="BO11">
+        <v>238.89</v>
+      </c>
+      <c r="BP11">
+        <v>258.44499999999999</v>
+      </c>
+      <c r="BQ11">
+        <v>282.45100000000002</v>
+      </c>
+      <c r="BR11">
+        <v>525.79100000000005</v>
+      </c>
+      <c r="BS11">
+        <v>217.583</v>
+      </c>
+      <c r="BT11">
+        <v>238.35300000000001</v>
+      </c>
+      <c r="BU11">
+        <v>263.10199999999998</v>
+      </c>
+      <c r="BV11">
+        <v>231.892</v>
+      </c>
+      <c r="BW11">
+        <v>305.649</v>
+      </c>
+      <c r="BX11">
+        <v>294.40300000000002</v>
+      </c>
+      <c r="BY11">
+        <v>300.50700000000001</v>
+      </c>
+      <c r="BZ11">
+        <v>235.154</v>
+      </c>
+      <c r="CA11">
+        <v>275.68599999999998</v>
+      </c>
+      <c r="CB11">
+        <v>213.767</v>
+      </c>
+      <c r="CC11">
+        <v>420.43700000000001</v>
+      </c>
+      <c r="CD11">
+        <v>333.88600000000002</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>96</v>
+      </c>
+      <c r="CF11" t="s">
+        <v>96</v>
+      </c>
+      <c r="CG11">
+        <v>236.727</v>
+      </c>
+      <c r="CH11">
+        <v>252.96299999999999</v>
+      </c>
+      <c r="CI11">
+        <v>226.94399999999999</v>
+      </c>
+      <c r="CJ11">
+        <v>282.38299999999998</v>
+      </c>
+      <c r="CK11">
+        <v>213.767</v>
+      </c>
+      <c r="CL11">
+        <v>359.86399999999998</v>
+      </c>
+      <c r="CM11">
+        <v>307.27300000000002</v>
+      </c>
+      <c r="CN11">
+        <v>294.67200000000003</v>
+      </c>
+      <c r="CO11">
+        <v>396.33</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ11" t="s">
+        <v>97</v>
+      </c>
+      <c r="CR11">
+        <v>41</v>
+      </c>
+      <c r="CS11">
+        <v>0.63230500000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EEC4ED-A2A6-48CB-9363-E12F4E5CCB23}">
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -13944,8 +17567,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2165B25E-5849-4D0E-BE2E-04E16316E776}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66B822B-9B57-4CCE-806F-6F770B4082B7}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
@@ -13962,24 +17585,24 @@
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B2" s="5">
-        <v>25020260</v>
+        <v>25020280</v>
       </c>
       <c r="C2" s="5">
-        <v>25020260</v>
+        <v>25020280</v>
       </c>
       <c r="D2" s="5">
-        <v>25020260</v>
+        <v>25020280</v>
       </c>
       <c r="E2" s="5">
-        <v>25020260</v>
+        <v>25020280</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
@@ -13988,19 +17611,19 @@
       </c>
       <c r="B3" s="5" t="str">
         <f>_xlfn.CONCAT(B2,"-",B1)</f>
-        <v>25020260-Excel-Gumbel</v>
+        <v>25020280-Excel-Gumbel</v>
       </c>
       <c r="C3" s="5" t="str">
         <f t="shared" ref="C3:E3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
-        <v>25020260-R.HydroTools-Gumbel</v>
+        <v>25020280-R.HydroTools-Gumbel</v>
       </c>
       <c r="D3" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>25020260-R.HydroTools-Invgauss</v>
+        <v>25020280-R.HydroTools-levy_stable</v>
       </c>
       <c r="E3" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>25020260-R.HydroTools-powernorm</v>
+        <v>25020280-R.HydroTools-fisk</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -14008,16 +17631,16 @@
         <v>2.33</v>
       </c>
       <c r="B4" s="6">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C4" s="6">
-        <v>126.64700000000001</v>
+        <v>123.529</v>
       </c>
       <c r="D4" s="6">
-        <v>114.58799999999999</v>
+        <v>107.05200000000001</v>
       </c>
       <c r="E4" s="6">
-        <v>116.089</v>
+        <v>107.17100000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -14025,16 +17648,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="6">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C5" s="6">
-        <v>148.64699999999999</v>
+        <v>148.44499999999999</v>
       </c>
       <c r="D5" s="6">
-        <v>137.27699999999999</v>
+        <v>124.768</v>
       </c>
       <c r="E5" s="6">
-        <v>138.012</v>
+        <v>125.602</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -14042,16 +17665,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="6">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C6" s="6">
-        <v>166.56700000000001</v>
+        <v>168.738</v>
       </c>
       <c r="D6" s="6">
-        <v>154.149</v>
+        <v>139.649</v>
       </c>
       <c r="E6" s="6">
-        <v>153.345</v>
+        <v>141.155</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -14059,16 +17682,16 @@
         <v>25</v>
       </c>
       <c r="B7" s="6">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="C7" s="6">
-        <v>189.208</v>
+        <v>194.37899999999999</v>
       </c>
       <c r="D7" s="6">
-        <v>173.86199999999999</v>
+        <v>162.364</v>
       </c>
       <c r="E7" s="6">
-        <v>170.226</v>
+        <v>162.54300000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -14076,16 +17699,16 @@
         <v>50</v>
       </c>
       <c r="B8" s="6">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="C8" s="6">
-        <v>206.00399999999999</v>
+        <v>213.40100000000001</v>
       </c>
       <c r="D8" s="6">
-        <v>187.59200000000001</v>
+        <v>186.10499999999999</v>
       </c>
       <c r="E8" s="6">
-        <v>181.36799999999999</v>
+        <v>180.10400000000001</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -14093,195 +17716,16 @@
         <v>100</v>
       </c>
       <c r="B9" s="6">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="C9" s="6">
-        <v>222.67599999999999</v>
+        <v>232.28200000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>200.636</v>
+        <v>221.024</v>
       </c>
       <c r="E9" s="6">
-        <v>191.523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
-      <c r="D13" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4705146-3AD3-466C-A74B-8A5D295CE547}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="34.86328125" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="5">
-        <v>25020230</v>
-      </c>
-      <c r="C2" s="5">
-        <v>25020230</v>
-      </c>
-      <c r="D2" s="5">
-        <v>25020230</v>
-      </c>
-      <c r="E2" s="5">
-        <v>25020230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <f>_xlfn.CONCAT(B2,"-",B1)</f>
-        <v>25020230-Excel-Gumbel</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <f t="shared" ref="C3:E3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
-        <v>25020230-R.HydroTools-Gumbel</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>25020230-R.HydroTools-Betaprime</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>25020230-R.HydroTools-Levy_stable</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="6">
-        <v>2.33</v>
-      </c>
-      <c r="B4" s="6">
-        <v>103</v>
-      </c>
-      <c r="C4" s="6">
-        <v>122.61199999999999</v>
-      </c>
-      <c r="D4" s="6">
-        <v>110.43300000000001</v>
-      </c>
-      <c r="E4" s="6">
-        <v>116.01</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="6">
-        <v>5</v>
-      </c>
-      <c r="B5" s="6">
-        <v>132</v>
-      </c>
-      <c r="C5" s="6">
-        <v>147.001</v>
-      </c>
-      <c r="D5" s="6">
-        <v>135.857</v>
-      </c>
-      <c r="E5" s="6">
-        <v>142.06200000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="6">
-        <v>10</v>
-      </c>
-      <c r="B6" s="6">
-        <v>155</v>
-      </c>
-      <c r="C6" s="6">
-        <v>166.86600000000001</v>
-      </c>
-      <c r="D6" s="6">
-        <v>154.33199999999999</v>
-      </c>
-      <c r="E6" s="6">
-        <v>159.34399999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="6">
-        <v>25</v>
-      </c>
-      <c r="B7" s="6">
-        <v>184</v>
-      </c>
-      <c r="C7" s="6">
-        <v>191.965</v>
-      </c>
-      <c r="D7" s="6">
-        <v>175.51300000000001</v>
-      </c>
-      <c r="E7" s="6">
-        <v>177.773</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="6">
-        <v>50</v>
-      </c>
-      <c r="B8" s="6">
-        <v>205</v>
-      </c>
-      <c r="C8" s="6">
-        <v>210.584</v>
-      </c>
-      <c r="D8" s="6">
-        <v>190.035</v>
-      </c>
-      <c r="E8" s="6">
-        <v>189.679</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="6">
-        <v>100</v>
-      </c>
-      <c r="B9" s="6">
-        <v>226</v>
-      </c>
-      <c r="C9" s="6">
-        <v>229.06700000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>203.67599999999999</v>
-      </c>
-      <c r="E9" s="6">
-        <v>200.38800000000001</v>
+        <v>199.251</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.6">
@@ -14303,6 +17747,364 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2165B25E-5849-4D0E-BE2E-04E16316E776}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="34.86328125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="5">
+        <v>25020260</v>
+      </c>
+      <c r="C2" s="5">
+        <v>25020260</v>
+      </c>
+      <c r="D2" s="5">
+        <v>25020260</v>
+      </c>
+      <c r="E2" s="5">
+        <v>25020260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,"-",B1)</f>
+        <v>25020260-Excel-Gumbel</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <f t="shared" ref="C3:E3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
+        <v>25020260-R.HydroTools-Gumbel</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>25020260-R.HydroTools-Invgauss</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>25020260-R.HydroTools-powernorm</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="B4" s="6">
+        <v>107</v>
+      </c>
+      <c r="C4" s="6">
+        <v>126.64700000000001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>114.58799999999999</v>
+      </c>
+      <c r="E4" s="6">
+        <v>116.089</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6">
+        <v>133</v>
+      </c>
+      <c r="C5" s="6">
+        <v>148.64699999999999</v>
+      </c>
+      <c r="D5" s="6">
+        <v>137.27699999999999</v>
+      </c>
+      <c r="E5" s="6">
+        <v>138.012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6">
+        <v>154</v>
+      </c>
+      <c r="C6" s="6">
+        <v>166.56700000000001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>154.149</v>
+      </c>
+      <c r="E6" s="6">
+        <v>153.345</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
+        <v>25</v>
+      </c>
+      <c r="B7" s="6">
+        <v>181</v>
+      </c>
+      <c r="C7" s="6">
+        <v>189.208</v>
+      </c>
+      <c r="D7" s="6">
+        <v>173.86199999999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>170.226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6">
+        <v>201</v>
+      </c>
+      <c r="C8" s="6">
+        <v>206.00399999999999</v>
+      </c>
+      <c r="D8" s="6">
+        <v>187.59200000000001</v>
+      </c>
+      <c r="E8" s="6">
+        <v>181.36799999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
+        <v>100</v>
+      </c>
+      <c r="B9" s="6">
+        <v>220</v>
+      </c>
+      <c r="C9" s="6">
+        <v>222.67599999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>200.636</v>
+      </c>
+      <c r="E9" s="6">
+        <v>191.523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D13" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4705146-3AD3-466C-A74B-8A5D295CE547}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="4.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="34.86328125" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="5">
+        <v>25020230</v>
+      </c>
+      <c r="C2" s="5">
+        <v>25020230</v>
+      </c>
+      <c r="D2" s="5">
+        <v>25020230</v>
+      </c>
+      <c r="E2" s="5">
+        <v>25020230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="str">
+        <f>_xlfn.CONCAT(B2,"-",B1)</f>
+        <v>25020230-Excel-Gumbel</v>
+      </c>
+      <c r="C3" s="5" t="str">
+        <f t="shared" ref="C3:E3" si="0">_xlfn.CONCAT(C2,"-",C1)</f>
+        <v>25020230-R.HydroTools-Gumbel</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>25020230-R.HydroTools-Betaprime</v>
+      </c>
+      <c r="E3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>25020230-R.HydroTools-Levy_stable</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="B4" s="6">
+        <v>103</v>
+      </c>
+      <c r="C4" s="6">
+        <v>122.61199999999999</v>
+      </c>
+      <c r="D4" s="6">
+        <v>110.43300000000001</v>
+      </c>
+      <c r="E4" s="6">
+        <v>116.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6">
+        <v>132</v>
+      </c>
+      <c r="C5" s="6">
+        <v>147.001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>135.857</v>
+      </c>
+      <c r="E5" s="6">
+        <v>142.06200000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6">
+        <v>155</v>
+      </c>
+      <c r="C6" s="6">
+        <v>166.86600000000001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>154.33199999999999</v>
+      </c>
+      <c r="E6" s="6">
+        <v>159.34399999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
+        <v>25</v>
+      </c>
+      <c r="B7" s="6">
+        <v>184</v>
+      </c>
+      <c r="C7" s="6">
+        <v>191.965</v>
+      </c>
+      <c r="D7" s="6">
+        <v>175.51300000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>177.773</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6">
+        <v>205</v>
+      </c>
+      <c r="C8" s="6">
+        <v>210.584</v>
+      </c>
+      <c r="D8" s="6">
+        <v>190.035</v>
+      </c>
+      <c r="E8" s="6">
+        <v>189.679</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
+        <v>100</v>
+      </c>
+      <c r="B9" s="6">
+        <v>226</v>
+      </c>
+      <c r="C9" s="6">
+        <v>229.06700000000001</v>
+      </c>
+      <c r="D9" s="6">
+        <v>203.67599999999999</v>
+      </c>
+      <c r="E9" s="6">
+        <v>200.38800000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="D13" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC3BD22-A60D-404D-A6C3-12A1448027F8}">
   <dimension ref="A1:BH11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
@@ -16407,7 +20209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14F8E49-787B-42A5-8853-3A8AB20BD89C}">
   <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
@@ -17003,29 +20805,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C93394-4CAA-4D45-B4FF-F549FD11CBF9}">
-  <dimension ref="AC7:AC11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="7" spans="29:29" x14ac:dyDescent="0.45">
-      <c r="AC7" s="9"/>
-    </row>
-    <row r="8" spans="29:29" x14ac:dyDescent="0.45">
-      <c r="AC8" s="9"/>
-    </row>
-    <row r="9" spans="29:29" x14ac:dyDescent="0.45">
-      <c r="AC9" s="9"/>
-    </row>
-    <row r="10" spans="29:29" x14ac:dyDescent="0.45">
-      <c r="AC10" s="9"/>
-    </row>
-    <row r="11" spans="29:29" x14ac:dyDescent="0.45">
-      <c r="AC11" s="9"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>